--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,44 @@
       </c>
       <c r="F2" t="n">
         <v>64739.66796875</v>
+      </c>
+      <c r="G2" t="n">
+        <v>65422.140625</v>
+      </c>
+      <c r="H2" t="n">
+        <v>682.47265625</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.043183010720998</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8337426893252096</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-21 03:31:21</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F3" t="n">
+        <v>65243.078125</v>
       </c>
     </row>
   </sheetData>
@@ -506,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,6 +641,24 @@
           <t>64815.089844,64824.550781,64808.476562,64808.160156,64802.359375,64806.531250,64828.597656,64823.746094,64816.613281,64800.351562,64826.062500,64828.230469,64824.910156,64816.347656,64825.363281,64801.781250,64806.285156,64794.035156,64793.492188,64777.175781,64758.878906,64753.386719,64754.367188,64739.667969</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>64493.660156,64072.468750,63859.031250,64214.238281,63997.351562,64138.718750,64242.351562,64944.011719,64585.988281,64274.640625,64346.628906,65551.007812,65454.011719,65533.519531,65192.320312,65085.019531,65327.988281,65241.691406,65105.441406,65213.050781,65522.308594,65193.531250,65366.949219,65422.140625</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>321.429688,752.082031,949.445312,593.921875,805.007812,667.812500,586.246093,120.265625,230.625000,525.710937,479.433594,722.777343,629.101563,717.171875,366.957032,283.238281,521.703125,447.656250,311.949218,435.875000,763.429688,440.144531,612.582031,682.472656</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.498390,1.173799,1.486783,0.924907,1.257877,1.041200,0.912554,0.185184,0.357082,0.817913,0.745080,1.102618,0.961135,1.094359,0.562884,0.435182,0.798591,0.686151,0.479145,0.668386,1.165145,0.675135,0.937143,1.043183</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8337426893252096</v>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>64798.414062,64764.507812,64799.359375,64769.902344,64736.546875,64759.699219,64806.539062,64815.250000,64743.437500,64795.441406,64725.976562,64781.035156,64720.757812,64740.308594,64756.507812,64765.671875,64754.437500,64649.843750,64675.953125,64729.785156,64680.433594,64724.714844,64629.343750,64646.097656</t>
@@ -616,6 +672,49 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>64710.097656,64689.917969,64637.527344,64609.113281,64553.968750,64521.765625,64537.410156,64490.687500,64466.773438,64411.289062,64410.832031,64405.558594,64396.894531,64328.085938,64336.730469,64320.058594,64303.929688,64255.546875,64221.316406,64179.574219,64142.125000,64103.078125,64101.390625,64054.679688</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-21 03:31:21</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>65390.125000,65366.765625,65365.957031,65362.347656,65362.050781,65336.343750,65342.496094,65342.218750,65356.285156,65359.960938,65380.570312,65373.320312,65357.515625,65369.242188,65372.226562,65360.484375,65352.843750,65342.140625,65317.195312,65305.792969,65282.464844,65262.496094,65265.554688,65243.078125</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>65337.789062,65335.812500,65375.402344,65308.121094,65293.695312,65288.136719,65277.812500,65314.917969,65274.468750,65334.781250,65285.578125,65278.484375,65227.210938,65269.414062,65289.339844,65314.679688,65257.406250,65175.847656,65217.785156,65217.257812,65184.750000,65237.613281,65111.691406,65146.718750</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>65085.742188,64981.207031,64879.656250,64805.175781,64758.140625,64664.121094,64607.695312,64571.843750,64550.238281,64506.441406,64491.835938,64441.058594,64417.695312,64363.644531,64339.347656,64292.394531,64229.109375,64225.859375,64103.445312,64070.152344,64013.531250,63963.902344,63929.718750,63892.632812</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>65202.445312,65125.511719,65063.246094,65039.031250,64973.878906,64918.976562,64910.542969,64874.953125,64876.609375,64845.542969,64844.355469,64844.578125,64814.906250,64771.085938,64767.714844,64748.222656,64695.691406,64680.171875,64608.242188,64589.144531,64527.203125,64493.960938,64482.011719,64435.406250</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,6 +531,44 @@
       </c>
       <c r="F3" t="n">
         <v>65243.078125</v>
+      </c>
+      <c r="G3" t="n">
+        <v>66274.453125</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1031.375</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.556218046876566</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.438379771084452</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-22 03:29:53</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F4" t="n">
+        <v>66005.9765625</v>
       </c>
     </row>
   </sheetData>
@@ -544,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,6 +740,24 @@
           <t>65390.125000,65366.765625,65365.957031,65362.347656,65362.050781,65336.343750,65342.496094,65342.218750,65356.285156,65359.960938,65380.570312,65373.320312,65357.515625,65369.242188,65372.226562,65360.484375,65352.843750,65342.140625,65317.195312,65305.792969,65282.464844,65262.496094,65265.554688,65243.078125</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>65472.011719,65704.101562,65874.679688,66143.031250,66186.390625,66250.781250,66148.210938,66309.468750,66508.851562,66742.921875,66809.718750,66648.398438,66512.632812,66170.421875,66282.007812,66415.437500,66370.007812,66346.906250,66268.007812,66405.007812,66586.687500,66389.179688,66268.007812,66274.453125</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>81.886719,337.335938,508.722657,780.683594,824.339844,914.437500,805.714843,967.250000,1152.566407,1382.960937,1429.148438,1275.078125,1155.117188,801.179687,909.781250,1054.953125,1017.164062,1004.765625,950.812500,1099.214843,1304.222656,1126.683593,1002.453125,1031.375000</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.125071,0.513417,0.772258,1.180296,1.245482,1.380267,1.218045,1.458691,1.732952,2.072071,2.139133,1.913141,1.736688,1.210782,1.372592,1.588416,1.532566,1.514412,1.434799,1.655319,1.958684,1.697089,1.512726,1.556218</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1.438379771084452</v>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>65337.789062,65335.812500,65375.402344,65308.121094,65293.695312,65288.136719,65277.812500,65314.917969,65274.468750,65334.781250,65285.578125,65278.484375,65227.210938,65269.414062,65289.339844,65314.679688,65257.406250,65175.847656,65217.785156,65217.257812,65184.750000,65237.613281,65111.691406,65146.718750</t>
@@ -715,6 +771,49 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>65202.445312,65125.511719,65063.246094,65039.031250,64973.878906,64918.976562,64910.542969,64874.953125,64876.609375,64845.542969,64844.355469,64844.578125,64814.906250,64771.085938,64767.714844,64748.222656,64695.691406,64680.171875,64608.242188,64589.144531,64527.203125,64493.960938,64482.011719,64435.406250</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-22 03:29:53</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>66259.257812,66222.171875,66207.718750,66216.398438,66200.187500,66203.085938,66205.468750,66186.617188,66204.390625,66172.500000,66177.843750,66185.406250,66152.406250,66137.687500,66128.000000,66130.046875,66113.718750,66100.312500,66088.523438,66075.820312,66064.679688,66030.664062,66047.320312,66005.976562</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>66170.953125,66203.429688,66163.187500,66156.078125,66131.984375,66101.156250,66129.945312,66138.421875,66102.718750,66071.148438,66047.390625,66034.984375,66034.960938,65952.257812,65980.101562,66035.820312,66002.242188,65879.851562,65950.820312,65887.460938,65942.164062,65917.109375,65833.804688,65825.710938</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>65977.812500,65861.718750,65740.585938,65667.710938,65574.531250,65519.757812,65444.457031,65403.015625,65378.867188,65302.183594,65243.160156,65182.257812,65125.046875,65031.968750,64973.734375,64926.730469,64854.867188,64829.632812,64689.148438,64624.308594,64578.062500,64523.210938,64485.445312,64435.703125</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>66105.257812,66002.476562,65922.218750,65909.328125,65826.851562,65799.171875,65764.453125,65724.484375,65741.398438,65676.820312,65648.273438,65627.171875,65562.515625,65490.898438,65437.031250,65428.105469,65386.578125,65351.000000,65288.320312,65240.914062,65200.035156,65153.324219,65141.605469,65090.667969</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,6 +569,44 @@
       </c>
       <c r="F4" t="n">
         <v>66005.9765625</v>
+      </c>
+      <c r="G4" t="n">
+        <v>65643.8203125</v>
+      </c>
+      <c r="H4" t="n">
+        <v>362.15625</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5516989234872999</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3478518534520157</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-23 03:34:52</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F5" t="n">
+        <v>65287.01953125</v>
       </c>
     </row>
   </sheetData>
@@ -582,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,6 +839,24 @@
           <t>66259.257812,66222.171875,66207.718750,66216.398438,66200.187500,66203.085938,66205.468750,66186.617188,66204.390625,66172.500000,66177.843750,66185.406250,66152.406250,66137.687500,66128.000000,66130.046875,66113.718750,66100.312500,66088.523438,66075.820312,66064.679688,66030.664062,66047.320312,66005.976562</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>66336.000000,65937.328125,65891.273438,65795.273438,65940.476562,65884.273438,66008.992188,65972.500000,65587.757812,65914.742188,65760.953125,66020.039062,66208.523438,66001.640625,65858.296875,65900.992188,65892.421875,66040.257812,66014.382812,66086.609375,66033.593750,65799.007812,65777.226562,65643.820312</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>76.742188,284.843750,316.445312,421.125001,259.710938,318.812501,196.476562,214.117188,616.632812,257.757812,416.890625,165.367188,56.117188,136.046875,269.703125,229.054688,221.296875,60.054688,74.140626,10.789063,31.085938,231.656249,270.093749,362.156249</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.115687,0.431992,0.480254,0.640054,0.393857,0.483898,0.297651,0.324555,0.940164,0.391047,0.633949,0.250480,0.084758,0.206127,0.409520,0.347574,0.335846,0.090936,0.112310,0.016326,0.047076,0.352066,0.410619,0.551699</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3478518534520157</v>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>66170.953125,66203.429688,66163.187500,66156.078125,66131.984375,66101.156250,66129.945312,66138.421875,66102.718750,66071.148438,66047.390625,66034.984375,66034.960938,65952.257812,65980.101562,66035.820312,66002.242188,65879.851562,65950.820312,65887.460938,65942.164062,65917.109375,65833.804688,65825.710938</t>
@@ -814,6 +870,49 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>66105.257812,66002.476562,65922.218750,65909.328125,65826.851562,65799.171875,65764.453125,65724.484375,65741.398438,65676.820312,65648.273438,65627.171875,65562.515625,65490.898438,65437.031250,65428.105469,65386.578125,65351.000000,65288.320312,65240.914062,65200.035156,65153.324219,65141.605469,65090.667969</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-23 03:34:52</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>65635.414062,65591.062500,65578.632812,65561.375000,65526.011719,65530.488281,65532.269531,65529.335938,65531.105469,65507.812500,65487.972656,65497.992188,65473.156250,65458.136719,65453.878906,65440.187500,65428.199219,65398.722656,65384.656250,65379.574219,65364.578125,65346.226562,65327.726562,65287.019531</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>65590.781250,65602.093750,65535.156250,65508.277344,65508.460938,65512.894531,65517.761719,65483.410156,65449.410156,65484.375000,65390.718750,65384.078125,65419.156250,65386.160156,65389.695312,65359.160156,65347.792969,65268.148438,65306.027344,65277.593750,65277.226562,65247.507812,65229.277344,65188.093750</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>65369.226562,65258.765625,65164.562500,65098.886719,64985.148438,64929.027344,64878.257812,64838.574219,64785.355469,64720.562500,64653.054688,64653.628906,64605.050781,64550.062500,64502.953125,64446.945312,64393.371094,64352.550781,64232.792969,64188.621094,64154.410156,64114.347656,64052.210938,63991.789062</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>65481.328125,65385.632812,65320.308594,65282.203125,65202.257812,65175.699219,65146.812500,65122.210938,65088.058594,65045.917969,65001.378906,65020.328125,64962.675781,64922.554688,64891.605469,64856.660156,64813.390625,64766.136719,64720.531250,64690.042969,64653.058594,64608.953125,64579.558594,64526.148438</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,6 +607,44 @@
       </c>
       <c r="F5" t="n">
         <v>65287.01953125</v>
+      </c>
+      <c r="G5" t="n">
+        <v>65305.30859375</v>
+      </c>
+      <c r="H5" t="n">
+        <v>18.2890625</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.02800547596179699</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5302708216226634</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-24 03:31:17</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>24</v>
+      </c>
+      <c r="F6" t="n">
+        <v>64904.43359375</v>
       </c>
     </row>
   </sheetData>
@@ -620,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -900,6 +938,24 @@
           <t>65635.414062,65591.062500,65578.632812,65561.375000,65526.011719,65530.488281,65532.269531,65529.335938,65531.105469,65507.812500,65487.972656,65497.992188,65473.156250,65458.136719,65453.878906,65440.187500,65428.199219,65398.722656,65384.656250,65379.574219,65364.578125,65346.226562,65327.726562,65287.019531</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>65570.539062,65660.203125,65758.109375,65394.808594,65619.226562,65607.070312,65708.562500,65525.218750,65132.140625,64836.000000,64868.199219,64898.250000,64691.011719,64619.121094,64807.578125,64778.218750,65095.281250,65120.191406,65142.511719,65051.230469,64925.851562,65030.000000,65066.980469,65305.308594</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>64.874999,69.140625,179.476563,166.566406,93.214843,76.582032,176.292969,4.117188,398.964844,671.812500,619.773437,599.742188,782.144531,839.015625,646.300781,661.968750,332.917969,278.531250,242.144531,328.343750,438.726562,316.226562,260.746093,18.289063</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.098939,0.105301,0.272934,0.254709,0.142054,0.116728,0.268295,0.006283,0.612547,1.036172,0.955435,0.924127,1.209047,1.298401,0.997261,1.021900,0.511432,0.427719,0.371715,0.504746,0.675735,0.486278,0.400735,0.028005</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5302708216226634</v>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>65590.781250,65602.093750,65535.156250,65508.277344,65508.460938,65512.894531,65517.761719,65483.410156,65449.410156,65484.375000,65390.718750,65384.078125,65419.156250,65386.160156,65389.695312,65359.160156,65347.792969,65268.148438,65306.027344,65277.593750,65277.226562,65247.507812,65229.277344,65188.093750</t>
@@ -913,6 +969,49 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>65481.328125,65385.632812,65320.308594,65282.203125,65202.257812,65175.699219,65146.812500,65122.210938,65088.058594,65045.917969,65001.378906,65020.328125,64962.675781,64922.554688,64891.605469,64856.660156,64813.390625,64766.136719,64720.531250,64690.042969,64653.058594,64608.953125,64579.558594,64526.148438</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-24 03:31:17</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>24</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>65267.113281,65241.535156,65205.152344,65196.167969,65161.304688,65161.605469,65148.710938,65110.593750,65094.656250,65075.832031,65058.632812,65061.156250,65054.902344,65037.972656,65021.480469,65006.531250,65007.160156,64998.417969,64981.730469,64978.707031,64974.125000,64931.289062,64926.503906,64904.433594</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>65242.914062,65267.355469,65183.378906,65149.726562,65155.089844,65146.664062,65131.046875,65082.750000,65037.437500,65042.667969,64979.417969,64923.109375,64990.828125,65000.277344,64971.925781,64938.687500,64926.988281,64891.660156,64944.140625,64876.835938,64877.179688,64824.113281,64862.429688,64833.570312</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>64923.503906,64808.070312,64700.820312,64637.457031,64522.906250,64463.167969,64397.437500,64307.792969,64227.320312,64167.425781,64120.144531,64107.371094,64068.773438,64017.781250,63979.769531,63930.796875,63896.507812,63874.562500,63753.246094,63727.746094,63720.414062,63648.773438,63621.378906,63569.347656</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>65073.781250,64978.355469,64884.707031,64850.660156,64771.152344,64727.554688,64681.183594,64607.566406,64571.667969,64515.707031,64477.820312,64482.207031,64453.597656,64399.113281,64378.621094,64348.429688,64331.027344,64295.218750,64252.937500,64231.675781,64219.101562,64143.585938,64137.171875,64090.171875</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,6 +645,44 @@
       </c>
       <c r="F6" t="n">
         <v>64904.43359375</v>
+      </c>
+      <c r="G6" t="n">
+        <v>64017.01171875</v>
+      </c>
+      <c r="H6" t="n">
+        <v>887.421875</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.38622820899352</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.013755627928459</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-25 03:29:10</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>24</v>
+      </c>
+      <c r="F7" t="n">
+        <v>63942.1640625</v>
       </c>
     </row>
   </sheetData>
@@ -658,7 +696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,6 +1037,24 @@
           <t>65267.113281,65241.535156,65205.152344,65196.167969,65161.304688,65161.605469,65148.710938,65110.593750,65094.656250,65075.832031,65058.632812,65061.156250,65054.902344,65037.972656,65021.480469,65006.531250,65007.160156,64998.417969,64981.730469,64978.707031,64974.125000,64931.289062,64926.503906,64904.433594</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>65240.968750,65268.421875,65426.941406,65453.988281,65259.019531,65064.289062,64903.089844,65027.648438,64715.980469,64063.070312,63990.910156,64031.101562,63889.839844,64117.050781,64210.898438,64158.339844,64102.601562,64088.089844,64100.519531,64083.320312,64009.011719,64005.011719,63980.570312,64017.011719</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>26.144531,26.886719,221.789062,257.820312,97.714843,97.316407,245.621094,82.945312,378.675781,1012.761718,1067.722656,1030.054688,1165.062500,920.921875,810.582032,848.191406,904.558593,910.328125,881.210938,895.386718,965.113281,926.277343,945.933593,887.421875</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.040074,0.041194,0.338987,0.393895,0.149734,0.149570,0.378443,0.127554,0.585135,1.580882,1.668554,1.608679,1.823549,1.436314,1.262375,1.322028,1.411111,1.420433,1.374733,1.397223,1.507777,1.447195,1.478470,1.386228</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1.013755627928459</v>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>65242.914062,65267.355469,65183.378906,65149.726562,65155.089844,65146.664062,65131.046875,65082.750000,65037.437500,65042.667969,64979.417969,64923.109375,64990.828125,65000.277344,64971.925781,64938.687500,64926.988281,64891.660156,64944.140625,64876.835938,64877.179688,64824.113281,64862.429688,64833.570312</t>
@@ -1012,6 +1068,49 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>65073.781250,64978.355469,64884.707031,64850.660156,64771.152344,64727.554688,64681.183594,64607.566406,64571.667969,64515.707031,64477.820312,64482.207031,64453.597656,64399.113281,64378.621094,64348.429688,64331.027344,64295.218750,64252.937500,64231.675781,64219.101562,64143.585938,64137.171875,64090.171875</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-25 03:29:10</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>24</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>64025.277344,64018.460938,64019.113281,64023.300781,64003.691406,64004.730469,64009.449219,63997.367188,63975.679688,63961.207031,63953.386719,63960.527344,63958.816406,63946.839844,63957.195312,63963.632812,63968.285156,63969.191406,63973.109375,63963.167969,63984.773438,63963.261719,63955.382812,63942.164062</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>64003.429688,64056.992188,63995.332031,64004.433594,64004.320312,64029.105469,64015.093750,63978.347656,63963.781250,63944.734375,63914.855469,63902.000000,63933.535156,63945.023438,63967.839844,63923.632812,63956.304688,63960.644531,63975.441406,63900.921875,63955.503906,63901.101562,63922.125000,63889.148438</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>63759.644531,63679.867188,63606.597656,63556.867188,63464.023438,63406.890625,63366.335938,63315.101562,63222.878906,63163.769531,63122.023438,63114.382812,63074.824219,63051.484375,63034.179688,62996.593750,62964.734375,62947.917969,62856.890625,62836.476562,62820.023438,62769.402344,62741.519531,62706.457031</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>63869.339844,63804.449219,63743.800781,63724.503906,63662.562500,63625.648438,63606.429688,63562.027344,63522.613281,63467.113281,63427.609375,63434.843750,63416.453125,63389.773438,63404.457031,63379.589844,63352.933594,63319.582031,63316.027344,63283.167969,63284.847656,63209.816406,63214.300781,63179.031250</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,6 +683,44 @@
       </c>
       <c r="F7" t="n">
         <v>63942.1640625</v>
+      </c>
+      <c r="G7" t="n">
+        <v>64507.12890625</v>
+      </c>
+      <c r="H7" t="n">
+        <v>564.96484375</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8758176860902911</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.3700240956205296</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-26 03:42:05</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>24</v>
+      </c>
+      <c r="F8" t="n">
+        <v>64552.8125</v>
       </c>
     </row>
   </sheetData>
@@ -696,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,6 +1136,24 @@
           <t>64025.277344,64018.460938,64019.113281,64023.300781,64003.691406,64004.730469,64009.449219,63997.367188,63975.679688,63961.207031,63953.386719,63960.527344,63958.816406,63946.839844,63957.195312,63963.632812,63968.285156,63969.191406,63973.109375,63963.167969,63984.773438,63963.261719,63955.382812,63942.164062</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>64117.191406,63959.488281,63952.210938,63951.750000,63808.550781,63939.371094,64000.078125,64005.738281,64055.980469,64103.890625,64149.070312,64117.691406,64151.308594,64203.289062,64353.789062,64328.718750,64275.050781,64288.011719,64352.269531,64339.281250,64450.000000,64402.820312,64460.898438,64507.128906</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>91.914062,58.972657,66.902343,71.550781,195.140625,65.359375,9.371094,8.371093,80.300781,142.683594,195.683593,157.164062,192.492188,256.449218,396.593750,365.085938,306.765625,318.820313,379.160156,376.113281,465.226562,439.558593,505.515625,564.964844</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.143353,0.092203,0.104613,0.111882,0.305822,0.102221,0.014642,0.013079,0.125360,0.222582,0.305045,0.245118,0.300060,0.399433,0.616271,0.567532,0.477270,0.495925,0.589195,0.584578,0.721841,0.682515,0.784221,0.875818</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.3700240956205296</v>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>64003.429688,64056.992188,63995.332031,64004.433594,64004.320312,64029.105469,64015.093750,63978.347656,63963.781250,63944.734375,63914.855469,63902.000000,63933.535156,63945.023438,63967.839844,63923.632812,63956.304688,63960.644531,63975.441406,63900.921875,63955.503906,63901.101562,63922.125000,63889.148438</t>
@@ -1111,6 +1167,49 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>63869.339844,63804.449219,63743.800781,63724.503906,63662.562500,63625.648438,63606.429688,63562.027344,63522.613281,63467.113281,63427.609375,63434.843750,63416.453125,63389.773438,63404.457031,63379.589844,63352.933594,63319.582031,63316.027344,63283.167969,63284.847656,63209.816406,63214.300781,63179.031250</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-26 03:42:05</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>24</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>64524.765625,64530.667969,64537.375000,64568.597656,64562.261719,64577.132812,64583.464844,64592.585938,64581.410156,64567.703125,64562.242188,64568.843750,64583.035156,64560.097656,64572.125000,64578.914062,64580.367188,64580.496094,64567.804688,64569.667969,64575.789062,64552.996094,64553.839844,64552.812500</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>64537.156250,64525.609375,64528.757812,64522.578125,64558.445312,64569.074219,64574.269531,64570.917969,64556.187500,64523.855469,64508.265625,64495.847656,64547.031250,64535.539062,64530.625000,64520.187500,64547.054688,64532.957031,64544.593750,64493.675781,64524.097656,64498.546875,64506.796875,64509.062500</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>64342.992188,64299.964844,64229.066406,64203.292969,64142.414062,64102.867188,64072.945312,64042.957031,63988.062500,63925.515625,63910.480469,63857.292969,63844.500000,63784.246094,63793.375000,63763.777344,63714.523438,63693.042969,63585.457031,63583.863281,63541.148438,63495.859375,63460.621094,63435.484375</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>64414.640625,64388.101562,64337.476562,64340.769531,64278.285156,64285.113281,64288.398438,64269.542969,64234.105469,64178.914062,64146.480469,64145.066406,64131.539062,64072.542969,64116.621094,64106.625000,64046.621094,64025.855469,63996.078125,63967.542969,63949.265625,63889.390625,63893.207031,63861.468750</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -721,6 +721,44 @@
       </c>
       <c r="F8" t="n">
         <v>64552.8125</v>
+      </c>
+      <c r="G8" t="n">
+        <v>65236.6015625</v>
+      </c>
+      <c r="H8" t="n">
+        <v>683.7890625</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.048167817026604</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.3933555109496066</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-27 03:51:36</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>24</v>
+      </c>
+      <c r="F9" t="n">
+        <v>65282.84375</v>
       </c>
     </row>
   </sheetData>
@@ -734,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1197,6 +1235,24 @@
           <t>64524.765625,64530.667969,64537.375000,64568.597656,64562.261719,64577.132812,64583.464844,64592.585938,64581.410156,64567.703125,64562.242188,64568.843750,64583.035156,64560.097656,64572.125000,64578.914062,64580.367188,64580.496094,64567.804688,64569.667969,64575.789062,64552.996094,64553.839844,64552.812500</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>64465.078125,64352.941406,64375.730469,64309.421875,64423.011719,64481.640625,64454.171875,64450.480469,64405.031250,64466.460938,64658.980469,64710.281250,64674.941406,64644.058594,64686.191406,64641.089844,64595.261719,64791.121094,65347.960938,65336.308594,65069.988281,65141.429688,65115.390625,65236.601562</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>59.687500,177.726563,161.644531,259.175781,139.250000,95.492187,129.292969,142.105469,176.378906,101.242188,96.738281,141.437500,91.906250,83.960938,114.066406,62.175782,14.894531,210.625000,780.156250,766.640625,494.199219,588.433593,561.550781,683.789062</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.092589,0.276175,0.251095,0.403014,0.216149,0.148092,0.200597,0.220488,0.273859,0.157046,0.149613,0.218570,0.142105,0.129882,0.176338,0.096186,0.023058,0.325083,1.193849,1.173376,0.759489,0.903317,0.862393,1.048168</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.3933555109496066</v>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>64537.156250,64525.609375,64528.757812,64522.578125,64558.445312,64569.074219,64574.269531,64570.917969,64556.187500,64523.855469,64508.265625,64495.847656,64547.031250,64535.539062,64530.625000,64520.187500,64547.054688,64532.957031,64544.593750,64493.675781,64524.097656,64498.546875,64506.796875,64509.062500</t>
@@ -1210,6 +1266,49 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>64414.640625,64388.101562,64337.476562,64340.769531,64278.285156,64285.113281,64288.398438,64269.542969,64234.105469,64178.914062,64146.480469,64145.066406,64131.539062,64072.542969,64116.621094,64106.625000,64046.621094,64025.855469,63996.078125,63967.542969,63949.265625,63889.390625,63893.207031,63861.468750</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-27 03:51:36</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>24</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>65246.875000,65230.781250,65249.332031,65256.996094,65266.617188,65278.062500,65289.695312,65284.109375,65265.812500,65254.894531,65269.101562,65285.765625,65296.328125,65276.722656,65302.289062,65287.273438,65313.976562,65308.285156,65313.207031,65296.964844,65302.761719,65293.476562,65282.640625,65282.843750</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>65220.847656,65219.882812,65215.750000,65246.539062,65264.753906,65227.007812,65282.906250,65264.992188,65193.738281,65225.742188,65202.828125,65180.929688,65244.527344,65219.847656,65241.335938,65238.492188,65273.949219,65212.355469,65233.304688,65218.542969,65222.437500,65235.164062,65187.105469,65179.964844</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>64961.644531,64883.160156,64836.636719,64785.894531,64739.492188,64700.882812,64687.339844,64645.554688,64591.808594,64529.582031,64531.246094,64485.019531,64468.128906,64417.066406,64409.347656,64365.914062,64350.171875,64332.457031,64241.695312,64187.121094,64172.937500,64135.171875,64077.847656,64049.855469</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>65080.281250,65024.628906,64990.125000,64973.312500,64924.718750,64915.535156,64919.109375,64890.750000,64856.941406,64799.343750,64783.363281,64790.636719,64798.449219,64729.019531,64763.742188,64747.988281,64731.472656,64715.343750,64683.632812,64636.214844,64627.925781,64583.097656,64550.058594,64524.128906</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -759,6 +759,44 @@
       </c>
       <c r="F9" t="n">
         <v>65282.84375</v>
+      </c>
+      <c r="G9" t="n">
+        <v>63239.62109375</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2043.22265625</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.230921724247859</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.090284066889077</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-28 03:22:42</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>24</v>
+      </c>
+      <c r="F10" t="n">
+        <v>63516.42578125</v>
       </c>
     </row>
   </sheetData>
@@ -772,7 +810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1296,6 +1334,24 @@
           <t>65246.875000,65230.781250,65249.332031,65256.996094,65266.617188,65278.062500,65289.695312,65284.109375,65265.812500,65254.894531,65269.101562,65285.765625,65296.328125,65276.722656,65302.289062,65287.273438,65313.976562,65308.285156,65313.207031,65296.964844,65302.761719,65293.476562,65282.640625,65282.843750</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>65229.531250,65403.988281,65358.000000,65165.101562,65104.488281,65203.000000,65277.988281,65040.320312,65024.179688,65150.718750,64611.750000,64475.171875,64828.300781,64951.078125,64801.300781,64919.308594,64903.488281,64760.648438,63746.238281,63693.570312,63423.460938,63170.480469,63115.558594,63239.621094</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>17.343750,173.207031,108.667969,91.894532,162.128907,75.062500,11.707031,243.789062,241.632812,104.175781,657.351562,810.593750,468.027344,325.644531,500.988281,367.964844,410.488281,547.636718,1566.968750,1603.394532,1879.300782,2122.996093,2167.082031,2043.222656</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.026589,0.264826,0.166266,0.141018,0.249029,0.115121,0.017934,0.374828,0.371605,0.159900,1.017387,1.257218,0.721949,0.501369,0.773115,0.566803,0.632460,0.845632,2.458135,2.517357,2.963100,3.360741,3.433515,3.230922</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1.090284066889077</v>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>65220.847656,65219.882812,65215.750000,65246.539062,65264.753906,65227.007812,65282.906250,65264.992188,65193.738281,65225.742188,65202.828125,65180.929688,65244.527344,65219.847656,65241.335938,65238.492188,65273.949219,65212.355469,65233.304688,65218.542969,65222.437500,65235.164062,65187.105469,65179.964844</t>
@@ -1309,6 +1365,49 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>65080.281250,65024.628906,64990.125000,64973.312500,64924.718750,64915.535156,64919.109375,64890.750000,64856.941406,64799.343750,64783.363281,64790.636719,64798.449219,64729.019531,64763.742188,64747.988281,64731.472656,64715.343750,64683.632812,64636.214844,64627.925781,64583.097656,64550.058594,64524.128906</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-28 03:22:42</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>24</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>63285.843750,63310.320312,63323.398438,63344.847656,63351.257812,63361.550781,63395.187500,63401.316406,63387.164062,63406.589844,63415.371094,63435.738281,63449.394531,63460.957031,63496.695312,63498.753906,63479.195312,63482.781250,63495.613281,63505.070312,63525.785156,63515.109375,63500.343750,63516.425781</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>63274.421875,63344.390625,63324.644531,63333.089844,63389.273438,63404.417969,63451.585938,63369.726562,63423.589844,63377.433594,63412.421875,63431.449219,63473.082031,63462.062500,63512.250000,63463.066406,63496.886719,63489.402344,63498.796875,63497.882812,63518.496094,63480.476562,63486.550781,63490.902344</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>62902.621094,62821.148438,62727.261719,62649.980469,62576.402344,62507.496094,62500.250000,62435.714844,62378.410156,62339.589844,62308.835938,62287.335938,62272.695312,62239.148438,62265.113281,62210.539062,62149.843750,62112.050781,62022.136719,61997.328125,62002.636719,61964.503906,61952.015625,61927.304688</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>63049.230469,62997.476562,62924.222656,62903.296875,62844.445312,62812.812500,62827.503906,62781.992188,62761.207031,62728.242188,62688.675781,62720.632812,62717.292969,62697.667969,62753.574219,62722.105469,62641.570312,62611.621094,62606.859375,62592.367188,62595.312500,62565.867188,62551.824219,62534.824219</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,44 @@
       </c>
       <c r="F10" t="n">
         <v>63516.42578125</v>
+      </c>
+      <c r="G10" t="n">
+        <v>63814.078125</v>
+      </c>
+      <c r="H10" t="n">
+        <v>297.65234375</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.466436799677579</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.3098912951980715</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-29 03:23:40</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>24</v>
+      </c>
+      <c r="F11" t="n">
+        <v>63880.0234375</v>
       </c>
     </row>
   </sheetData>
@@ -810,7 +848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1395,6 +1433,24 @@
           <t>63285.843750,63310.320312,63323.398438,63344.847656,63351.257812,63361.550781,63395.187500,63401.316406,63387.164062,63406.589844,63415.371094,63435.738281,63449.394531,63460.957031,63496.695312,63498.753906,63479.195312,63482.781250,63495.613281,63505.070312,63525.785156,63515.109375,63500.343750,63516.425781</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>63285.460938,63385.519531,63564.289062,63435.800781,63353.511719,63322.281250,63401.109375,63414.078125,63475.121094,63026.070312,63336.050781,63857.589844,63973.398438,63615.921875,63656.578125,63817.558594,63834.480469,63892.890625,63704.941406,63533.089844,63883.000000,63619.078125,63883.011719,63814.078125</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.382812,75.199219,240.890625,90.953125,2.253907,39.269531,5.921875,12.761719,87.957032,380.519532,79.320313,421.851563,524.003907,154.964844,159.882813,318.804688,355.285157,410.109375,209.328125,28.019532,357.214844,103.968750,382.667969,297.652344</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.000605,0.118638,0.378972,0.143378,0.003558,0.062015,0.009340,0.020124,0.138569,0.603749,0.125237,0.660613,0.819097,0.243594,0.251165,0.499556,0.556572,0.641870,0.328590,0.044102,0.559170,0.163424,0.599014,0.466437</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.3098912951980715</v>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>63274.421875,63344.390625,63324.644531,63333.089844,63389.273438,63404.417969,63451.585938,63369.726562,63423.589844,63377.433594,63412.421875,63431.449219,63473.082031,63462.062500,63512.250000,63463.066406,63496.886719,63489.402344,63498.796875,63497.882812,63518.496094,63480.476562,63486.550781,63490.902344</t>
@@ -1408,6 +1464,49 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>63049.230469,62997.476562,62924.222656,62903.296875,62844.445312,62812.812500,62827.503906,62781.992188,62761.207031,62728.242188,62688.675781,62720.632812,62717.292969,62697.667969,62753.574219,62722.105469,62641.570312,62611.621094,62606.859375,62592.367188,62595.312500,62565.867188,62551.824219,62534.824219</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-29 03:23:40</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>24</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>63801.078125,63815.832031,63805.742188,63818.859375,63828.179688,63820.511719,63821.300781,63839.007812,63833.511719,63817.257812,63831.140625,63839.304688,63861.730469,63877.488281,63890.156250,63904.679688,63894.300781,63898.214844,63896.261719,63894.824219,63915.875000,63895.679688,63885.351562,63880.023438</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>63815.011719,63826.250000,63820.789062,63807.320312,63811.515625,63818.308594,63860.519531,63816.316406,63825.542969,63770.480469,63821.968750,63781.417969,63856.949219,63877.843750,63887.121094,63806.289062,63833.035156,63891.433594,63871.496094,63823.597656,63880.035156,63824.824219,63836.695312,63814.316406</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>63464.738281,63410.792969,63297.406250,63258.015625,63200.355469,63137.355469,63093.214844,63033.136719,62991.500000,62946.441406,62926.609375,62895.398438,62895.539062,62869.761719,62888.734375,62869.011719,62815.449219,62811.535156,62704.773438,62686.781250,62678.191406,62641.164062,62621.757812,62601.890625</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>63591.449219,63563.613281,63474.953125,63465.371094,63424.781250,63383.109375,63371.429688,63340.953125,63320.128906,63276.074219,63258.730469,63274.257812,63264.007812,63252.894531,63297.445312,63287.511719,63218.718750,63211.578125,63190.683594,63166.390625,63168.042969,63135.761719,63128.429688,63097.535156</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -835,6 +835,44 @@
       </c>
       <c r="F11" t="n">
         <v>63880.0234375</v>
+      </c>
+      <c r="G11" t="n">
+        <v>64091.359375</v>
+      </c>
+      <c r="H11" t="n">
+        <v>211.3359375</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.3297416992881499</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.53938140577514</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-30 02:57:59</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>24</v>
+      </c>
+      <c r="F12" t="n">
+        <v>63987.41015625</v>
       </c>
     </row>
   </sheetData>
@@ -848,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1494,6 +1532,24 @@
           <t>63801.078125,63815.832031,63805.742188,63818.859375,63828.179688,63820.511719,63821.300781,63839.007812,63833.511719,63817.257812,63831.140625,63839.304688,63861.730469,63877.488281,63890.156250,63904.679688,63894.300781,63898.214844,63896.261719,63894.824219,63915.875000,63895.679688,63885.351562,63880.023438</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>63878.160156,63976.871094,64352.601562,64477.691406,64342.351562,64611.281250,64395.339844,64437.000000,64201.910156,64585.761719,64016.070312,63867.929688,63717.058594,64183.019531,64430.519531,63526.828125,63439.988281,63778.140625,63853.988281,63875.851562,63586.230469,64187.648438,64091.359375,64091.359375</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>77.082031,161.039063,546.859375,658.832031,514.171875,790.769531,574.039063,597.992188,368.398437,768.503907,184.929688,28.625000,144.671875,305.531250,540.363281,377.851563,454.312500,120.074219,42.273438,18.972657,329.644531,291.968750,206.007813,211.335937</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.120670,0.251715,0.849786,1.021798,0.799119,1.223888,0.891430,0.928026,0.573812,1.189897,0.288880,0.044819,0.227054,0.476031,0.838676,0.594791,0.716130,0.188269,0.066203,0.029702,0.518421,0.454867,0.321428,0.329742</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.53938140577514</v>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>63815.011719,63826.250000,63820.789062,63807.320312,63811.515625,63818.308594,63860.519531,63816.316406,63825.542969,63770.480469,63821.968750,63781.417969,63856.949219,63877.843750,63887.121094,63806.289062,63833.035156,63891.433594,63871.496094,63823.597656,63880.035156,63824.824219,63836.695312,63814.316406</t>
@@ -1507,6 +1563,49 @@
       <c r="M11" t="inlineStr">
         <is>
           <t>63591.449219,63563.613281,63474.953125,63465.371094,63424.781250,63383.109375,63371.429688,63340.953125,63320.128906,63276.074219,63258.730469,63274.257812,63264.007812,63252.894531,63297.445312,63287.511719,63218.718750,63211.578125,63190.683594,63166.390625,63168.042969,63135.761719,63128.429688,63097.535156</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-30 02:57:59</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>24</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>64070.007812,64079.910156,64061.968750,64067.675781,64050.734375,64066.566406,64077.531250,64079.871094,64062.746094,64063.890625,64028.453125,64043.203125,64058.554688,64054.843750,64046.593750,64041.714844,64029.546875,64041.757812,64047.417969,64049.851562,64043.832031,64011.707031,63989.894531,63987.410156</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>64095.257812,64063.875000,64070.601562,64050.074219,64056.726562,64023.878906,64110.128906,64054.898438,64025.683594,64010.730469,63990.605469,63997.753906,64038.328125,64027.441406,64043.710938,63988.644531,64003.402344,64035.921875,64007.925781,63978.003906,64015.199219,63947.660156,63956.378906,63939.687500</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>63735.250000,63657.722656,63543.343750,63492.437500,63416.203125,63374.257812,63339.050781,63292.304688,63222.019531,63183.765625,63121.375000,63107.976562,63071.027344,63026.113281,62989.769531,62957.753906,62899.464844,62902.820312,62831.968750,62812.234375,62788.867188,62747.285156,62709.980469,62692.484375</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>63862.128906,63819.925781,63734.199219,63704.523438,63639.597656,63629.328125,63622.660156,63580.917969,63542.828125,63514.835938,63450.054688,63474.117188,63463.796875,63421.773438,63425.593750,63407.910156,63326.875000,63346.269531,63327.285156,63318.847656,63291.085938,63253.757812,63224.816406,63212.921875</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,6 +873,44 @@
       </c>
       <c r="F12" t="n">
         <v>63987.41015625</v>
+      </c>
+      <c r="G12" t="n">
+        <v>64230.03125</v>
+      </c>
+      <c r="H12" t="n">
+        <v>242.62109375</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.3777377793973906</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.7645784403125254</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-31 03:39:51</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>24</v>
+      </c>
+      <c r="F13" t="n">
+        <v>64078.9296875</v>
       </c>
     </row>
   </sheetData>
@@ -886,7 +924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1593,6 +1631,24 @@
           <t>64070.007812,64079.910156,64061.968750,64067.675781,64050.734375,64066.566406,64077.531250,64079.871094,64062.746094,64063.890625,64028.453125,64043.203125,64058.554688,64054.843750,64046.593750,64041.714844,64029.546875,64041.757812,64047.417969,64049.851562,64043.832031,64011.707031,63989.894531,63987.410156</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>64071.421875,63933.281250,63947.718750,63915.308594,63918.308594,64211.878906,64480.570312,64472.289062,64700.839844,64839.601562,64950.000000,64614.519531,64658.410156,64750.441406,64809.660156,64634.019531,64727.519531,64711.328125,64670.679688,64788.789062,64721.890625,64677.121094,64493.679688,64230.031250</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1.414063,146.628906,114.250000,152.367187,132.425781,145.312500,403.039062,392.417968,638.093750,775.710938,921.546875,571.316406,599.855468,695.597656,763.066406,592.304687,697.972656,669.570313,623.261718,738.937500,678.058594,665.414063,503.785157,242.621094</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.002207,0.229347,0.178662,0.238389,0.207180,0.226302,0.625055,0.608661,0.986222,1.196354,1.418856,0.884192,0.927730,1.074275,1.177396,0.916398,1.078324,1.034703,0.963747,1.140533,1.047650,1.028824,0.781139,0.377738</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.7645784403125254</v>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>64095.257812,64063.875000,64070.601562,64050.074219,64056.726562,64023.878906,64110.128906,64054.898438,64025.683594,64010.730469,63990.605469,63997.753906,64038.328125,64027.441406,64043.710938,63988.644531,64003.402344,64035.921875,64007.925781,63978.003906,64015.199219,63947.660156,63956.378906,63939.687500</t>
@@ -1606,6 +1662,49 @@
       <c r="M12" t="inlineStr">
         <is>
           <t>63862.128906,63819.925781,63734.199219,63704.523438,63639.597656,63629.328125,63622.660156,63580.917969,63542.828125,63514.835938,63450.054688,63474.117188,63463.796875,63421.773438,63425.593750,63407.910156,63326.875000,63346.269531,63327.285156,63318.847656,63291.085938,63253.757812,63224.816406,63212.921875</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-31 03:39:51</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>24</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>64272.695312,64245.128906,64226.492188,64237.132812,64220.851562,64232.394531,64251.410156,64243.949219,64236.777344,64236.132812,64218.824219,64234.957031,64228.332031,64200.503906,64191.082031,64190.011719,64171.101562,64160.050781,64153.265625,64127.832031,64126.562500,64117.964844,64091.421875,64078.929688</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>64257.925781,64247.777344,64196.046875,64214.714844,64234.125000,64199.457031,64251.441406,64206.324219,64198.820312,64211.433594,64163.710938,64179.976562,64192.511719,64128.121094,64140.980469,64135.597656,64106.906250,64117.222656,64064.425781,64067.339844,64067.546875,64011.929688,64013.792969,63989.699219</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>63960.687500,63850.316406,63740.046875,63694.648438,63597.429688,63547.062500,63514.644531,63464.113281,63400.449219,63353.429688,63313.976562,63285.781250,63233.910156,63164.839844,63134.894531,63082.476562,63036.457031,63005.542969,62922.136719,62864.886719,62839.808594,62812.816406,62768.074219,62731.121094</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>64090.789062,63996.871094,63922.824219,63895.046875,63834.945312,63803.722656,63793.171875,63755.558594,63730.332031,63699.835938,63648.656250,63647.265625,63623.867188,63557.886719,63548.128906,63521.273438,63467.460938,63449.882812,63416.730469,63376.589844,63352.164062,63319.613281,63294.593750,63265.812500</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,6 +911,44 @@
       </c>
       <c r="F13" t="n">
         <v>64078.9296875</v>
+      </c>
+      <c r="G13" t="n">
+        <v>62915.44140625</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1163.48828125</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.849288911027841</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.456573639100343</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-01 03:40:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>24</v>
+      </c>
+      <c r="F14" t="n">
+        <v>62976.19140625</v>
       </c>
     </row>
   </sheetData>
@@ -924,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1692,6 +1730,24 @@
           <t>64272.695312,64245.128906,64226.492188,64237.132812,64220.851562,64232.394531,64251.410156,64243.949219,64236.777344,64236.132812,64218.824219,64234.957031,64228.332031,64200.503906,64191.082031,64190.011719,64171.101562,64160.050781,64153.265625,64127.832031,64126.562500,64117.964844,64091.421875,64078.929688</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>64239.468750,64290.140625,64171.070312,63872.109375,63754.531250,63646.699219,63850.421875,63738.750000,63677.859375,63201.859375,62601.449219,62625.761719,62800.640625,63179.171875,63026.468750,62892.000000,62892.398438,62894.820312,62884.949219,62825.820312,62875.738281,62903.039062,62999.800781,62915.441406</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>33.226562,45.011719,55.421875,365.023437,466.320312,585.695312,400.988281,505.199219,558.917969,1034.273437,1617.375000,1609.195312,1427.691406,1021.332031,1164.613281,1298.011719,1278.703125,1265.230468,1268.316406,1302.011718,1250.824219,1214.925782,1091.621094,1163.488282</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.051723,0.070013,0.086366,0.571491,0.731431,0.920229,0.628012,0.792609,0.877727,1.636460,2.583606,2.569542,2.273371,1.616564,1.847816,2.063874,2.033160,2.011661,2.016884,2.072415,1.989359,1.931426,1.732737,1.849289</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1.456573639100343</v>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>64257.925781,64247.777344,64196.046875,64214.714844,64234.125000,64199.457031,64251.441406,64206.324219,64198.820312,64211.433594,64163.710938,64179.976562,64192.511719,64128.121094,64140.980469,64135.597656,64106.906250,64117.222656,64064.425781,64067.339844,64067.546875,64011.929688,64013.792969,63989.699219</t>
@@ -1705,6 +1761,49 @@
       <c r="M13" t="inlineStr">
         <is>
           <t>64090.789062,63996.871094,63922.824219,63895.046875,63834.945312,63803.722656,63793.171875,63755.558594,63730.332031,63699.835938,63648.656250,63647.265625,63623.867188,63557.886719,63548.128906,63521.273438,63467.460938,63449.882812,63416.730469,63376.589844,63352.164062,63319.613281,63294.593750,63265.812500</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-01 03:40:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>24</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>62927.468750,62933.437500,62929.222656,62941.644531,62931.093750,62933.125000,62945.042969,62932.359375,62912.390625,62925.496094,62924.511719,62927.277344,62927.542969,62935.378906,62939.324219,62937.828125,62924.277344,62944.328125,62947.644531,62968.152344,62969.089844,62973.042969,62961.261719,62976.191406</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>62949.082031,62966.312500,62922.941406,62941.125000,62947.636719,62964.523438,62998.199219,62915.230469,62945.445312,62968.652344,62941.765625,62942.003906,62984.152344,62969.933594,62974.578125,62909.320312,62939.898438,63027.273438,62967.984375,62969.593750,62984.332031,62912.800781,63003.468750,63007.304688</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>62644.828125,62581.921875,62485.050781,62435.523438,62343.382812,62297.488281,62270.843750,62215.085938,62165.996094,62130.367188,62113.562500,62091.945312,62035.074219,62005.585938,62002.835938,61952.472656,61899.859375,61870.890625,61786.339844,61795.855469,61756.750000,61756.207031,61730.753906,61725.074219</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>62750.507812,62703.625000,62630.144531,62607.859375,62546.031250,62521.628906,62512.019531,62472.253906,62454.109375,62435.445312,62395.746094,62413.210938,62364.269531,62358.781250,62385.160156,62349.859375,62288.625000,62265.964844,62254.363281,62269.265625,62244.062500,62228.410156,62216.976562,62224.710938</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -949,6 +949,44 @@
       </c>
       <c r="F14" t="n">
         <v>62976.19140625</v>
+      </c>
+      <c r="G14" t="n">
+        <v>63401.3515625</v>
+      </c>
+      <c r="H14" t="n">
+        <v>425.16015625</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.670585319984676</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.2751092833584172</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-02 03:39:50</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>24</v>
+      </c>
+      <c r="F15" t="n">
+        <v>63459.83203125</v>
       </c>
     </row>
   </sheetData>
@@ -962,7 +1000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1791,6 +1829,24 @@
           <t>62927.468750,62933.437500,62929.222656,62941.644531,62931.093750,62933.125000,62945.042969,62932.359375,62912.390625,62925.496094,62924.511719,62927.277344,62927.542969,62935.378906,62939.324219,62937.828125,62924.277344,62944.328125,62947.644531,62968.152344,62969.089844,62973.042969,62961.261719,62976.191406</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>63035.710938,62965.769531,63013.199219,62988.589844,63061.339844,62993.289062,62999.441406,63016.468750,63039.621094,63005.121094,63066.238281,62938.820312,62879.148438,62652.578125,62523.789062,62471.531250,62604.921875,62761.359375,62765.359375,62766.671875,62775.000000,62921.050781,63381.988281,63401.351562</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>108.242188,32.332031,83.976563,46.945313,130.246094,60.164062,54.398437,84.109375,127.230469,79.625000,141.726562,11.542968,48.394532,282.800781,415.535157,466.296875,319.355469,182.968750,182.285156,201.480469,194.089844,51.992188,420.726562,425.160157</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.171716,0.051349,0.133268,0.074530,0.206539,0.095509,0.086347,0.133472,0.201826,0.126379,0.224727,0.018340,0.076964,0.451379,0.664603,0.746415,0.510112,0.291531,0.290423,0.320999,0.309183,0.082631,0.663795,0.670585</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.2751092833584172</v>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>62949.082031,62966.312500,62922.941406,62941.125000,62947.636719,62964.523438,62998.199219,62915.230469,62945.445312,62968.652344,62941.765625,62942.003906,62984.152344,62969.933594,62974.578125,62909.320312,62939.898438,63027.273438,62967.984375,62969.593750,62984.332031,62912.800781,63003.468750,63007.304688</t>
@@ -1804,6 +1860,49 @@
       <c r="M14" t="inlineStr">
         <is>
           <t>62750.507812,62703.625000,62630.144531,62607.859375,62546.031250,62521.628906,62512.019531,62472.253906,62454.109375,62435.445312,62395.746094,62413.210938,62364.269531,62358.781250,62385.160156,62349.859375,62288.625000,62265.964844,62254.363281,62269.265625,62244.062500,62228.410156,62216.976562,62224.710938</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-02 03:39:50</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>24</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>63339.375000,63363.046875,63367.812500,63382.996094,63406.375000,63419.824219,63420.519531,63435.449219,63428.695312,63423.496094,63407.785156,63418.851562,63422.402344,63414.328125,63411.660156,63400.230469,63401.621094,63421.300781,63407.957031,63424.558594,63445.941406,63426.359375,63430.136719,63459.832031</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>63323.390625,63351.925781,63369.421875,63387.078125,63384.425781,63420.621094,63420.425781,63453.566406,63377.730469,63421.472656,63396.144531,63396.390625,63395.328125,63426.328125,63424.890625,63367.390625,63366.824219,63452.277344,63366.191406,63366.390625,63397.664062,63393.226562,63452.203125,63410.308594</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>63039.886719,62999.222656,62909.667969,62871.585938,62826.593750,62774.960938,62744.367188,62718.609375,62660.441406,62599.039062,62549.628906,62524.414062,62481.351562,62458.078125,62430.988281,62375.957031,62345.046875,62343.312500,62248.335938,62249.746094,62259.117188,62207.832031,62194.750000,62200.078125</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>63160.246094,63142.375000,63080.902344,63063.886719,63036.925781,63008.269531,63016.699219,62991.750000,62970.468750,62921.980469,62856.914062,62883.332031,62851.269531,62815.074219,62824.410156,62798.656250,62752.320312,62747.394531,62720.480469,62730.234375,62742.757812,62670.644531,62682.707031,62696.382812</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -987,6 +987,44 @@
       </c>
       <c r="F15" t="n">
         <v>63459.83203125</v>
+      </c>
+      <c r="G15" t="n">
+        <v>62971.62109375</v>
+      </c>
+      <c r="H15" t="n">
+        <v>488.2109375</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.7752872310102487</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.3482046252174619</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:42:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>24</v>
+      </c>
+      <c r="F16" t="n">
+        <v>62985.734375</v>
       </c>
     </row>
   </sheetData>
@@ -1000,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1890,6 +1928,24 @@
           <t>63339.375000,63363.046875,63367.812500,63382.996094,63406.375000,63419.824219,63420.519531,63435.449219,63428.695312,63423.496094,63407.785156,63418.851562,63422.402344,63414.328125,63411.660156,63400.230469,63401.621094,63421.300781,63407.957031,63424.558594,63445.941406,63426.359375,63430.136719,63459.832031</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>63519.609375,63394.921875,63409.730469,63448.261719,63130.039062,63206.230469,63136.648438,62964.218750,63062.089844,63053.988281,63002.308594,63041.429688,63119.281250,63227.941406,63307.601562,63380.179688,63424.089844,63501.191406,63351.050781,63493.351562,63244.398438,63130.878906,63065.519531,62971.621094</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>180.234375,31.875000,41.917969,65.265625,276.335938,213.593750,283.871093,471.230469,366.605468,369.507813,405.476562,377.421875,303.121094,186.386719,104.058593,20.050782,22.468750,79.890625,56.906250,68.792968,201.542968,295.480469,364.617188,488.210937</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.283746,0.050280,0.066107,0.102864,0.437725,0.337931,0.449614,0.748410,0.581340,0.586018,0.643590,0.598689,0.480235,0.294785,0.164370,0.031636,0.035426,0.125810,0.089827,0.108347,0.318673,0.468044,0.578156,0.775287</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.3482046252174619</v>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>63323.390625,63351.925781,63369.421875,63387.078125,63384.425781,63420.621094,63420.425781,63453.566406,63377.730469,63421.472656,63396.144531,63396.390625,63395.328125,63426.328125,63424.890625,63367.390625,63366.824219,63452.277344,63366.191406,63366.390625,63397.664062,63393.226562,63452.203125,63410.308594</t>
@@ -1903,6 +1959,49 @@
       <c r="M15" t="inlineStr">
         <is>
           <t>63160.246094,63142.375000,63080.902344,63063.886719,63036.925781,63008.269531,63016.699219,62991.750000,62970.468750,62921.980469,62856.914062,62883.332031,62851.269531,62815.074219,62824.410156,62798.656250,62752.320312,62747.394531,62720.480469,62730.234375,62742.757812,62670.644531,62682.707031,62696.382812</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:42:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>24</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>62978.996094,62949.378906,62937.660156,62925.449219,62911.160156,62922.902344,62912.589844,62912.785156,62911.015625,62932.027344,62909.699219,62929.230469,62938.250000,62955.679688,62962.472656,62979.089844,62968.132812,62982.566406,62989.062500,62990.175781,63012.128906,62993.226562,62979.222656,62985.734375</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>62975.949219,62961.929688,62927.972656,62929.414062,62916.175781,62932.964844,62930.332031,62912.265625,62895.546875,62902.414062,62923.144531,62928.636719,62942.367188,62948.117188,62987.062500,62956.714844,62936.285156,63025.847656,62951.718750,62950.695312,62997.136719,62969.433594,62971.828125,62968.570312</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>62761.117188,62674.347656,62585.984375,62511.003906,62439.691406,62382.902344,62354.304688,62298.539062,62234.933594,62187.105469,62126.007812,62106.648438,62066.160156,62034.882812,62002.761719,61959.546875,61918.324219,61902.906250,61842.929688,61809.917969,61809.046875,61783.843750,61754.539062,61730.605469</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>62854.128906,62780.449219,62714.441406,62667.972656,62616.121094,62601.359375,62567.605469,62538.429688,62519.851562,62494.535156,62426.980469,62448.007812,62418.109375,62397.371094,62392.957031,62378.437500,62332.691406,62324.074219,62332.437500,62316.375000,62316.855469,62270.648438,62262.292969,62256.945312</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1025,6 +1025,44 @@
       </c>
       <c r="F16" t="n">
         <v>62985.734375</v>
+      </c>
+      <c r="G16" t="n">
+        <v>63661.44140625</v>
+      </c>
+      <c r="H16" t="n">
+        <v>675.70703125</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.0614070563342</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.8625142263271287</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-04 03:26:07</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>24</v>
+      </c>
+      <c r="F17" t="n">
+        <v>63522.06640625</v>
       </c>
     </row>
   </sheetData>
@@ -1038,7 +1076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1989,6 +2027,24 @@
           <t>62978.996094,62949.378906,62937.660156,62925.449219,62911.160156,62922.902344,62912.589844,62912.785156,62911.015625,62932.027344,62909.699219,62929.230469,62938.250000,62955.679688,62962.472656,62979.089844,62968.132812,62982.566406,62989.062500,62990.175781,63012.128906,62993.226562,62979.222656,62985.734375</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>62707.750000,62743.539062,62541.839844,62524.601562,62457.589844,62749.359375,62656.000000,62481.289062,62622.738281,63267.199219,63899.031250,63624.261719,63708.480469,63852.750000,63808.058594,63802.781250,63736.750000,63540.410156,63553.429688,63466.519531,63302.050781,63782.300781,63758.988281,63661.441406</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>271.246094,205.839843,395.820312,400.847657,453.570312,173.542969,256.589844,431.496093,288.277344,335.171875,989.332031,695.031250,770.230469,897.070312,845.585938,823.691406,768.617188,557.843750,564.367188,476.343750,289.921875,789.074219,779.765625,675.707031</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.432556,0.328065,0.632889,0.641104,0.726205,0.276565,0.409522,0.690600,0.460340,0.529772,1.548274,1.092400,1.208992,1.404905,1.325202,1.290996,1.205925,0.877935,0.888020,0.750543,0.457998,1.237137,1.222989,1.061407</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.8625142263271287</v>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>62975.949219,62961.929688,62927.972656,62929.414062,62916.175781,62932.964844,62930.332031,62912.265625,62895.546875,62902.414062,62923.144531,62928.636719,62942.367188,62948.117188,62987.062500,62956.714844,62936.285156,63025.847656,62951.718750,62950.695312,62997.136719,62969.433594,62971.828125,62968.570312</t>
@@ -2002,6 +2058,49 @@
       <c r="M16" t="inlineStr">
         <is>
           <t>62854.128906,62780.449219,62714.441406,62667.972656,62616.121094,62601.359375,62567.605469,62538.429688,62519.851562,62494.535156,62426.980469,62448.007812,62418.109375,62397.371094,62392.957031,62378.437500,62332.691406,62324.074219,62332.437500,62316.375000,62316.855469,62270.648438,62262.292969,62256.945312</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-04 03:26:07</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>24</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>63637.988281,63620.421875,63611.226562,63608.820312,63607.726562,63616.289062,63602.343750,63601.593750,63609.621094,63604.050781,63612.648438,63618.441406,63611.761719,63612.675781,63613.738281,63587.324219,63584.195312,63569.085938,63565.308594,63541.042969,63542.222656,63525.351562,63510.566406,63522.066406</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>63637.070312,63605.890625,63597.417969,63612.316406,63579.675781,63575.539062,63563.761719,63599.953125,63566.152344,63552.746094,63581.660156,63540.527344,63561.144531,63567.074219,63588.117188,63561.906250,63533.843750,63531.351562,63493.097656,63482.566406,63491.519531,63507.777344,63463.921875,63422.117188</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>63284.519531,63197.238281,63110.023438,63059.082031,62999.925781,62963.148438,62918.925781,62876.074219,62842.453125,62787.542969,62761.070312,62725.398438,62675.300781,62658.074219,62622.863281,62550.796875,62510.976562,62469.785156,62387.707031,62317.769531,62313.941406,62279.621094,62242.015625,62214.945312</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>63431.023438,63366.210938,63291.464844,63277.285156,63233.984375,63211.175781,63184.824219,63168.867188,63164.023438,63129.914062,63091.976562,63088.980469,63052.105469,63037.113281,63028.812500,62988.980469,62937.613281,62911.800781,62878.277344,62835.132812,62825.164062,62769.531250,62747.050781,62750.703125</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,6 +1063,44 @@
       </c>
       <c r="F17" t="n">
         <v>63522.06640625</v>
+      </c>
+      <c r="G17" t="n">
+        <v>64127.94140625</v>
+      </c>
+      <c r="H17" t="n">
+        <v>605.875</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9447909705408859</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5772776785977458</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:21:02</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>24</v>
+      </c>
+      <c r="F18" t="n">
+        <v>64070.78515625</v>
       </c>
     </row>
   </sheetData>
@@ -1076,7 +1114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2088,6 +2126,24 @@
           <t>63637.988281,63620.421875,63611.226562,63608.820312,63607.726562,63616.289062,63602.343750,63601.593750,63609.621094,63604.050781,63612.648438,63618.441406,63611.761719,63612.675781,63613.738281,63587.324219,63584.195312,63569.085938,63565.308594,63541.042969,63542.222656,63525.351562,63510.566406,63522.066406</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>63975.449219,63768.851562,63607.160156,63617.410156,63514.769531,63534.578125,63694.148438,63853.320312,63840.640625,63619.851562,64069.250000,64068.738281,63899.718750,63919.718750,64261.410156,64181.000000,64299.078125,64148.511719,64189.621094,63934.531250,63934.531250,64284.789062,64315.949219,64127.941406</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>337.460938,148.429688,4.066406,8.589844,92.957031,81.710937,91.804688,251.726562,231.019531,15.800782,456.601562,450.296875,287.957031,307.042969,647.671875,593.675781,714.882813,579.425781,624.312500,393.488281,392.308594,759.437500,805.382813,605.875000</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.527485,0.232762,0.006393,0.013502,0.146355,0.128609,0.144134,0.394226,0.361869,0.024836,0.712669,0.702834,0.450639,0.480357,1.007871,0.925002,1.111809,0.903257,0.972607,0.615455,0.613610,1.181364,1.252229,0.944791</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5772776785977458</v>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>63637.070312,63605.890625,63597.417969,63612.316406,63579.675781,63575.539062,63563.761719,63599.953125,63566.152344,63552.746094,63581.660156,63540.527344,63561.144531,63567.074219,63588.117188,63561.906250,63533.843750,63531.351562,63493.097656,63482.566406,63491.519531,63507.777344,63463.921875,63422.117188</t>
@@ -2101,6 +2157,49 @@
       <c r="M17" t="inlineStr">
         <is>
           <t>63431.023438,63366.210938,63291.464844,63277.285156,63233.984375,63211.175781,63184.824219,63168.867188,63164.023438,63129.914062,63091.976562,63088.980469,63052.105469,63037.113281,63028.812500,62988.980469,62937.613281,62911.800781,62878.277344,62835.132812,62825.164062,62769.531250,62747.050781,62750.703125</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:21:02</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>24</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>64135.910156,64129.187500,64113.386719,64120.546875,64117.585938,64106.773438,64106.675781,64103.539062,64116.531250,64112.730469,64135.343750,64149.617188,64161.222656,64152.988281,64165.757812,64147.714844,64158.492188,64154.648438,64142.031250,64109.324219,64099.246094,64088.699219,64074.214844,64070.785156</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>64102.656250,64093.441406,64106.695312,64093.003906,64077.519531,64059.281250,64072.867188,64094.015625,64058.808594,64086.523438,64085.226562,64071.808594,64057.546875,64076.863281,64131.949219,64117.457031,64084.289062,64051.062500,64011.835938,64046.750000,63999.605469,64046.445312,64000.718750,63936.601562</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>63813.300781,63727.792969,63624.152344,63577.578125,63516.300781,63454.656250,63398.023438,63344.929688,63322.007812,63272.312500,63262.300781,63229.082031,63206.054688,63157.367188,63141.937500,63075.472656,63047.667969,63036.964844,62925.886719,62857.066406,62834.816406,62809.007812,62767.105469,62746.281250</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>63947.093750,63894.613281,63806.015625,63799.890625,63747.312500,63693.867188,63683.375000,63658.718750,63644.019531,63621.406250,63601.273438,63611.171875,63589.675781,63552.875000,63556.835938,63520.660156,63488.488281,63485.164062,63437.097656,63375.167969,63358.414062,63314.832031,63288.992188,63276.699219</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1101,6 +1101,44 @@
       </c>
       <c r="F18" t="n">
         <v>64070.78515625</v>
+      </c>
+      <c r="G18" t="n">
+        <v>64470.26171875</v>
+      </c>
+      <c r="H18" t="n">
+        <v>399.4765625</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.6196291931351343</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.4787021743307638</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:23:48</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>24</v>
+      </c>
+      <c r="F19" t="n">
+        <v>64352.984375</v>
       </c>
     </row>
   </sheetData>
@@ -1114,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2187,6 +2225,24 @@
           <t>64135.910156,64129.187500,64113.386719,64120.546875,64117.585938,64106.773438,64106.675781,64103.539062,64116.531250,64112.730469,64135.343750,64149.617188,64161.222656,64152.988281,64165.757812,64147.714844,64158.492188,64154.648438,64142.031250,64109.324219,64099.246094,64088.699219,64074.214844,64070.785156</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>64113.968750,64275.218750,64199.308594,64109.980469,64063.031250,64097.269531,64004.269531,64018.289062,64277.039062,64361.238281,64426.839844,64328.250000,64606.019531,64695.351562,64741.109375,64794.628906,64778.601562,64671.679688,64573.531250,64597.859375,64582.300781,64520.621094,64516.679688,64470.261719</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>21.941406,146.031250,85.921875,10.566406,54.554688,9.503907,102.406250,85.250000,160.507812,248.507812,291.496094,178.632812,444.796875,542.363282,575.351563,646.914062,620.109375,517.031250,431.500000,488.535156,483.054687,431.921875,442.464843,399.476563</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.034223,0.227197,0.133836,0.016482,0.085158,0.014827,0.159999,0.133165,0.249713,0.386114,0.452445,0.277690,0.688476,0.838334,0.888696,0.998407,0.957275,0.799471,0.668230,0.756271,0.747968,0.669432,0.685815,0.619629</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0.4787021743307638</v>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>64102.656250,64093.441406,64106.695312,64093.003906,64077.519531,64059.281250,64072.867188,64094.015625,64058.808594,64086.523438,64085.226562,64071.808594,64057.546875,64076.863281,64131.949219,64117.457031,64084.289062,64051.062500,64011.835938,64046.750000,63999.605469,64046.445312,64000.718750,63936.601562</t>
@@ -2200,6 +2256,49 @@
       <c r="M18" t="inlineStr">
         <is>
           <t>63947.093750,63894.613281,63806.015625,63799.890625,63747.312500,63693.867188,63683.375000,63658.718750,63644.019531,63621.406250,63601.273438,63611.171875,63589.675781,63552.875000,63556.835938,63520.660156,63488.488281,63485.164062,63437.097656,63375.167969,63358.414062,63314.832031,63288.992188,63276.699219</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:23:48</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>24</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>64469.050781,64450.820312,64433.238281,64436.062500,64428.230469,64410.750000,64399.855469,64382.281250,64386.480469,64378.164062,64386.187500,64398.335938,64402.632812,64403.496094,64420.949219,64408.531250,64428.527344,64415.171875,64414.812500,64411.496094,64394.054688,64373.621094,64367.386719,64352.984375</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>64448.917969,64418.332031,64432.207031,64419.039062,64443.753906,64393.292969,64367.292969,64407.773438,64326.000000,64357.898438,64344.265625,64363.824219,64341.242188,64367.582031,64383.949219,64371.527344,64362.097656,64341.687500,64307.460938,64336.445312,64315.371094,64323.800781,64313.472656,64235.191406</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>64272.347656,64169.679688,64062.527344,63997.960938,63931.757812,63850.324219,63793.988281,63714.539062,63683.937500,63630.304688,63608.992188,63569.964844,63541.210938,63522.269531,63501.921875,63457.144531,63441.054688,63430.187500,63329.644531,63271.175781,63266.683594,63221.203125,63196.863281,63166.945312</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>64366.882812,64300.230469,64216.546875,64182.796875,64135.406250,64060.488281,64040.804688,63997.144531,63972.554688,63942.714844,63902.597656,63905.761719,63890.855469,63846.167969,63855.941406,63840.718750,63828.660156,63830.824219,63789.937500,63755.269531,63732.304688,63698.457031,63679.511719,63664.015625</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1139,6 +1139,44 @@
       </c>
       <c r="F19" t="n">
         <v>64352.984375</v>
+      </c>
+      <c r="G19" t="n">
+        <v>64319.359375</v>
+      </c>
+      <c r="H19" t="n">
+        <v>33.625</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.05227819481838551</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.2479726415651065</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:10:59</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>24</v>
+      </c>
+      <c r="F20" t="n">
+        <v>64287.73828125</v>
       </c>
     </row>
   </sheetData>
@@ -1152,7 +1190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2286,6 +2324,24 @@
           <t>64469.050781,64450.820312,64433.238281,64436.062500,64428.230469,64410.750000,64399.855469,64382.281250,64386.480469,64378.164062,64386.187500,64398.335938,64402.632812,64403.496094,64420.949219,64408.531250,64428.527344,64415.171875,64414.812500,64411.496094,64394.054688,64373.621094,64367.386719,64352.984375</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>64666.289062,64845.378906,64798.089844,64744.410156,64873.601562,64615.941406,64546.789062,64552.621094,64346.011719,64360.519531,64709.550781,64570.921875,64690.128906,64557.160156,64356.351562,64397.949219,64381.398438,64388.371094,64296.378906,64267.300781,64258.820312,64364.250000,64337.968750,64319.359375</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>197.238282,394.558594,364.851563,308.347656,445.371093,205.191406,146.933593,170.339844,40.468750,17.644531,323.363281,172.585937,287.496094,153.664062,64.597657,10.582031,47.128907,26.800781,118.433594,144.195313,135.234375,9.371094,29.417969,33.625000</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.305009,0.608461,0.563059,0.476254,0.686521,0.317555,0.227639,0.263878,0.062892,0.027415,0.499715,0.267281,0.444420,0.238028,0.100375,0.016432,0.073203,0.041624,0.184199,0.224368,0.210453,0.014559,0.045724,0.052278</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.2479726415651065</v>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>64448.917969,64418.332031,64432.207031,64419.039062,64443.753906,64393.292969,64367.292969,64407.773438,64326.000000,64357.898438,64344.265625,64363.824219,64341.242188,64367.582031,64383.949219,64371.527344,64362.097656,64341.687500,64307.460938,64336.445312,64315.371094,64323.800781,64313.472656,64235.191406</t>
@@ -2299,6 +2355,49 @@
       <c r="M19" t="inlineStr">
         <is>
           <t>64366.882812,64300.230469,64216.546875,64182.796875,64135.406250,64060.488281,64040.804688,63997.144531,63972.554688,63942.714844,63902.597656,63905.761719,63890.855469,63846.167969,63855.941406,63840.718750,63828.660156,63830.824219,63789.937500,63755.269531,63732.304688,63698.457031,63679.511719,63664.015625</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:10:59</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>24</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>64323.242188,64305.496094,64304.496094,64302.703125,64303.355469,64298.429688,64308.902344,64291.285156,64297.179688,64290.527344,64297.437500,64304.472656,64299.441406,64308.679688,64320.355469,64303.507812,64326.562500,64314.324219,64311.011719,64309.285156,64298.562500,64286.167969,64293.585938,64287.738281</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>64292.664062,64288.703125,64295.820312,64304.812500,64322.449219,64286.765625,64298.890625,64273.382812,64268.796875,64279.535156,64254.640625,64268.765625,64248.625000,64275.714844,64287.664062,64288.320312,64269.593750,64258.359375,64239.519531,64265.132812,64231.671875,64235.652344,64255.117188,64218.175781</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>64145.457031,64054.449219,63973.328125,63917.847656,63853.406250,63786.175781,63777.382812,63702.964844,63685.296875,63631.371094,63605.281250,63592.011719,63560.472656,63544.625000,63518.648438,63480.328125,63464.855469,63450.960938,63332.156250,63286.371094,63280.179688,63243.613281,63230.371094,63199.714844</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>64235.160156,64163.496094,64115.925781,64075.671875,64038.968750,63984.777344,63984.421875,63947.410156,63945.722656,63899.441406,63875.539062,63885.968750,63878.429688,63841.144531,63840.617188,63823.968750,63820.613281,63791.851562,63756.582031,63733.691406,63716.925781,63676.914062,63675.257812,63655.222656</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1177,6 +1177,44 @@
       </c>
       <c r="F20" t="n">
         <v>64287.73828125</v>
+      </c>
+      <c r="G20" t="n">
+        <v>64873.828125</v>
+      </c>
+      <c r="H20" t="n">
+        <v>586.08984375</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9034303365306454</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.7465755768400338</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-08 02:08:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>24</v>
+      </c>
+      <c r="F21" t="n">
+        <v>64760.7578125</v>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2385,6 +2423,24 @@
           <t>64323.242188,64305.496094,64304.496094,64302.703125,64303.355469,64298.429688,64308.902344,64291.285156,64297.179688,64290.527344,64297.437500,64304.472656,64299.441406,64308.679688,64320.355469,64303.507812,64326.562500,64314.324219,64311.011719,64309.285156,64298.562500,64286.167969,64293.585938,64287.738281</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>64191.671875,64276.050781,64254.398438,64264.191406,64552.898438,64794.058594,64849.109375,64975.628906,65250.558594,64960.890625,64906.859375,64852.910156,64758.070312,64713.890625,64667.820312,64914.789062,64935.718750,64960.921875,64960.921875,64878.218750,64878.218750,64868.859375,64873.828125,64873.828125</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>131.570313,29.445313,50.097657,38.511719,249.542968,495.628906,540.207031,684.343750,953.378906,670.363281,609.421875,548.437500,458.628907,405.210937,347.464843,611.281250,609.156250,646.597656,649.910156,568.933594,579.656250,582.691406,580.242187,586.089844</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.204965,0.045811,0.077968,0.059927,0.386571,0.764930,0.833022,1.053231,1.461105,1.031949,0.938918,0.845664,0.708219,0.626158,0.537307,0.941667,0.938091,0.995364,1.000463,0.876925,0.893453,0.898261,0.894416,0.903430</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0.7465755768400338</v>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>64292.664062,64288.703125,64295.820312,64304.812500,64322.449219,64286.765625,64298.890625,64273.382812,64268.796875,64279.535156,64254.640625,64268.765625,64248.625000,64275.714844,64287.664062,64288.320312,64269.593750,64258.359375,64239.519531,64265.132812,64231.671875,64235.652344,64255.117188,64218.175781</t>
@@ -2398,6 +2454,49 @@
       <c r="M20" t="inlineStr">
         <is>
           <t>64235.160156,64163.496094,64115.925781,64075.671875,64038.968750,63984.777344,63984.421875,63947.410156,63945.722656,63899.441406,63875.539062,63885.968750,63878.429688,63841.144531,63840.617188,63823.968750,63820.613281,63791.851562,63756.582031,63733.691406,63716.925781,63676.914062,63675.257812,63655.222656</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-08 02:08:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>24</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>64874.195312,64848.902344,64842.570312,64848.457031,64848.167969,64844.941406,64862.019531,64844.597656,64858.554688,64845.394531,64856.765625,64846.648438,64833.437500,64821.355469,64826.242188,64802.031250,64815.675781,64801.523438,64806.136719,64790.843750,64791.996094,64779.109375,64770.687500,64760.757812</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>64831.453125,64800.484375,64842.546875,64835.312500,64830.878906,64816.230469,64834.218750,64814.406250,64770.125000,64826.156250,64779.488281,64763.449219,64759.093750,64772.003906,64778.250000,64778.628906,64745.984375,64712.125000,64714.488281,64714.941406,64696.375000,64724.632812,64663.457031,64652.171875</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>64702.789062,64589.468750,64503.734375,64464.000000,64407.074219,64343.996094,64323.980469,64249.835938,64232.273438,64181.808594,64177.605469,64151.527344,64125.683594,64067.847656,64034.953125,63984.242188,63963.492188,63952.515625,63855.503906,63800.996094,63800.121094,63781.304688,63755.554688,63706.289062</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>64784.335938,64702.910156,64645.820312,64620.433594,64592.621094,64528.183594,64530.371094,64483.609375,64489.687500,64444.332031,64440.707031,64435.289062,64425.652344,64353.562500,64349.921875,64328.695312,64311.433594,64284.449219,64250.140625,64223.906250,64213.851562,64174.859375,64171.238281,64141.121094</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1215,6 +1215,44 @@
       </c>
       <c r="F21" t="n">
         <v>64760.7578125</v>
+      </c>
+      <c r="G21" t="n">
+        <v>64782.26171875</v>
+      </c>
+      <c r="H21" t="n">
+        <v>21.50390625</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.03319412703335133</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.2109715758051328</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-09 02:19:03</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>24</v>
+      </c>
+      <c r="F22" t="n">
+        <v>64679.80859375</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2484,6 +2522,24 @@
           <t>64874.195312,64848.902344,64842.570312,64848.457031,64848.167969,64844.941406,64862.019531,64844.597656,64858.554688,64845.394531,64856.765625,64846.648438,64833.437500,64821.355469,64826.242188,64802.031250,64815.675781,64801.523438,64806.136719,64790.843750,64791.996094,64779.109375,64770.687500,64760.757812</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>64989.859375,64974.140625,64961.000000,64968.730469,64928.800781,64957.718750,64955.289062,64966.679688,64922.839844,64960.890625,64973.609375,65082.738281,65029.660156,65039.988281,65073.140625,64992.851562,65025.421875,65032.179688,64968.031250,64892.511719,64905.281250,64922.078125,64806.000000,64782.261719</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>115.664063,125.238281,118.429688,120.273438,80.632812,112.777344,93.269532,122.082032,64.285156,115.496094,116.843750,236.089843,196.222656,218.632812,246.898437,190.820312,209.746094,230.656250,161.894531,101.667969,113.285156,142.968750,35.312500,21.503907</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.177972,0.192751,0.182309,0.185125,0.124187,0.173617,0.143590,0.187915,0.099018,0.177793,0.179833,0.362753,0.301743,0.336151,0.379417,0.293602,0.322560,0.354680,0.249191,0.156671,0.174539,0.220216,0.054490,0.033194</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0.2109715758051328</v>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>64831.453125,64800.484375,64842.546875,64835.312500,64830.878906,64816.230469,64834.218750,64814.406250,64770.125000,64826.156250,64779.488281,64763.449219,64759.093750,64772.003906,64778.250000,64778.628906,64745.984375,64712.125000,64714.488281,64714.941406,64696.375000,64724.632812,64663.457031,64652.171875</t>
@@ -2497,6 +2553,49 @@
       <c r="M21" t="inlineStr">
         <is>
           <t>64784.335938,64702.910156,64645.820312,64620.433594,64592.621094,64528.183594,64530.371094,64483.609375,64489.687500,64444.332031,64440.707031,64435.289062,64425.652344,64353.562500,64349.921875,64328.695312,64311.433594,64284.449219,64250.140625,64223.906250,64213.851562,64174.859375,64171.238281,64141.121094</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-09 02:19:03</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>24</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>64791.535156,64760.746094,64758.992188,64746.300781,64737.437500,64744.160156,64757.203125,64735.242188,64747.058594,64746.921875,64742.148438,64736.117188,64731.566406,64738.078125,64723.691406,64710.859375,64721.046875,64701.746094,64704.152344,64694.964844,64688.414062,64692.714844,64689.136719,64679.808594</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>64743.449219,64751.390625,64759.875000,64733.046875,64735.765625,64741.093750,64743.367188,64715.468750,64699.808594,64744.371094,64699.253906,64686.074219,64675.910156,64702.945312,64672.312500,64697.066406,64651.289062,64659.070312,64606.527344,64650.203125,64600.609375,64629.148438,64606.230469,64590.007812</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>64657.601562,64568.835938,64504.312500,64447.582031,64388.093750,64340.742188,64322.257812,64253.007812,64233.414062,64191.242188,64157.664062,64127.371094,64118.820312,64089.507812,64033.921875,63987.964844,63977.417969,63946.855469,63857.183594,63817.859375,63808.343750,63800.304688,63790.558594,63761.027344</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>64729.589844,64657.437500,64615.878906,64571.527344,64529.785156,64497.214844,64492.863281,64453.644531,64450.277344,64401.671875,64380.632812,64384.312500,64378.464844,64334.093750,64315.628906,64287.601562,64283.605469,64244.519531,64228.296875,64192.824219,64186.210938,64167.203125,64170.277344,64149.851562</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1253,6 +1253,44 @@
       </c>
       <c r="F22" t="n">
         <v>64679.80859375</v>
+      </c>
+      <c r="G22" t="n">
+        <v>64912.7109375</v>
+      </c>
+      <c r="H22" t="n">
+        <v>232.90234375</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.3587931244687126</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.3875192809993403</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:24:22</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>24</v>
+      </c>
+      <c r="F23" t="n">
+        <v>64824.765625</v>
       </c>
     </row>
   </sheetData>
@@ -1266,7 +1304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2583,6 +2621,24 @@
           <t>64791.535156,64760.746094,64758.992188,64746.300781,64737.437500,64744.160156,64757.203125,64735.242188,64747.058594,64746.921875,64742.148438,64736.117188,64731.566406,64738.078125,64723.691406,64710.859375,64721.046875,64701.746094,64704.152344,64694.964844,64688.414062,64692.714844,64689.136719,64679.808594</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>64734.968750,64735.429688,64754.320312,64792.898438,64770.871094,64770.070312,64832.308594,64905.460938,64899.968750,64906.589844,65178.679688,65214.289062,65174.988281,65181.968750,65142.000000,65147.121094,65130.738281,65095.570312,65143.699219,65023.078125,64848.691406,64916.980469,65146.851562,64912.710938</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>56.566406,25.316407,4.671875,46.597657,33.433594,25.910157,75.105469,170.218750,152.910156,159.667969,436.531250,478.171875,443.421875,443.890625,418.308594,436.261719,409.691406,393.824218,439.546875,328.113281,160.277344,224.265625,457.714843,232.902343</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.087382,0.039107,0.007215,0.071918,0.051618,0.040003,0.115846,0.262256,0.235609,0.245997,0.669745,0.733232,0.680356,0.681002,0.642149,0.669656,0.629029,0.604994,0.674734,0.504611,0.247156,0.345465,0.702589,0.358793</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0.3875192809993403</v>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>64743.449219,64751.390625,64759.875000,64733.046875,64735.765625,64741.093750,64743.367188,64715.468750,64699.808594,64744.371094,64699.253906,64686.074219,64675.910156,64702.945312,64672.312500,64697.066406,64651.289062,64659.070312,64606.527344,64650.203125,64600.609375,64629.148438,64606.230469,64590.007812</t>
@@ -2596,6 +2652,49 @@
       <c r="M22" t="inlineStr">
         <is>
           <t>64729.589844,64657.437500,64615.878906,64571.527344,64529.785156,64497.214844,64492.863281,64453.644531,64450.277344,64401.671875,64380.632812,64384.312500,64378.464844,64334.093750,64315.628906,64287.601562,64283.605469,64244.519531,64228.296875,64192.824219,64186.210938,64167.203125,64170.277344,64149.851562</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:24:22</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>24</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>64908.859375,64879.656250,64877.820312,64878.273438,64871.121094,64869.355469,64883.863281,64876.488281,64901.042969,64902.546875,64905.160156,64903.890625,64910.488281,64897.835938,64899.683594,64875.757812,64894.679688,64878.320312,64864.820312,64858.214844,64848.839844,64851.007812,64837.183594,64824.765625</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>64863.019531,64857.773438,64868.750000,64879.226562,64884.738281,64863.050781,64840.945312,64871.093750,64844.292969,64907.230469,64875.097656,64846.296875,64860.273438,64874.468750,64859.625000,64850.585938,64837.703125,64792.875000,64745.101562,64798.980469,64758.105469,64782.261719,64757.167969,64708.843750</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>64752.582031,64654.070312,64593.886719,64561.683594,64487.972656,64446.843750,64443.046875,64380.570312,64375.972656,64338.367188,64326.511719,64296.296875,64276.382812,64239.500000,64211.273438,64163.437500,64160.125000,64130.675781,64013.792969,63960.585938,63976.351562,63950.203125,63937.132812,63906.226562</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>64826.300781,64757.968750,64708.132812,64685.750000,64647.953125,64604.257812,64605.859375,64585.554688,64592.046875,64547.175781,64531.640625,64534.929688,64542.148438,64480.898438,64470.593750,64441.804688,64459.960938,64416.117188,64371.605469,64337.542969,64328.328125,64310.867188,64300.562500,64262.656250</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1291,6 +1291,44 @@
       </c>
       <c r="F23" t="n">
         <v>64824.765625</v>
+      </c>
+      <c r="G23" t="n">
+        <v>63979.55859375</v>
+      </c>
+      <c r="H23" t="n">
+        <v>845.20703125</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.321057928231105</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.8571340628425328</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:14:57</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>24</v>
+      </c>
+      <c r="F24" t="n">
+        <v>64002.8671875</v>
       </c>
     </row>
   </sheetData>
@@ -1304,7 +1342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2682,6 +2720,24 @@
           <t>64908.859375,64879.656250,64877.820312,64878.273438,64871.121094,64869.355469,64883.863281,64876.488281,64901.042969,64902.546875,64905.160156,64903.890625,64910.488281,64897.835938,64899.683594,64875.757812,64894.679688,64878.320312,64864.820312,64858.214844,64848.839844,64851.007812,64837.183594,64824.765625</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>64921.089844,64950.769531,65085.601562,65248.078125,65149.839844,65190.351562,64907.648438,64956.261719,65069.460938,64817.101562,64494.730469,64562.761719,64235.851562,63833.921875,63884.980469,63815.898438,63975.878906,64096.859375,63929.390625,63929.390625,63972.089844,63972.089844,63993.250000,63979.558594</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>12.230469,71.113281,207.781250,369.804687,278.718750,320.996093,23.785157,79.773438,168.417968,85.445312,410.429687,341.128906,674.636718,1063.914063,1014.703125,1059.859375,918.800782,781.460937,935.429687,928.824219,876.750000,878.917968,843.933594,845.207031</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.018839,0.109488,0.319243,0.566767,0.427812,0.492398,0.036645,0.122811,0.258828,0.131825,0.636377,0.528368,1.050250,1.666691,1.588328,1.660808,1.436168,1.219188,1.463223,1.452891,1.370520,1.373908,1.318785,1.321058</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0.8571340628425328</v>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>64863.019531,64857.773438,64868.750000,64879.226562,64884.738281,64863.050781,64840.945312,64871.093750,64844.292969,64907.230469,64875.097656,64846.296875,64860.273438,64874.468750,64859.625000,64850.585938,64837.703125,64792.875000,64745.101562,64798.980469,64758.105469,64782.261719,64757.167969,64708.843750</t>
@@ -2695,6 +2751,49 @@
       <c r="M23" t="inlineStr">
         <is>
           <t>64826.300781,64757.968750,64708.132812,64685.750000,64647.953125,64604.257812,64605.859375,64585.554688,64592.046875,64547.175781,64531.640625,64534.929688,64542.148438,64480.898438,64470.593750,64441.804688,64459.960938,64416.117188,64371.605469,64337.542969,64328.328125,64310.867188,64300.562500,64262.656250</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:14:57</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>24</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>63980.253906,63971.761719,63964.593750,63954.925781,63976.035156,63984.792969,63993.402344,63965.675781,63974.078125,63992.296875,63994.820312,63981.453125,63993.261719,63997.941406,63998.855469,63975.460938,63988.734375,63991.406250,63979.613281,64001.011719,63995.160156,63989.253906,63996.644531,64002.867188</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>63973.675781,63988.539062,63946.218750,63962.269531,63991.039062,64014.230469,63976.480469,63928.558594,63956.929688,63989.394531,63964.882812,63933.804688,63963.238281,64007.773438,63980.171875,63941.199219,63940.746094,63916.781250,63923.050781,63955.054688,63923.574219,63912.476562,63958.460938,63944.007812</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>63727.078125,63637.238281,63563.371094,63491.800781,63437.175781,63413.527344,63390.621094,63289.382812,63292.058594,63249.117188,63239.234375,63202.699219,63184.976562,63146.320312,63146.128906,63104.035156,63073.804688,63057.484375,62929.039062,62923.343750,62925.566406,62908.449219,62899.640625,62880.031250</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>63830.226562,63774.566406,63706.175781,63672.941406,63645.820312,63631.144531,63620.945312,63564.230469,63572.171875,63542.812500,63516.585938,63517.332031,63499.179688,63473.968750,63472.289062,63450.007812,63437.281250,63401.972656,63373.324219,63374.132812,63354.968750,63339.125000,63349.742188,63332.421875</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1329,6 +1329,44 @@
       </c>
       <c r="F24" t="n">
         <v>64002.8671875</v>
+      </c>
+      <c r="G24" t="n">
+        <v>63788.53125</v>
+      </c>
+      <c r="H24" t="n">
+        <v>214.3359375</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.3360101468083261</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.4445336917947317</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-12 02:32:42</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>24</v>
+      </c>
+      <c r="F25" t="n">
+        <v>63825.72265625</v>
       </c>
     </row>
   </sheetData>
@@ -1342,7 +1380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2781,6 +2819,24 @@
           <t>63980.253906,63971.761719,63964.593750,63954.925781,63976.035156,63984.792969,63993.402344,63965.675781,63974.078125,63992.296875,63994.820312,63981.453125,63993.261719,63997.941406,63998.855469,63975.460938,63988.734375,63991.406250,63979.613281,64001.011719,63995.160156,63989.253906,63996.644531,64002.867188</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>64074.718750,63960.210938,63926.890625,63897.941406,63999.171875,64073.851562,64242.449219,64171.171875,64327.171875,64266.519531,64139.988281,63713.960938,63541.371094,63440.589844,63537.121094,63305.789062,63477.968750,63682.160156,63615.578125,63604.660156,63482.839844,63685.039062,63760.898438,63788.531250</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>94.464844,11.550782,37.703125,56.984375,23.136719,89.058593,249.046875,205.496094,353.093750,274.222656,145.167969,267.492188,451.890625,557.351562,461.734375,669.671875,510.765625,309.246094,364.035156,396.351563,512.320312,304.214843,235.746093,214.335938</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.147429,0.018059,0.058979,0.089180,0.036152,0.138994,0.387667,0.320231,0.548903,0.426696,0.226330,0.419833,0.711175,0.878541,0.726716,1.057837,0.804634,0.485609,0.572242,0.623149,0.807022,0.477687,0.369735,0.336010</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.4445336917947317</v>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>63973.675781,63988.539062,63946.218750,63962.269531,63991.039062,64014.230469,63976.480469,63928.558594,63956.929688,63989.394531,63964.882812,63933.804688,63963.238281,64007.773438,63980.171875,63941.199219,63940.746094,63916.781250,63923.050781,63955.054688,63923.574219,63912.476562,63958.460938,63944.007812</t>
@@ -2794,6 +2850,49 @@
       <c r="M24" t="inlineStr">
         <is>
           <t>63830.226562,63774.566406,63706.175781,63672.941406,63645.820312,63631.144531,63620.945312,63564.230469,63572.171875,63542.812500,63516.585938,63517.332031,63499.179688,63473.968750,63472.289062,63450.007812,63437.281250,63401.972656,63373.324219,63374.132812,63354.968750,63339.125000,63349.742188,63332.421875</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-12 02:32:42</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>24</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>63768.378906,63788.281250,63789.023438,63795.281250,63803.109375,63814.152344,63807.644531,63802.996094,63800.730469,63807.394531,63788.625000,63790.660156,63785.832031,63791.003906,63791.324219,63786.800781,63794.570312,63791.433594,63787.125000,63807.699219,63818.488281,63800.792969,63807.234375,63825.722656</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>63757.804688,63821.609375,63770.136719,63811.019531,63821.042969,63805.820312,63801.984375,63759.765625,63800.812500,63801.648438,63768.742188,63759.230469,63763.894531,63796.839844,63784.785156,63760.765625,63733.472656,63787.765625,63761.718750,63761.367188,63765.148438,63744.500000,63798.585938,63756.867188</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>63525.687500,63473.324219,63389.402344,63336.882812,63285.183594,63267.367188,63236.710938,63190.394531,63155.808594,63095.703125,63072.171875,63038.339844,62999.359375,62967.800781,62963.511719,62936.546875,62915.203125,62886.937500,62791.125000,62772.214844,62773.980469,62741.742188,62739.378906,62733.179688</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>63631.593750,63602.230469,63535.351562,63509.957031,63485.207031,63475.531250,63459.753906,63431.683594,63419.734375,63374.171875,63322.046875,63338.636719,63309.527344,63283.203125,63291.066406,63284.355469,63251.460938,63226.726562,63200.484375,63200.390625,63194.472656,63164.164062,63177.726562,63188.617188</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1367,6 +1367,44 @@
       </c>
       <c r="F25" t="n">
         <v>63825.72265625</v>
+      </c>
+      <c r="G25" t="n">
+        <v>63345.58984375</v>
+      </c>
+      <c r="H25" t="n">
+        <v>480.1328125</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.7579577578870274</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.4466582019727329</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-13 02:34:10</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>24</v>
+      </c>
+      <c r="F26" t="n">
+        <v>63392.21484375</v>
       </c>
     </row>
   </sheetData>
@@ -1380,7 +1418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2880,6 +2918,24 @@
           <t>63768.378906,63788.281250,63789.023438,63795.281250,63803.109375,63814.152344,63807.644531,63802.996094,63800.730469,63807.394531,63788.625000,63790.660156,63785.832031,63791.003906,63791.324219,63786.800781,63794.570312,63791.433594,63787.125000,63807.699219,63818.488281,63800.792969,63807.234375,63825.722656</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>63762.019531,63713.621094,63786.769531,63650.691406,63767.031250,63730.500000,64052.339844,64079.988281,64175.898438,64066.441406,63780.558594,63296.710938,63368.640625,63427.449219,63398.820312,63309.609375,63345.718750,63535.468750,63403.191406,63361.570312,63413.058594,63489.839844,63385.511719,63345.589844</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>6.359375,74.660156,2.253907,144.589844,36.078125,83.652344,244.695313,276.992187,375.167968,259.046875,8.066406,493.949218,417.191406,363.554687,392.503907,477.191406,448.851562,255.964844,383.933594,446.128907,405.429687,310.953125,421.722656,480.132812</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.009974,0.117181,0.003534,0.227161,0.056578,0.131260,0.382024,0.432260,0.584593,0.404341,0.012647,0.780371,0.658356,0.573182,0.619103,0.753742,0.708574,0.402869,0.605543,0.704100,0.639347,0.489768,0.665330,0.757958</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0.4466582019727329</v>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>63757.804688,63821.609375,63770.136719,63811.019531,63821.042969,63805.820312,63801.984375,63759.765625,63800.812500,63801.648438,63768.742188,63759.230469,63763.894531,63796.839844,63784.785156,63760.765625,63733.472656,63787.765625,63761.718750,63761.367188,63765.148438,63744.500000,63798.585938,63756.867188</t>
@@ -2893,6 +2949,49 @@
       <c r="M25" t="inlineStr">
         <is>
           <t>63631.593750,63602.230469,63535.351562,63509.957031,63485.207031,63475.531250,63459.753906,63431.683594,63419.734375,63374.171875,63322.046875,63338.636719,63309.527344,63283.203125,63291.066406,63284.355469,63251.460938,63226.726562,63200.484375,63200.390625,63194.472656,63164.164062,63177.726562,63188.617188</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-13 02:34:10</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>24</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>63364.492188,63358.984375,63363.730469,63369.207031,63370.757812,63386.468750,63392.785156,63397.378906,63396.367188,63411.878906,63388.093750,63384.542969,63371.394531,63368.878906,63363.542969,63363.777344,63353.765625,63345.878906,63349.433594,63342.410156,63354.039062,63361.273438,63369.574219,63392.214844</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>63369.312500,63383.996094,63361.968750,63389.445312,63410.195312,63387.628906,63407.796875,63367.808594,63424.277344,63402.687500,63384.335938,63397.871094,63383.128906,63372.257812,63380.121094,63358.011719,63337.218750,63374.039062,63359.738281,63327.816406,63327.785156,63334.300781,63364.437500,63348.796875</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>63112.550781,63045.796875,62980.050781,62941.808594,62885.445312,62883.437500,62856.652344,62812.210938,62765.308594,62729.734375,62687.839844,62661.171875,62620.078125,62583.980469,62567.988281,62540.242188,62509.312500,62474.734375,62422.132812,62393.933594,62379.746094,62388.093750,62382.132812,62383.710938</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>63217.371094,63170.906250,63121.386719,63105.113281,63068.398438,63072.207031,63058.535156,63032.468750,63013.171875,62989.109375,62936.316406,62940.218750,62914.671875,62887.414062,62887.652344,62879.605469,62842.363281,62815.414062,62814.593750,62786.015625,62786.347656,62781.714844,62797.085938,62807.152344</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1405,6 +1405,44 @@
       </c>
       <c r="F26" t="n">
         <v>63392.21484375</v>
+      </c>
+      <c r="G26" t="n">
+        <v>63500.75</v>
+      </c>
+      <c r="H26" t="n">
+        <v>108.53515625</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.1709194871714114</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.3349750060360263</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-14 02:32:58</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>24</v>
+      </c>
+      <c r="F27" t="n">
+        <v>63652.515625</v>
       </c>
     </row>
   </sheetData>
@@ -1418,7 +1456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2979,6 +3017,24 @@
           <t>63364.492188,63358.984375,63363.730469,63369.207031,63370.757812,63386.468750,63392.785156,63397.378906,63396.367188,63411.878906,63388.093750,63384.542969,63371.394531,63368.878906,63363.542969,63363.777344,63353.765625,63345.878906,63349.433594,63342.410156,63354.039062,63361.273438,63369.574219,63392.214844</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>63580.261719,63627.449219,63806.000000,63875.761719,63803.980469,63708.019531,63718.121094,63582.410156,63414.898438,63621.640625,63653.039062,63801.511719,63358.121094,63092.441406,63070.019531,63235.828125,63335.078125,63349.179688,63409.171875,63558.511719,63480.941406,63480.941406,63511.089844,63500.750000</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>215.769531,268.464844,442.269531,506.554688,433.222657,321.550781,325.335938,185.031250,18.531250,209.761719,264.945312,416.968750,13.273437,276.437500,293.523438,127.949219,18.687500,3.300782,59.738281,216.101563,126.902344,119.667968,141.515625,108.535156</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0.339366,0.421932,0.693147,0.793031,0.678990,0.504726,0.510586,0.291010,0.029222,0.329702,0.416234,0.653541,0.020950,0.438147,0.465393,0.202337,0.029506,0.005210,0.094211,0.340004,0.199906,0.188510,0.222820,0.170919</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0.3349750060360263</v>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>63369.312500,63383.996094,63361.968750,63389.445312,63410.195312,63387.628906,63407.796875,63367.808594,63424.277344,63402.687500,63384.335938,63397.871094,63383.128906,63372.257812,63380.121094,63358.011719,63337.218750,63374.039062,63359.738281,63327.816406,63327.785156,63334.300781,63364.437500,63348.796875</t>
@@ -2992,6 +3048,49 @@
       <c r="M26" t="inlineStr">
         <is>
           <t>63217.371094,63170.906250,63121.386719,63105.113281,63068.398438,63072.207031,63058.535156,63032.468750,63013.171875,62989.109375,62936.316406,62940.218750,62914.671875,62887.414062,62887.652344,62879.605469,62842.363281,62815.414062,62814.593750,62786.015625,62786.347656,62781.714844,62797.085938,62807.152344</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-14 02:32:58</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>24</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>63507.953125,63513.570312,63513.164062,63532.667969,63526.832031,63542.546875,63564.753906,63576.167969,63592.851562,63591.507812,63591.531250,63579.792969,63575.503906,63570.570312,63561.414062,63558.156250,63556.898438,63575.773438,63598.589844,63604.542969,63618.410156,63636.824219,63649.058594,63652.515625</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>63511.582031,63524.328125,63527.218750,63531.738281,63558.359375,63558.785156,63589.910156,63576.593750,63607.250000,63595.500000,63607.359375,63611.828125,63603.550781,63590.738281,63574.058594,63582.925781,63583.250000,63627.863281,63633.808594,63636.449219,63644.828125,63643.804688,63685.179688,63666.152344</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>63282.738281,63224.097656,63161.882812,63145.960938,63090.031250,63078.652344,63074.027344,63044.394531,63023.453125,62989.714844,62977.839844,62953.636719,62933.125000,62911.617188,62889.347656,62866.535156,62852.101562,62857.597656,62841.750000,62842.652344,62842.226562,62854.277344,62867.308594,62861.687500</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>63375.472656,63337.433594,63289.074219,63289.730469,63250.871094,63246.703125,63249.894531,63226.761719,63237.152344,63204.714844,63193.621094,63186.585938,63169.683594,63143.875000,63139.976562,63122.656250,63104.902344,63107.105469,63127.562500,63133.257812,63132.335938,63145.859375,63166.605469,63164.859375</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,6 +1443,44 @@
       </c>
       <c r="F27" t="n">
         <v>63652.515625</v>
+      </c>
+      <c r="G27" t="n">
+        <v>62957.44140625</v>
+      </c>
+      <c r="H27" t="n">
+        <v>695.07421875</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.104038225227173</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.074894587041367</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-15 01:42:56</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>24</v>
+      </c>
+      <c r="F28" t="n">
+        <v>63118.1328125</v>
       </c>
     </row>
   </sheetData>
@@ -1456,7 +1494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3078,6 +3116,24 @@
           <t>63507.953125,63513.570312,63513.164062,63532.667969,63526.832031,63542.546875,63564.753906,63576.167969,63592.851562,63591.507812,63591.531250,63579.792969,63575.503906,63570.570312,63561.414062,63558.156250,63556.898438,63575.773438,63598.589844,63604.542969,63618.410156,63636.824219,63649.058594,63652.515625</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>63246.691406,63307.140625,63314.500000,62909.761719,62848.679688,62870.480469,62723.910156,62746.128906,62793.300781,62661.851562,62584.320312,62547.980469,62913.050781,63071.089844,62951.691406,62855.910156,62895.820312,62835.148438,62843.210938,62843.210938,62950.718750,62950.718750,62957.441406,62957.441406</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>261.261719,206.429687,198.664062,622.906250,678.152343,672.066406,840.843750,830.039063,799.550781,929.656250,1007.210938,1031.812500,662.453125,499.480468,609.722656,702.246094,661.078125,740.625000,755.378907,761.332032,667.691406,686.105469,691.617188,695.074219</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.413084,0.326076,0.313773,0.990158,1.079024,1.068970,1.340547,1.322853,1.273306,1.483608,1.609366,1.649634,1.052966,0.791933,0.968556,1.117232,1.051068,1.178679,1.202006,1.211479,1.060657,1.089909,1.098547,1.104038</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>1.074894587041367</v>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>63511.582031,63524.328125,63527.218750,63531.738281,63558.359375,63558.785156,63589.910156,63576.593750,63607.250000,63595.500000,63607.359375,63611.828125,63603.550781,63590.738281,63574.058594,63582.925781,63583.250000,63627.863281,63633.808594,63636.449219,63644.828125,63643.804688,63685.179688,63666.152344</t>
@@ -3091,6 +3147,49 @@
       <c r="M27" t="inlineStr">
         <is>
           <t>63375.472656,63337.433594,63289.074219,63289.730469,63250.871094,63246.703125,63249.894531,63226.761719,63237.152344,63204.714844,63193.621094,63186.585938,63169.683594,63143.875000,63139.976562,63122.656250,63104.902344,63107.105469,63127.562500,63133.257812,63132.335938,63145.859375,63166.605469,63164.859375</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-15 01:42:56</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>24</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>62963.593750,62979.617188,62977.992188,62979.531250,62981.980469,62994.519531,62994.082031,62987.406250,62987.468750,63000.531250,63016.390625,63019.312500,63032.070312,63046.601562,63050.453125,63049.644531,63052.042969,63075.441406,63084.382812,63095.933594,63093.214844,63103.136719,63109.367188,63118.132812</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>62979.890625,62995.621094,62998.378906,62990.464844,63004.269531,63034.000000,63028.476562,62992.527344,63023.832031,63025.222656,63060.843750,63096.445312,63090.410156,63091.546875,63100.753906,63085.710938,63092.523438,63155.171875,63152.246094,63150.480469,63146.460938,63127.507812,63175.140625,63197.265625</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>62747.230469,62712.574219,62661.789062,62638.468750,62600.468750,62590.144531,62563.921875,62511.707031,62485.425781,62464.304688,62461.300781,62455.898438,62447.800781,62430.601562,62427.042969,62404.734375,62391.425781,62397.894531,62355.230469,62368.988281,62355.988281,62363.609375,62368.226562,62352.769531</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>62829.910156,62814.789062,62765.722656,62758.691406,62730.046875,62736.496094,62723.347656,62680.843750,62674.472656,62661.292969,62648.777344,62670.453125,62652.515625,62645.882812,62661.585938,62645.281250,62620.507812,62624.804688,62630.035156,62646.171875,62636.296875,62628.171875,62646.945312,62646.796875</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1481,6 +1481,44 @@
       </c>
       <c r="F28" t="n">
         <v>63118.1328125</v>
+      </c>
+      <c r="G28" t="n">
+        <v>63000.58984375</v>
+      </c>
+      <c r="H28" t="n">
+        <v>117.54296875</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.1865743940517422</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.08096302560052822</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-16 01:49:58</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>24</v>
+      </c>
+      <c r="F29" t="n">
+        <v>63086.1484375</v>
       </c>
     </row>
   </sheetData>
@@ -1494,7 +1532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3177,6 +3215,24 @@
           <t>62963.593750,62979.617188,62977.992188,62979.531250,62981.980469,62994.519531,62994.082031,62987.406250,62987.468750,63000.531250,63016.390625,63019.312500,63032.070312,63046.601562,63050.453125,63049.644531,63052.042969,63075.441406,63084.382812,63095.933594,63093.214844,63103.136719,63109.367188,63118.132812</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>63071.390625,62988.390625,63052.019531,63016.101562,63045.539062,63005.660156,62869.070312,62957.640625,62976.031250,62949.218750,62985.929688,62985.921875,62966.421875,63022.949219,63024.058594,63000.339844,62989.121094,63051.378906,63036.500000,63085.921875,63061.679688,63017.609375,63012.929688,63000.589844</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>107.796875,8.773437,74.027343,36.570312,63.558593,11.140625,125.011718,29.765625,11.437500,51.312500,30.460938,33.390625,65.648437,23.652343,26.394531,49.304687,62.921875,24.062500,47.882812,10.011719,31.535157,85.527344,96.437500,117.542968</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.170912,0.013929,0.117407,0.058033,0.100814,0.017682,0.198845,0.047279,0.018162,0.081514,0.048361,0.053013,0.104259,0.037530,0.041880,0.078261,0.099893,0.038163,0.075960,0.015870,0.050007,0.135720,0.153044,0.186574</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0.08096302560052822</v>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>62979.890625,62995.621094,62998.378906,62990.464844,63004.269531,63034.000000,63028.476562,62992.527344,63023.832031,63025.222656,63060.843750,63096.445312,63090.410156,63091.546875,63100.753906,63085.710938,63092.523438,63155.171875,63152.246094,63150.480469,63146.460938,63127.507812,63175.140625,63197.265625</t>
@@ -3190,6 +3246,49 @@
       <c r="M28" t="inlineStr">
         <is>
           <t>62829.910156,62814.789062,62765.722656,62758.691406,62730.046875,62736.496094,62723.347656,62680.843750,62674.472656,62661.292969,62648.777344,62670.453125,62652.515625,62645.882812,62661.585938,62645.281250,62620.507812,62624.804688,62630.035156,62646.171875,62636.296875,62628.171875,62646.945312,62646.796875</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-16 01:49:58</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>24</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>63001.593750,63007.441406,63005.007812,63005.644531,63009.433594,63004.507812,63000.085938,63007.636719,63009.101562,63017.257812,63016.140625,63015.230469,63015.601562,63032.476562,63023.300781,63041.480469,63042.421875,63049.839844,63061.988281,63076.546875,63071.671875,63078.414062,63086.304688,63086.148438</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>63017.226562,63029.035156,63009.574219,63001.773438,63037.773438,63027.222656,63034.281250,63028.175781,63051.324219,63054.117188,63038.289062,63071.824219,63104.230469,63080.375000,63092.351562,63120.515625,63110.878906,63149.285156,63130.554688,63135.992188,63144.289062,63142.203125,63161.324219,63160.003906</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>62884.226562,62860.312500,62822.855469,62811.554688,62784.500000,62759.242188,62746.222656,62729.699219,62708.636719,62687.644531,62668.550781,62656.652344,62642.929688,62636.042969,62614.375000,62622.652344,62620.082031,62611.671875,62577.726562,62581.398438,62569.640625,62574.035156,62569.332031,62554.632812</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>62929.421875,62917.148438,62885.019531,62873.929688,62855.179688,62847.933594,62842.007812,62831.546875,62835.054688,62814.710938,62788.601562,62800.371094,62770.476562,62777.574219,62773.445312,62789.808594,62768.828125,62765.847656,62771.363281,62778.136719,62761.968750,62754.632812,62763.968750,62757.273438</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1519,6 +1519,44 @@
       </c>
       <c r="F29" t="n">
         <v>63086.1484375</v>
+      </c>
+      <c r="G29" t="n">
+        <v>63120.26953125</v>
+      </c>
+      <c r="H29" t="n">
+        <v>34.12109375</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.05405726877181204</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.120136302032002</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-17 01:47:30</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>24</v>
+      </c>
+      <c r="F30" t="n">
+        <v>63176.9609375</v>
       </c>
     </row>
   </sheetData>
@@ -1532,7 +1570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3276,6 +3314,24 @@
           <t>63001.593750,63007.441406,63005.007812,63005.644531,63009.433594,63004.507812,63000.085938,63007.636719,63009.101562,63017.257812,63016.140625,63015.230469,63015.601562,63032.476562,63023.300781,63041.480469,63042.421875,63049.839844,63061.988281,63076.546875,63071.671875,63078.414062,63086.304688,63086.148438</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>63054.449219,63059.429688,63016.929688,62997.828125,62993.718750,62991.230469,63001.910156,62917.519531,62940.191406,62945.320312,62948.000000,62993.628906,63034.539062,63070.031250,63186.921875,63087.421875,63074.289062,63040.171875,63000.730469,62862.800781,62843.449219,62830.578125,62840.550781,63120.269531</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>52.855469,51.988282,11.921875,7.816406,15.714844,13.277343,1.824218,90.117188,68.910156,71.937500,68.140625,21.601563,18.937500,37.554688,163.621094,45.941406,31.867188,9.667969,61.257812,213.746094,228.222656,247.835937,245.753907,34.121093</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0.083825,0.082443,0.018919,0.012407,0.024947,0.021078,0.002895,0.143231,0.109485,0.114286,0.108249,0.034292,0.030043,0.059544,0.258948,0.072822,0.050523,0.015336,0.097233,0.340020,0.363161,0.394451,0.391075,0.054057</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0.120136302032002</v>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>63017.226562,63029.035156,63009.574219,63001.773438,63037.773438,63027.222656,63034.281250,63028.175781,63051.324219,63054.117188,63038.289062,63071.824219,63104.230469,63080.375000,63092.351562,63120.515625,63110.878906,63149.285156,63130.554688,63135.992188,63144.289062,63142.203125,63161.324219,63160.003906</t>
@@ -3289,6 +3345,49 @@
       <c r="M29" t="inlineStr">
         <is>
           <t>62929.421875,62917.148438,62885.019531,62873.929688,62855.179688,62847.933594,62842.007812,62831.546875,62835.054688,62814.710938,62788.601562,62800.371094,62770.476562,62777.574219,62773.445312,62789.808594,62768.828125,62765.847656,62771.363281,62778.136719,62761.968750,62754.632812,62763.968750,62757.273438</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-17 01:47:30</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>24</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>63144.585938,63161.832031,63157.488281,63146.199219,63149.535156,63154.886719,63148.031250,63152.703125,63144.085938,63150.640625,63147.816406,63151.648438,63155.031250,63161.421875,63156.191406,63167.453125,63158.417969,63156.343750,63158.996094,63166.421875,63161.460938,63158.429688,63164.929688,63176.960938</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>63173.937500,63167.089844,63187.339844,63156.253906,63191.632812,63170.558594,63195.246094,63174.054688,63180.996094,63186.636719,63190.808594,63208.632812,63251.332031,63234.820312,63218.281250,63243.980469,63235.722656,63254.253906,63228.242188,63236.078125,63213.558594,63226.531250,63242.382812,63253.066406</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>62991.128906,62970.386719,62919.089844,62885.277344,62858.429688,62841.371094,62814.925781,62794.144531,62769.117188,62761.601562,62745.843750,62745.796875,62743.312500,62730.750000,62712.925781,62716.031250,62689.613281,62676.042969,62636.800781,62628.414062,62621.984375,62615.531250,62610.871094,62615.968750</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>63051.218750,63047.753906,63008.425781,62980.648438,62959.984375,62955.769531,62936.363281,62918.882812,62908.875000,62903.550781,62879.238281,62900.394531,62887.011719,62880.113281,62879.679688,62886.449219,62848.488281,62843.238281,62833.593750,62839.324219,62819.378906,62814.136719,62818.000000,62831.234375</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1557,6 +1557,44 @@
       </c>
       <c r="F30" t="n">
         <v>63176.9609375</v>
+      </c>
+      <c r="G30" t="n">
+        <v>64211.3984375</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1034.4375</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.610987340521585</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.079353432829409</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-08-18 01:42:50</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>24</v>
+      </c>
+      <c r="F31" t="n">
+        <v>64185.55078125</v>
       </c>
     </row>
   </sheetData>
@@ -1570,7 +1608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3375,6 +3413,24 @@
           <t>63144.585938,63161.832031,63157.488281,63146.199219,63149.535156,63154.886719,63148.031250,63152.703125,63144.085938,63150.640625,63147.816406,63151.648438,63155.031250,63161.421875,63156.191406,63167.453125,63158.417969,63156.343750,63158.996094,63166.421875,63161.460938,63158.429688,63164.929688,63176.960938</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>63335.738281,63367.808594,63479.980469,63456.601562,63603.339844,63461.460938,63307.859375,63246.199219,63627.281250,63559.890625,63478.250000,63601.390625,63830.781250,64139.699219,64060.351562,64276.808594,64380.578125,64266.441406,64341.769531,64337.371094,64337.371094,64322.289062,64322.289062,64211.398438</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>191.152343,205.976563,322.492188,310.402343,453.804688,306.574218,159.828125,93.496094,483.195312,409.250000,330.433594,449.742187,675.750000,978.277344,904.160157,1109.355469,1222.160156,1110.097656,1182.773437,1170.949219,1175.910156,1163.859375,1157.359375,1034.437500</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0.301808,0.325049,0.508022,0.489157,0.713492,0.483087,0.252462,0.147829,0.759415,0.643881,0.520546,0.707126,1.058659,1.525229,1.411419,1.725903,1.898337,1.727336,1.838267,1.820014,1.827725,1.809418,1.799313,1.610987</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>1.079353432829409</v>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>63173.937500,63167.089844,63187.339844,63156.253906,63191.632812,63170.558594,63195.246094,63174.054688,63180.996094,63186.636719,63190.808594,63208.632812,63251.332031,63234.820312,63218.281250,63243.980469,63235.722656,63254.253906,63228.242188,63236.078125,63213.558594,63226.531250,63242.382812,63253.066406</t>
@@ -3388,6 +3444,49 @@
       <c r="M30" t="inlineStr">
         <is>
           <t>63051.218750,63047.753906,63008.425781,62980.648438,62959.984375,62955.769531,62936.363281,62918.882812,62908.875000,62903.550781,62879.238281,62900.394531,62887.011719,62880.113281,62879.679688,62886.449219,62848.488281,62843.238281,62833.593750,62839.324219,62819.378906,62814.136719,62818.000000,62831.234375</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-08-18 01:42:50</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>24</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>64226.265625,64234.246094,64218.726562,64218.378906,64219.195312,64227.558594,64227.531250,64241.503906,64238.828125,64224.699219,64225.328125,64219.058594,64218.855469,64231.515625,64226.882812,64224.027344,64224.710938,64230.175781,64236.167969,64237.417969,64215.230469,64207.390625,64203.789062,64185.550781</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>64211.960938,64209.046875,64233.769531,64201.011719,64217.722656,64189.734375,64202.632812,64229.738281,64212.476562,64196.421875,64197.144531,64180.125000,64187.726562,64212.101562,64195.203125,64228.734375,64193.648438,64200.898438,64182.343750,64236.664062,64182.781250,64227.093750,64167.261719,64165.257812</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>63992.496094,63943.722656,63859.316406,63807.109375,63766.222656,63732.203125,63690.324219,63677.378906,63631.875000,63585.859375,63557.570312,63547.718750,63546.195312,63515.652344,63489.652344,63454.890625,63445.476562,63446.851562,63391.933594,63356.304688,63317.445312,63315.750000,63310.019531,63282.117188</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>64093.562500,64057.378906,63999.085938,63971.367188,63944.496094,63921.195312,63887.414062,63878.691406,63860.902344,63824.468750,63805.750000,63797.441406,63786.691406,63784.925781,63758.125000,63741.437500,63720.343750,63727.039062,63715.933594,63709.101562,63659.652344,63631.457031,63647.457031,63623.066406</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1595,6 +1595,44 @@
       </c>
       <c r="F31" t="n">
         <v>64185.55078125</v>
+      </c>
+      <c r="G31" t="n">
+        <v>64361.58984375</v>
+      </c>
+      <c r="H31" t="n">
+        <v>176.0390625</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.2735157147723795</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.3544574555948733</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-19 01:44:34</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>24</v>
+      </c>
+      <c r="F32" t="n">
+        <v>64283.62890625</v>
       </c>
     </row>
   </sheetData>
@@ -1608,7 +1646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3474,6 +3512,24 @@
           <t>64226.265625,64234.246094,64218.726562,64218.378906,64219.195312,64227.558594,64227.531250,64241.503906,64238.828125,64224.699219,64225.328125,64219.058594,64218.855469,64231.515625,64226.882812,64224.027344,64224.710938,64230.175781,64236.167969,64237.417969,64215.230469,64207.390625,64203.789062,64185.550781</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>64036.128906,64117.210938,64149.691406,64169.460938,64266.410156,64139.781250,64228.640625,64110.011719,64134.539062,64288.179688,64161.671875,64155.929688,64668.140625,64808.000000,64795.179688,64629.558594,64737.171875,64603.929688,64538.480469,64556.320312,64556.320312,64445.429688,64445.429688,64361.589844</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>190.136719,117.035157,69.035156,48.917968,47.214844,87.777344,1.109375,131.492187,104.289062,63.480468,63.656250,63.128907,449.285156,576.484375,568.296875,405.531250,512.460937,373.753907,302.312500,318.902343,341.089843,238.039062,241.640625,176.039063</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0.296921,0.182533,0.107616,0.076232,0.073467,0.136853,0.001727,0.205104,0.162610,0.098744,0.099212,0.098399,0.694755,0.889527,0.877067,0.627470,0.791602,0.578531,0.468422,0.493991,0.528360,0.369365,0.374954,0.273516</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.3544574555948733</v>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>64211.960938,64209.046875,64233.769531,64201.011719,64217.722656,64189.734375,64202.632812,64229.738281,64212.476562,64196.421875,64197.144531,64180.125000,64187.726562,64212.101562,64195.203125,64228.734375,64193.648438,64200.898438,64182.343750,64236.664062,64182.781250,64227.093750,64167.261719,64165.257812</t>
@@ -3487,6 +3543,49 @@
       <c r="M31" t="inlineStr">
         <is>
           <t>64093.562500,64057.378906,63999.085938,63971.367188,63944.496094,63921.195312,63887.414062,63878.691406,63860.902344,63824.468750,63805.750000,63797.441406,63786.691406,63784.925781,63758.125000,63741.437500,63720.343750,63727.039062,63715.933594,63709.101562,63659.652344,63631.457031,63647.457031,63623.066406</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-19 01:44:34</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>24</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>64374.335938,64359.367188,64344.898438,64338.492188,64345.359375,64355.000000,64368.089844,64372.707031,64363.730469,64361.195312,64373.773438,64363.097656,64366.933594,64363.589844,64364.289062,64355.917969,64357.183594,64361.710938,64341.179688,64336.289062,64312.949219,64322.929688,64304.917969,64283.628906</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>64363.480469,64339.246094,64369.253906,64327.808594,64328.820312,64350.015625,64348.218750,64365.074219,64334.527344,64339.644531,64340.039062,64357.980469,64322.175781,64346.949219,64341.156250,64330.960938,64319.062500,64297.910156,64274.050781,64347.281250,64300.703125,64305.355469,64257.968750,64267.328125</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>64159.660156,64088.390625,64018.652344,63963.566406,63924.988281,63893.242188,63865.957031,63836.632812,63807.789062,63778.742188,63752.539062,63729.296875,63722.968750,63674.320312,63656.144531,63615.304688,63595.996094,63597.363281,63507.109375,63486.304688,63454.152344,63451.410156,63428.761719,63381.796875</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>64241.464844,64186.816406,64131.515625,64103.265625,64077.128906,64060.667969,64047.289062,64029.515625,64007.589844,63994.214844,63978.085938,63964.656250,63941.078125,63919.277344,63911.156250,63887.906250,63872.339844,63875.652344,63829.886719,63824.695312,63788.078125,63774.664062,63759.148438,63720.867188</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1633,6 +1633,44 @@
       </c>
       <c r="F32" t="n">
         <v>64283.62890625</v>
+      </c>
+      <c r="G32" t="n">
+        <v>69585.78125</v>
+      </c>
+      <c r="H32" t="n">
+        <v>5302.15234375</v>
+      </c>
+      <c r="I32" t="n">
+        <v>7.619591601193671</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.266939029373757</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-20 01:43:34</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>24</v>
+      </c>
+      <c r="F33" t="n">
+        <v>68969.171875</v>
       </c>
     </row>
   </sheetData>
@@ -1646,7 +1684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3573,6 +3611,24 @@
           <t>64374.335938,64359.367188,64344.898438,64338.492188,64345.359375,64355.000000,64368.089844,64372.707031,64363.730469,64361.195312,64373.773438,64363.097656,64366.933594,64363.589844,64364.289062,64355.917969,64357.183594,64361.710938,64341.179688,64336.289062,64312.949219,64322.929688,64304.917969,64283.628906</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>64295.839844,64269.359375,64255.101562,64185.230469,64289.820312,64243.550781,64357.121094,64371.570312,64393.800781,64459.109375,64830.890625,64966.718750,65886.250000,68519.632812,68453.976562,68168.312500,68389.117188,68406.132812,69043.250000,69700.000000,69271.429688,69387.773438,69387.773438,69585.781250</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>78.496094,90.007813,89.796875,153.261719,55.539062,111.449219,10.968750,1.136718,30.070312,97.914063,457.117187,603.621094,1519.316406,4156.042968,4089.687500,3812.394531,4031.933593,4044.421875,4702.070312,5363.710938,4958.480468,5064.843750,5082.855468,5302.152344</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0.122086,0.140048,0.139751,0.238780,0.086389,0.173479,0.017044,0.001766,0.046698,0.151901,0.705092,0.929124,2.305969,6.065478,5.974361,5.592620,5.895578,5.912367,6.810326,7.695425,7.158046,7.299332,7.325290,7.619592</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>3.266939029373757</v>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>64363.480469,64339.246094,64369.253906,64327.808594,64328.820312,64350.015625,64348.218750,64365.074219,64334.527344,64339.644531,64340.039062,64357.980469,64322.175781,64346.949219,64341.156250,64330.960938,64319.062500,64297.910156,64274.050781,64347.281250,64300.703125,64305.355469,64257.968750,64267.328125</t>
@@ -3586,6 +3642,49 @@
       <c r="M32" t="inlineStr">
         <is>
           <t>64241.464844,64186.816406,64131.515625,64103.265625,64077.128906,64060.667969,64047.289062,64029.515625,64007.589844,63994.214844,63978.085938,63964.656250,63941.078125,63919.277344,63911.156250,63887.906250,63872.339844,63875.652344,63829.886719,63824.695312,63788.078125,63774.664062,63759.148438,63720.867188</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-20 01:43:34</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>24</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>69503.414062,69495.093750,69399.601562,69428.335938,69377.601562,69435.687500,69431.492188,69392.328125,69366.156250,69306.312500,69301.984375,69276.734375,69181.257812,69230.960938,69237.492188,69194.132812,69203.023438,69198.382812,69181.257812,69113.164062,69078.382812,69061.890625,69028.132812,68969.171875</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>69401.195312,69346.328125,69429.804688,69323.164062,69208.109375,69212.789062,69176.890625,69229.257812,69043.882812,69051.148438,69026.093750,68902.710938,68839.359375,68892.156250,68903.382812,68946.867188,68718.812500,68900.101562,68728.695312,68715.601562,68645.992188,68697.953125,68631.015625,68518.015625</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>68798.062500,68611.210938,68354.578125,68197.445312,68065.851562,67965.695312,67843.296875,67683.875000,67695.976562,67595.757812,67543.523438,67363.460938,67387.242188,67248.796875,67211.820312,67136.437500,67064.007812,67027.867188,66944.375000,66731.367188,66742.054688,66623.492188,66567.593750,66534.218750</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>69062.750000,68958.500000,68740.453125,68734.851562,68556.765625,68530.679688,68492.031250,68381.617188,68337.937500,68250.242188,68179.414062,68169.601562,68022.500000,67982.570312,67970.187500,67940.945312,67911.476562,67866.687500,67808.531250,67704.937500,67680.367188,67576.046875,67556.343750,67463.789062</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1671,6 +1671,44 @@
       </c>
       <c r="F33" t="n">
         <v>68969.171875</v>
+      </c>
+      <c r="G33" t="n">
+        <v>75432.4921875</v>
+      </c>
+      <c r="H33" t="n">
+        <v>6463.3203125</v>
+      </c>
+      <c r="I33" t="n">
+        <v>8.56835048805539</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.514362054098437</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-21 01:48:55</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>24</v>
+      </c>
+      <c r="F34" t="n">
+        <v>73546.7109375</v>
       </c>
     </row>
   </sheetData>
@@ -1684,7 +1722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3672,6 +3710,24 @@
           <t>69503.414062,69495.093750,69399.601562,69428.335938,69377.601562,69435.687500,69431.492188,69392.328125,69366.156250,69306.312500,69301.984375,69276.734375,69181.257812,69230.960938,69237.492188,69194.132812,69203.023438,69198.382812,69181.257812,69113.164062,69078.382812,69061.890625,69028.132812,68969.171875</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>69258.562500,69139.992188,69442.523438,69356.000000,69813.992188,69783.609375,71527.937500,71740.890625,71943.578125,71875.273438,71894.507812,71639.273438,71780.289062,72439.671875,72808.562500,72715.328125,72410.921875,72627.921875,72660.226562,72725.632812,72663.906250,72998.320312,73686.929688,75432.492188</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>244.851562,355.101562,42.921876,72.335938,436.390626,347.921875,2096.445312,2348.562500,2577.421875,2568.960938,2592.523438,2362.539062,2599.031251,3208.710937,3571.070312,3521.195313,3207.898437,3429.539063,3478.968751,3612.468751,3585.523438,3936.429688,4658.796876,6463.320312</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0.353533,0.513598,0.061809,0.104297,0.625076,0.498572,2.930946,3.273673,3.582560,3.574193,3.606010,3.297827,3.620815,4.429494,4.904739,4.842439,4.430131,4.722067,4.787996,4.967257,4.934394,5.392494,6.322420,8.568350</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>3.514362054098437</v>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>69401.195312,69346.328125,69429.804688,69323.164062,69208.109375,69212.789062,69176.890625,69229.257812,69043.882812,69051.148438,69026.093750,68902.710938,68839.359375,68892.156250,68903.382812,68946.867188,68718.812500,68900.101562,68728.695312,68715.601562,68645.992188,68697.953125,68631.015625,68518.015625</t>
@@ -3685,6 +3741,49 @@
       <c r="M33" t="inlineStr">
         <is>
           <t>69062.750000,68958.500000,68740.453125,68734.851562,68556.765625,68530.679688,68492.031250,68381.617188,68337.937500,68250.242188,68179.414062,68169.601562,68022.500000,67982.570312,67970.187500,67940.945312,67911.476562,67866.687500,67808.531250,67704.937500,67680.367188,67576.046875,67556.343750,67463.789062</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-21 01:48:55</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>24</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>75611.953125,75607.781250,75483.546875,75469.156250,75349.625000,75297.695312,75296.484375,75226.656250,75153.343750,75130.414062,75108.820312,75064.859375,74826.132812,74755.859375,74705.039062,74424.945312,74365.539062,74242.835938,74175.515625,74057.085938,73923.554688,73833.085938,73675.414062,73546.710938</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>75566.953125,75374.843750,75557.328125,75250.187500,75224.601562,75127.179688,74845.070312,75069.687500,74868.468750,74884.921875,74781.804688,74529.468750,74432.945312,74409.812500,74293.812500,74173.484375,74021.789062,73852.312500,73812.812500,73492.578125,73469.750000,73478.351562,73179.859375,73011.328125</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>74563.000000,74213.281250,73754.453125,73261.171875,72860.054688,72491.015625,72030.625000,71722.046875,71577.929688,71405.320312,71190.585938,70776.718750,70737.804688,70231.296875,70136.703125,69778.726562,69568.687500,69298.289062,69057.257812,68715.531250,68569.250000,68437.039062,68233.273438,68192.679688</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>74959.179688,74775.101562,74340.718750,74152.546875,73760.843750,73460.367188,73326.242188,73002.945312,72833.382812,72705.265625,72541.375000,72427.437500,72051.312500,71857.976562,71726.937500,71446.656250,71311.226562,71066.578125,70948.390625,70697.898438,70540.320312,70383.328125,70190.593750,70097.328125</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,6 +1709,44 @@
       </c>
       <c r="F34" t="n">
         <v>73546.7109375</v>
+      </c>
+      <c r="G34" t="n">
+        <v>77982.1015625</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4435.390625</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5.687703378249156</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.254810901850366</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-22 01:41:57</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>24</v>
+      </c>
+      <c r="F35" t="n">
+        <v>77047.53125</v>
       </c>
     </row>
   </sheetData>
@@ -1722,7 +1760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3771,6 +3809,24 @@
           <t>75611.953125,75607.781250,75483.546875,75469.156250,75349.625000,75297.695312,75296.484375,75226.656250,75153.343750,75130.414062,75108.820312,75064.859375,74826.132812,74755.859375,74705.039062,74424.945312,74365.539062,74242.835938,74175.515625,74057.085938,73923.554688,73833.085938,73675.414062,73546.710938</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>74412.851562,74478.953125,74999.992188,75438.093750,75615.789062,76288.117188,79250.007812,77888.179688,77812.820312,76709.632812,77188.773438,77251.867188,77369.320312,77191.796875,77451.343750,77370.281250,77110.523438,77003.921875,77497.968750,78546.851562,78546.851562,77934.062500,77934.062500,77982.101562</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>1199.101562,1128.828125,483.554688,31.062500,266.164062,990.421876,3953.523438,2661.523438,2659.476562,1579.218751,2079.953126,2187.007812,2543.187501,2435.937500,2746.304688,2945.335938,2744.984376,2761.085937,3322.453125,4489.765624,4623.296874,4100.976562,4258.648438,4435.390624</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1.611417,1.515634,0.644740,0.041176,0.351995,1.298265,4.988673,3.417108,3.417787,2.058697,2.694632,2.831010,3.287075,3.155695,3.545845,3.806805,3.559805,3.585643,4.287149,5.716035,5.886037,5.262111,5.464425,5.687703</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>3.254810901850366</v>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>75566.953125,75374.843750,75557.328125,75250.187500,75224.601562,75127.179688,74845.070312,75069.687500,74868.468750,74884.921875,74781.804688,74529.468750,74432.945312,74409.812500,74293.812500,74173.484375,74021.789062,73852.312500,73812.812500,73492.578125,73469.750000,73478.351562,73179.859375,73011.328125</t>
@@ -3784,6 +3840,49 @@
       <c r="M34" t="inlineStr">
         <is>
           <t>74959.179688,74775.101562,74340.718750,74152.546875,73760.843750,73460.367188,73326.242188,73002.945312,72833.382812,72705.265625,72541.375000,72427.437500,72051.312500,71857.976562,71726.937500,71446.656250,71311.226562,71066.578125,70948.390625,70697.898438,70540.320312,70383.328125,70190.593750,70097.328125</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-22 01:41:57</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>24</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>78030.515625,78028.125000,78008.718750,78027.812500,77942.226562,77928.007812,77837.031250,77844.734375,77794.210938,77678.750000,77680.406250,77660.992188,77498.359375,77380.789062,77433.593750,77308.398438,77307.843750,77263.992188,77267.195312,77183.773438,77081.757812,77084.593750,77119.820312,77047.531250</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>77933.250000,77863.632812,78050.421875,77926.835938,77688.679688,77741.062500,77371.742188,77752.359375,77452.976562,77416.906250,77256.125000,77142.914062,76884.820312,77025.429688,76995.382812,76867.281250,76700.343750,76716.742188,76761.929688,76630.179688,76635.476562,76660.828125,76313.875000,76335.656250</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>77285.101562,77118.421875,76786.828125,76524.664062,76160.968750,76040.476562,75594.015625,75312.015625,75230.937500,75011.984375,74783.164062,74409.640625,74422.125000,73967.484375,73857.976562,73718.937500,73501.367188,73296.492188,73063.679688,72646.882812,72461.070312,72316.039062,72251.851562,72256.617188</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>77565.531250,77440.148438,77137.710938,77120.296875,76815.585938,76701.289062,76528.367188,76328.328125,76210.039062,76032.390625,75901.921875,75776.593750,75467.687500,75304.617188,75194.226562,75150.445312,75038.390625,74905.593750,74789.820312,74584.445312,74393.328125,74231.468750,74252.773438,74192.906250</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1747,6 +1747,44 @@
       </c>
       <c r="F35" t="n">
         <v>77047.53125</v>
+      </c>
+      <c r="G35" t="n">
+        <v>77249.171875</v>
+      </c>
+      <c r="H35" t="n">
+        <v>201.640625</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.2610262610015844</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.4856350845390183</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-23 01:51:50</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>24</v>
+      </c>
+      <c r="F36" t="n">
+        <v>76906.234375</v>
       </c>
     </row>
   </sheetData>
@@ -1760,7 +1798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3870,6 +3908,24 @@
           <t>78030.515625,78028.125000,78008.718750,78027.812500,77942.226562,77928.007812,77837.031250,77844.734375,77794.210938,77678.750000,77680.406250,77660.992188,77498.359375,77380.789062,77433.593750,77308.398438,77307.843750,77263.992188,77267.195312,77183.773438,77081.757812,77084.593750,77119.820312,77047.531250</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>78462.796875,78402.617188,78475.710938,77351.187500,77477.250000,77286.242188,77195.492188,77049.398438,76964.882812,77114.351562,77300.007812,77277.296875,76995.593750,76970.562500,77282.460938,77270.523438,77261.921875,77419.937500,77312.976562,76847.367188,76979.992188,77289.000000,77289.000000,77249.171875</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>432.281250,374.492188,466.992188,676.625000,464.976562,641.765624,641.539062,795.335938,829.328126,564.398438,380.398438,383.695313,502.765625,410.226562,151.132812,37.875001,45.921875,155.945312,45.781251,336.406251,101.765624,204.406250,169.179688,201.640625</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0.550938,0.477653,0.595079,0.874744,0.600146,0.830375,0.831058,1.032242,1.077541,0.731898,0.492107,0.496518,0.652980,0.532966,0.195559,0.049016,0.059437,0.201428,0.059215,0.437759,0.132197,0.264470,0.218892,0.261026</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0.4856350845390183</v>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>77933.250000,77863.632812,78050.421875,77926.835938,77688.679688,77741.062500,77371.742188,77752.359375,77452.976562,77416.906250,77256.125000,77142.914062,76884.820312,77025.429688,76995.382812,76867.281250,76700.343750,76716.742188,76761.929688,76630.179688,76635.476562,76660.828125,76313.875000,76335.656250</t>
@@ -3883,6 +3939,49 @@
       <c r="M35" t="inlineStr">
         <is>
           <t>77565.531250,77440.148438,77137.710938,77120.296875,76815.585938,76701.289062,76528.367188,76328.328125,76210.039062,76032.390625,75901.921875,75776.593750,75467.687500,75304.617188,75194.226562,75150.445312,75038.390625,74905.593750,74789.820312,74584.445312,74393.328125,74231.468750,74252.773438,74192.906250</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-23 01:51:50</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>24</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>77185.601562,77146.742188,77135.156250,77150.375000,77091.609375,77093.359375,77104.492188,77041.671875,77005.203125,76931.171875,76936.953125,76928.515625,76917.562500,76875.703125,76962.828125,76956.953125,76914.492188,76929.257812,76890.359375,76921.781250,76881.593750,76915.406250,76898.562500,76906.234375</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>77176.039062,77031.898438,77110.125000,77080.257812,76977.960938,77054.921875,76932.140625,76955.359375,77044.984375,76889.562500,76860.507812,76821.195312,76586.500000,76729.828125,76762.632812,76746.359375,76648.937500,76734.093750,76622.171875,76725.671875,76802.429688,76669.234375,76554.382812,76690.890625</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>76992.132812,76920.625000,76787.851562,76736.789062,76544.539062,76497.507812,76388.210938,76197.632812,76151.742188,76075.109375,75980.351562,75794.187500,75809.890625,75595.750000,75579.546875,75521.609375,75376.507812,75324.390625,75095.507812,75035.468750,74914.242188,74804.007812,74736.242188,74763.281250</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>77108.507812,76999.390625,76950.195312,76913.289062,76751.960938,76719.812500,76714.328125,76591.984375,76572.164062,76496.765625,76433.250000,76417.453125,76310.359375,76184.109375,76247.492188,76220.929688,76130.335938,76068.625000,75939.593750,75980.281250,75872.382812,75780.445312,75798.062500,75766.296875</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1785,6 +1785,44 @@
       </c>
       <c r="F36" t="n">
         <v>76906.234375</v>
+      </c>
+      <c r="G36" t="n">
+        <v>77223.8671875</v>
+      </c>
+      <c r="H36" t="n">
+        <v>317.6328125</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.4113143048492841</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.6848298243546073</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:49:29</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>24</v>
+      </c>
+      <c r="F37" t="n">
+        <v>76932.65625</v>
       </c>
     </row>
   </sheetData>
@@ -1798,7 +1836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3969,6 +4007,24 @@
           <t>77185.601562,77146.742188,77135.156250,77150.375000,77091.609375,77093.359375,77104.492188,77041.671875,77005.203125,76931.171875,76936.953125,76928.515625,76917.562500,76875.703125,76962.828125,76956.953125,76914.492188,76929.257812,76890.359375,76921.781250,76881.593750,76915.406250,76898.562500,76906.234375</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>77064.679688,76916.992188,76599.437500,76058.070312,76090.820312,75986.992188,76464.937500,76540.000000,76776.937500,77288.156250,77201.593750,77477.242188,77179.281250,77141.093750,77405.671875,77171.648438,77325.000000,77328.296875,77393.187500,77832.500000,77600.656250,77725.593750,77668.242188,77223.867188</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>120.921874,229.750001,535.718750,1092.304688,1000.789062,1106.367188,639.554688,501.671875,228.265625,356.984375,264.640625,548.726562,261.718750,265.390625,442.843750,214.695312,410.507812,399.039063,502.828125,910.718750,719.062500,810.187500,769.679688,317.632812</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0.156910,0.298699,0.699377,1.436146,1.315256,1.455996,0.836403,0.655438,0.297310,0.461888,0.342792,0.708242,0.339105,0.344033,0.572108,0.278205,0.530886,0.516032,0.649706,1.170101,0.926619,1.042369,0.990984,0.411314</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0.6848298243546073</v>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>77176.039062,77031.898438,77110.125000,77080.257812,76977.960938,77054.921875,76932.140625,76955.359375,77044.984375,76889.562500,76860.507812,76821.195312,76586.500000,76729.828125,76762.632812,76746.359375,76648.937500,76734.093750,76622.171875,76725.671875,76802.429688,76669.234375,76554.382812,76690.890625</t>
@@ -3982,6 +4038,49 @@
       <c r="M36" t="inlineStr">
         <is>
           <t>77108.507812,76999.390625,76950.195312,76913.289062,76751.960938,76719.812500,76714.328125,76591.984375,76572.164062,76496.765625,76433.250000,76417.453125,76310.359375,76184.109375,76247.492188,76220.929688,76130.335938,76068.625000,75939.593750,75980.281250,75872.382812,75780.445312,75798.062500,75766.296875</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:49:29</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>24</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>77216.406250,77168.570312,77084.109375,77179.218750,77080.328125,77118.906250,77063.664062,77108.070312,77056.617188,77021.921875,76989.039062,77049.265625,77022.921875,76992.132812,76983.625000,77062.882812,77005.867188,77042.187500,76948.945312,76971.070312,76918.468750,76947.289062,76862.781250,76932.656250</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>77077.625000,77065.250000,77006.453125,77007.960938,76916.343750,77023.382812,76814.218750,77022.578125,76934.046875,76942.039062,76848.085938,76830.757812,76697.296875,76747.976562,76773.859375,76809.054688,76595.062500,76779.578125,76609.195312,76741.523438,76706.843750,76631.789062,76505.765625,76702.437500</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>76845.484375,76731.664062,76451.148438,76508.898438,76285.593750,76165.328125,76021.187500,76003.585938,75829.179688,75760.578125,75568.750000,75508.460938,75548.875000,75300.906250,75095.109375,75162.718750,75032.460938,75022.078125,74768.445312,74705.281250,74537.703125,74450.765625,74300.023438,74429.078125</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>77042.554688,76910.304688,76766.671875,76810.000000,76612.718750,76550.367188,76422.546875,76410.203125,76361.320312,76298.070312,76136.062500,76211.054688,76099.218750,75971.585938,75868.625000,75921.250000,75836.406250,75832.890625,75652.484375,75739.109375,75588.093750,75495.554688,75457.507812,75538.507812</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1823,6 +1823,44 @@
       </c>
       <c r="F37" t="n">
         <v>76932.65625</v>
+      </c>
+      <c r="G37" t="n">
+        <v>79729.7890625</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2797.1328125</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3.508265662545945</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.76825946500119</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-25 01:43:51</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>24</v>
+      </c>
+      <c r="F38" t="n">
+        <v>79914.09375</v>
       </c>
     </row>
   </sheetData>
@@ -1836,7 +1874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4068,6 +4106,24 @@
           <t>77216.406250,77168.570312,77084.109375,77179.218750,77080.328125,77118.906250,77063.664062,77108.070312,77056.617188,77021.921875,76989.039062,77049.265625,77022.921875,76992.132812,76983.625000,77062.882812,77005.867188,77042.187500,76948.945312,76971.070312,76918.468750,76947.289062,76862.781250,76932.656250</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>77466.328125,76933.460938,76893.226562,77159.593750,77459.132812,77297.867188,77032.906250,77540.882812,77608.859375,78434.023438,79137.039062,78562.398438,79484.320312,79079.500000,79041.039062,78744.937500,78926.492188,78744.359375,78913.781250,78868.007812,78868.007812,79743.828125,79743.828125,79729.789062</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>249.921875,235.109374,190.882812,19.625000,378.804688,178.960938,30.757812,432.812501,552.242187,1412.101562,2148.000001,1513.132812,2461.398438,2087.367188,2057.414062,1682.054688,1920.624999,1702.171875,1964.835938,1896.937501,1949.539062,2796.539063,2881.046875,2797.132812</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0.322620,0.305601,0.248244,0.025434,0.489038,0.231521,0.039928,0.558173,0.711571,1.800369,2.714279,1.926027,3.096709,2.639581,2.602969,2.136080,2.433435,2.161643,2.489851,2.405205,2.471901,3.506903,3.612878,3.508266</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>1.76825946500119</v>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>77077.625000,77065.250000,77006.453125,77007.960938,76916.343750,77023.382812,76814.218750,77022.578125,76934.046875,76942.039062,76848.085938,76830.757812,76697.296875,76747.976562,76773.859375,76809.054688,76595.062500,76779.578125,76609.195312,76741.523438,76706.843750,76631.789062,76505.765625,76702.437500</t>
@@ -4081,6 +4137,49 @@
       <c r="M37" t="inlineStr">
         <is>
           <t>77042.554688,76910.304688,76766.671875,76810.000000,76612.718750,76550.367188,76422.546875,76410.203125,76361.320312,76298.070312,76136.062500,76211.054688,76099.218750,75971.585938,75868.625000,75921.250000,75836.406250,75832.890625,75652.484375,75739.109375,75588.093750,75495.554688,75457.507812,75538.507812</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-25 01:43:51</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>24</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>79704.984375,79772.859375,79745.000000,79856.507812,79726.406250,79872.781250,79827.468750,79847.351562,79828.734375,79872.367188,79819.398438,79917.640625,79789.773438,79848.546875,79906.132812,79997.156250,79906.890625,79951.656250,79886.992188,79862.843750,79863.593750,79872.359375,79874.929688,79914.093750</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>79528.242188,79710.570312,79705.437500,79718.953125,79633.187500,79689.976562,79554.593750,79773.562500,79571.539062,79681.039062,79700.695312,79588.453125,79382.210938,79633.796875,79691.000000,79770.234375,79515.382812,79640.421875,79545.085938,79570.484375,79543.234375,79722.195312,79481.531250,79714.750000</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>79023.046875,79053.531250,78845.281250,78898.078125,78638.265625,78580.500000,78403.515625,78357.234375,78193.984375,78131.226562,77910.226562,77863.796875,77833.179688,77726.609375,77615.375000,77790.773438,77564.750000,77597.367188,77372.656250,77250.656250,77146.890625,77045.250000,76992.796875,77121.921875</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>79314.617188,79339.187500,79233.125000,79297.085938,79064.500000,79081.968750,78970.117188,78915.539062,78882.734375,78822.890625,78656.492188,78756.179688,78596.976562,78539.492188,78497.640625,78673.859375,78537.164062,78529.468750,78416.007812,78433.171875,78288.289062,78179.796875,78249.257812,78269.617188</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1861,6 +1861,44 @@
       </c>
       <c r="F38" t="n">
         <v>79914.09375</v>
+      </c>
+      <c r="G38" t="n">
+        <v>78822.5703125</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1091.5234375</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.384785389733608</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.058502043702079</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-26 01:49:16</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>24</v>
+      </c>
+      <c r="F39" t="n">
+        <v>78328.9375</v>
       </c>
     </row>
   </sheetData>
@@ -1874,7 +1912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4167,6 +4205,24 @@
           <t>79704.984375,79772.859375,79745.000000,79856.507812,79726.406250,79872.781250,79827.468750,79847.351562,79828.734375,79872.367188,79819.398438,79917.640625,79789.773438,79848.546875,79906.132812,79997.156250,79906.890625,79951.656250,79886.992188,79862.843750,79863.593750,79872.359375,79874.929688,79914.093750</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>80634.398438,80468.968750,80348.070312,80702.000000,80533.773438,79674.210938,79905.812500,79177.828125,79293.179688,79118.992188,78966.960938,78627.359375,79225.007812,79506.226562,79153.296875,79234.101562,79135.679688,78923.812500,78184.046875,78550.578125,78823.531250,78632.359375,78632.359375,78822.570312</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>929.414062,696.109375,603.070312,845.492188,807.367188,198.570312,78.343750,669.523437,535.554688,753.375001,852.437501,1290.281250,564.765626,342.320312,752.835937,763.054688,771.210938,1027.843750,1702.945313,1312.265625,1040.062500,1240.000000,1242.570313,1091.523438</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1.152627,0.865066,0.750572,1.047672,1.002520,0.249228,0.098045,0.845595,0.675411,0.952205,1.079486,1.641008,0.712863,0.430558,0.951111,0.963038,0.974543,1.302324,2.178124,1.670600,1.319482,1.576959,1.580228,1.384785</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>1.058502043702079</v>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>79528.242188,79710.570312,79705.437500,79718.953125,79633.187500,79689.976562,79554.593750,79773.562500,79571.539062,79681.039062,79700.695312,79588.453125,79382.210938,79633.796875,79691.000000,79770.234375,79515.382812,79640.421875,79545.085938,79570.484375,79543.234375,79722.195312,79481.531250,79714.750000</t>
@@ -4180,6 +4236,49 @@
       <c r="M38" t="inlineStr">
         <is>
           <t>79314.617188,79339.187500,79233.125000,79297.085938,79064.500000,79081.968750,78970.117188,78915.539062,78882.734375,78822.890625,78656.492188,78756.179688,78596.976562,78539.492188,78497.640625,78673.859375,78537.164062,78529.468750,78416.007812,78433.171875,78288.289062,78179.796875,78249.257812,78269.617188</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-26 01:49:16</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>24</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>78831.195312,78819.312500,78742.601562,78766.429688,78639.125000,78641.984375,78577.414062,78557.570312,78527.500000,78434.132812,78334.429688,78400.359375,78402.031250,78354.546875,78371.031250,78408.687500,78317.695312,78290.468750,78320.703125,78242.210938,78284.812500,78303.187500,78290.867188,78328.937500</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>78628.523438,78830.398438,78509.695312,78701.140625,78595.617188,78574.609375,78402.976562,78359.164062,78441.085938,78303.796875,78288.625000,78182.812500,78118.609375,78050.781250,78153.609375,78125.742188,78050.062500,78017.343750,78088.023438,77955.781250,78064.992188,78061.742188,77920.382812,78188.265625</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>78186.117188,78128.046875,77834.414062,77830.320312,77567.304688,77413.742188,77244.531250,77141.398438,76915.781250,76716.726562,76455.617188,76436.078125,76490.664062,76290.710938,76162.070312,76192.765625,75937.164062,75813.593750,75698.203125,75567.546875,75476.250000,75387.359375,75334.742188,75379.156250</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>78467.171875,78385.429688,78222.640625,78198.289062,77963.359375,77876.375000,77725.867188,77591.265625,77589.242188,77387.695312,77156.992188,77236.679688,77222.421875,77091.140625,77023.164062,77101.968750,76897.687500,76771.414062,76745.679688,76717.632812,76659.210938,76556.789062,76625.210938,76540.843750</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1899,6 +1899,44 @@
       </c>
       <c r="F39" t="n">
         <v>78328.9375</v>
+      </c>
+      <c r="G39" t="n">
+        <v>78893.5</v>
+      </c>
+      <c r="H39" t="n">
+        <v>564.5625</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.715600778264369</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.3412197791074567</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-27 08:54:21</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>24</v>
+      </c>
+      <c r="F40" t="n">
+        <v>79760.28125</v>
       </c>
     </row>
   </sheetData>
@@ -1912,7 +1950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4266,6 +4304,24 @@
           <t>78831.195312,78819.312500,78742.601562,78766.429688,78639.125000,78641.984375,78577.414062,78557.570312,78527.500000,78434.132812,78334.429688,78400.359375,78402.031250,78354.546875,78371.031250,78408.687500,78317.695312,78290.468750,78320.703125,78242.210938,78284.812500,78303.187500,78290.867188,78328.937500</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>79098.250000,79075.523438,78823.851562,79080.250000,78934.023438,78915.976562,78690.976562,78434.750000,78707.890625,78467.421875,78300.148438,78446.781250,77787.539062,78013.359375,77982.226562,78441.453125,78471.382812,78463.007812,78448.546875,78720.898438,78704.171875,79026.179688,78695.117188,78893.500000</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>267.054688,256.210938,81.250001,313.820312,294.898438,273.992188,113.562501,122.820312,180.390625,33.289063,34.281251,46.421875,614.492188,341.187500,388.804688,32.765625,153.687501,172.539062,127.843750,478.687499,419.359375,722.992188,404.249999,564.562500</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0.337624,0.324008,0.103078,0.396838,0.373601,0.347195,0.144315,0.156589,0.229190,0.042424,0.043782,0.059176,0.789962,0.437345,0.498581,0.041771,0.195852,0.219899,0.162965,0.608082,0.532830,0.914877,0.513691,0.715601</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0.3412197791074567</v>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>78628.523438,78830.398438,78509.695312,78701.140625,78595.617188,78574.609375,78402.976562,78359.164062,78441.085938,78303.796875,78288.625000,78182.812500,78118.609375,78050.781250,78153.609375,78125.742188,78050.062500,78017.343750,78088.023438,77955.781250,78064.992188,78061.742188,77920.382812,78188.265625</t>
@@ -4279,6 +4335,49 @@
       <c r="M39" t="inlineStr">
         <is>
           <t>78467.171875,78385.429688,78222.640625,78198.289062,77963.359375,77876.375000,77725.867188,77591.265625,77589.242188,77387.695312,77156.992188,77236.679688,77222.421875,77091.140625,77023.164062,77101.968750,76897.687500,76771.414062,76745.679688,76717.632812,76659.210938,76556.789062,76625.210938,76540.843750</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-27 08:54:21</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>24</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>79836.039062,79824.882812,79908.812500,79946.664062,79908.890625,79906.593750,79921.593750,79848.140625,79882.289062,79834.476562,79821.046875,79876.679688,79872.070312,79805.335938,79855.273438,79809.562500,79824.101562,79796.093750,79769.625000,79769.609375,79795.171875,79696.562500,79734.718750,79760.281250</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>79688.851562,79873.757812,79804.203125,79831.187500,79850.187500,79883.710938,79768.187500,79724.453125,79803.343750,79713.914062,79776.234375,79641.687500,79596.640625,79700.382812,79697.421875,79607.375000,79501.750000,79420.101562,79544.250000,79500.382812,79516.562500,79453.109375,79564.398438,79608.218750</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>79202.367188,79173.593750,79168.898438,79240.500000,79046.171875,78887.515625,78941.156250,78823.484375,78705.468750,78538.914062,78448.640625,78519.468750,78500.554688,78273.078125,78191.468750,78160.296875,78075.320312,78099.812500,77901.648438,77790.093750,77837.914062,77596.632812,77589.210938,77618.835938</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>79495.945312,79418.117188,79504.523438,79506.992188,79383.101562,79272.031250,79254.062500,79113.179688,79200.632812,79041.031250,79007.429688,79069.281250,79045.210938,78810.453125,78820.718750,78802.882812,78772.734375,78718.289062,78636.203125,78667.156250,78575.421875,78419.562500,78427.265625,78424.687500</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1937,6 +1937,44 @@
       </c>
       <c r="F40" t="n">
         <v>79760.28125</v>
+      </c>
+      <c r="G40" t="n">
+        <v>79520.046875</v>
+      </c>
+      <c r="H40" t="n">
+        <v>240.234375</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.3021054242807877</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.4162891409138172</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:07:18</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>24</v>
+      </c>
+      <c r="F41" t="n">
+        <v>79586.8515625</v>
       </c>
     </row>
   </sheetData>
@@ -1950,7 +1988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4365,6 +4403,24 @@
           <t>79836.039062,79824.882812,79908.812500,79946.664062,79908.890625,79906.593750,79921.593750,79848.140625,79882.289062,79834.476562,79821.046875,79876.679688,79872.070312,79805.335938,79855.273438,79809.562500,79824.101562,79796.093750,79769.625000,79769.609375,79795.171875,79696.562500,79734.718750,79760.281250</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>79988.742188,79619.492188,79476.343750,79276.062500,79533.000000,80221.312500,80320.570312,80384.789062,80445.132812,80174.531250,79932.531250,80111.046875,80202.156250,80322.046875,80269.390625,80597.593750,80509.109375,79937.492188,79824.703125,79649.226562,79691.539062,79909.078125,79677.000000,79520.046875</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>152.703126,205.390624,432.468750,670.601562,375.890625,314.718750,398.976562,536.648438,562.843751,340.054688,111.484375,234.367187,330.085938,516.710937,414.117187,788.031250,685.007813,141.398438,55.078125,120.382812,103.632812,212.515625,57.718750,240.234375</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0.190906,0.257965,0.544148,0.845907,0.472622,0.392313,0.496730,0.667599,0.699662,0.424143,0.139473,0.292553,0.411567,0.643299,0.515909,0.977735,0.850845,0.176886,0.068999,0.151141,0.130042,0.265947,0.072441,0.302105</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0.4162891409138172</v>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>79688.851562,79873.757812,79804.203125,79831.187500,79850.187500,79883.710938,79768.187500,79724.453125,79803.343750,79713.914062,79776.234375,79641.687500,79596.640625,79700.382812,79697.421875,79607.375000,79501.750000,79420.101562,79544.250000,79500.382812,79516.562500,79453.109375,79564.398438,79608.218750</t>
@@ -4378,6 +4434,49 @@
       <c r="M40" t="inlineStr">
         <is>
           <t>79495.945312,79418.117188,79504.523438,79506.992188,79383.101562,79272.031250,79254.062500,79113.179688,79200.632812,79041.031250,79007.429688,79069.281250,79045.210938,78810.453125,78820.718750,78802.882812,78772.734375,78718.289062,78636.203125,78667.156250,78575.421875,78419.562500,78427.265625,78424.687500</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:07:18</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>24</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>79672.117188,79598.609375,79627.851562,79686.500000,79631.390625,79630.835938,79665.585938,79667.578125,79632.937500,79650.468750,79623.921875,79659.132812,79656.640625,79608.281250,79616.656250,79666.718750,79688.179688,79576.296875,79568.539062,79580.953125,79584.789062,79543.210938,79555.093750,79586.851562</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>79536.312500,79648.281250,79465.117188,79556.007812,79591.648438,79596.187500,79535.242188,79484.031250,79625.007812,79591.023438,79628.554688,79518.101562,79436.359375,79471.304688,79441.867188,79473.062500,79455.757812,79366.296875,79411.148438,79293.226562,79327.085938,79290.937500,79475.265625,79435.078125</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>79138.968750,79140.687500,79142.054688,79221.539062,79046.187500,78968.039062,79026.242188,78978.031250,78798.781250,78765.984375,78658.562500,78722.531250,78709.562500,78592.250000,78540.171875,78540.515625,78518.875000,78424.296875,78265.812500,78198.796875,78183.414062,78071.187500,78028.625000,78060.882812</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>79413.226562,79311.859375,79377.343750,79404.281250,79290.867188,79231.250000,79222.710938,79180.687500,79165.429688,79098.031250,79045.851562,79113.890625,79148.750000,78992.984375,78980.523438,79029.359375,79064.445312,78851.343750,78813.359375,78840.789062,78786.015625,78691.968750,78693.171875,78673.500000</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1975,6 +1975,44 @@
       </c>
       <c r="F41" t="n">
         <v>79586.8515625</v>
+      </c>
+      <c r="G41" t="n">
+        <v>77469.2109375</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2117.640625</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.73352548628442</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.270141149469886</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-29 06:51:53</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>24</v>
+      </c>
+      <c r="F42" t="n">
+        <v>77422.859375</v>
       </c>
     </row>
   </sheetData>
@@ -1988,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4464,6 +4502,24 @@
           <t>79672.117188,79598.609375,79627.851562,79686.500000,79631.390625,79630.835938,79665.585938,79667.578125,79632.937500,79650.468750,79623.921875,79659.132812,79656.640625,79608.281250,79616.656250,79666.718750,79688.179688,79576.296875,79568.539062,79580.953125,79584.789062,79543.210938,79555.093750,79586.851562</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>79417.593750,79490.156250,79546.460938,78324.226562,77788.492188,77900.976562,77543.546875,77533.640625,77399.992188,77365.476562,77749.343750,77838.671875,77734.476562,77792.039062,77668.093750,77501.046875,77640.421875,77635.429688,77469.210938,77469.210938,77469.210938,77469.210938,77469.210938,77469.210938</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>254.523438,108.453125,81.390624,1362.273438,1842.898438,1729.859376,2122.039063,2133.937500,2232.945312,2284.992188,1874.578125,1820.460937,1922.164062,1816.242188,1948.562500,2165.671875,2047.757813,1940.867188,2099.328124,2111.742188,2115.578124,2074.000001,2085.882812,2117.640624</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0.320487,0.136436,0.102318,1.739275,2.369114,2.220588,2.736577,2.752273,2.884943,2.953504,2.411053,2.338762,2.472730,2.334740,2.508833,2.794378,2.637489,2.499976,2.709887,2.725912,2.730863,2.677193,2.692531,2.733525</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>2.270141149469886</v>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>79536.312500,79648.281250,79465.117188,79556.007812,79591.648438,79596.187500,79535.242188,79484.031250,79625.007812,79591.023438,79628.554688,79518.101562,79436.359375,79471.304688,79441.867188,79473.062500,79455.757812,79366.296875,79411.148438,79293.226562,79327.085938,79290.937500,79475.265625,79435.078125</t>
@@ -4477,6 +4533,49 @@
       <c r="M41" t="inlineStr">
         <is>
           <t>79413.226562,79311.859375,79377.343750,79404.281250,79290.867188,79231.250000,79222.710938,79180.687500,79165.429688,79098.031250,79045.851562,79113.890625,79148.750000,78992.984375,78980.523438,79029.359375,79064.445312,78851.343750,78813.359375,78840.789062,78786.015625,78691.968750,78693.171875,78673.500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-29 06:51:53</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>24</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>77519.265625,77421.093750,77429.023438,77446.562500,77398.078125,77443.445312,77446.718750,77397.773438,77427.039062,77425.992188,77340.703125,77378.875000,77390.835938,77317.023438,77364.960938,77369.140625,77400.468750,77356.054688,77364.031250,77431.093750,77459.500000,77424.054688,77399.312500,77422.859375</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>77472.390625,77527.039062,77316.710938,77401.195312,77427.843750,77429.031250,77319.453125,77274.289062,77471.421875,77379.468750,77390.562500,77252.812500,77207.937500,77348.304688,77253.101562,77157.195312,77184.156250,77193.195312,77376.523438,77154.429688,77262.882812,77108.320312,77278.632812,77113.726562</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>77026.484375,76920.343750,76813.429688,76836.500000,76614.000000,76534.234375,76592.617188,76491.468750,76302.828125,76229.554688,76039.539062,76094.187500,76029.593750,75870.476562,75825.328125,75754.312500,75725.382812,75636.343750,75493.906250,75471.273438,75433.015625,75327.804688,75222.281250,75216.843750</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>77302.304688,77133.460938,77101.125000,77072.609375,76921.156250,76920.453125,76881.421875,76786.992188,76831.640625,76734.421875,76567.882812,76629.734375,76637.664062,76431.976562,76463.875000,76449.148438,76430.640625,76303.406250,76253.914062,76353.203125,76290.242188,76168.835938,76145.187500,76172.789062</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2013,6 +2013,44 @@
       </c>
       <c r="F42" t="n">
         <v>77422.859375</v>
+      </c>
+      <c r="G42" t="n">
+        <v>78169.8828125</v>
+      </c>
+      <c r="H42" t="n">
+        <v>747.0234375</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.9556409842545457</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.726264685499683</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-30 05:05:36</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>24</v>
+      </c>
+      <c r="F43" t="n">
+        <v>78234.015625</v>
       </c>
     </row>
   </sheetData>
@@ -2026,7 +2064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4563,6 +4601,24 @@
           <t>77519.265625,77421.093750,77429.023438,77446.562500,77398.078125,77443.445312,77446.718750,77397.773438,77427.039062,77425.992188,77340.703125,77378.875000,77390.835938,77317.023438,77364.960938,77369.140625,77400.468750,77356.054688,77364.031250,77431.093750,77459.500000,77424.054688,77399.312500,77422.859375</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>77619.000000,77641.781250,77642.406250,77628.460938,77575.406250,77584.617188,77692.757812,78001.562500,77855.578125,78018.257812,78096.406250,78153.000000,78193.601562,78119.671875,78164.218750,78221.859375,78233.929688,78175.921875,78076.906250,78097.648438,78135.101562,78116.148438,78169.882812,78169.882812</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>99.734375,220.687500,213.382812,181.898438,177.328125,141.171876,246.039062,603.789062,428.539063,592.265624,755.703125,774.125000,802.765624,802.648437,799.257812,852.718750,833.460938,819.867187,712.875000,666.554688,675.601562,692.093749,770.570312,747.023438</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0.128492,0.284238,0.274828,0.234319,0.228588,0.181959,0.316682,0.774073,0.550428,0.759137,0.967654,0.990525,1.026639,1.027460,1.022537,1.090128,1.065345,1.048746,0.913042,0.853489,0.864658,0.885980,0.985764,0.955641</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0.726264685499683</v>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>77472.390625,77527.039062,77316.710938,77401.195312,77427.843750,77429.031250,77319.453125,77274.289062,77471.421875,77379.468750,77390.562500,77252.812500,77207.937500,77348.304688,77253.101562,77157.195312,77184.156250,77193.195312,77376.523438,77154.429688,77262.882812,77108.320312,77278.632812,77113.726562</t>
@@ -4576,6 +4632,49 @@
       <c r="M42" t="inlineStr">
         <is>
           <t>77302.304688,77133.460938,77101.125000,77072.609375,76921.156250,76920.453125,76881.421875,76786.992188,76831.640625,76734.421875,76567.882812,76629.734375,76637.664062,76431.976562,76463.875000,76449.148438,76430.640625,76303.406250,76253.914062,76353.203125,76290.242188,76168.835938,76145.187500,76172.789062</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-30 05:05:36</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>24</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>78245.554688,78188.515625,78233.726562,78298.851562,78278.960938,78274.859375,78299.375000,78293.296875,78298.960938,78301.242188,78267.867188,78311.781250,78293.109375,78237.000000,78296.265625,78287.726562,78322.765625,78225.117188,78220.906250,78254.710938,78282.109375,78205.148438,78192.156250,78234.015625</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>78232.882812,78191.726562,78139.375000,78244.414062,78340.453125,78227.585938,78295.296875,78314.367188,78289.703125,78277.695312,78311.976562,78206.187500,78196.179688,78301.695312,78267.992188,78112.335938,78199.609375,78095.703125,78211.296875,78100.968750,78171.359375,77963.109375,78188.984375,78093.703125</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>77848.695312,77818.750000,77807.960938,77909.554688,77769.453125,77692.992188,77760.921875,77752.500000,77598.109375,77563.343750,77507.890625,77537.453125,77460.570312,77357.914062,77374.625000,77315.242188,77288.695312,77224.726562,77048.742188,77004.335938,77024.875000,76886.593750,76825.570312,76860.250000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>78076.671875,77980.656250,78004.492188,78050.046875,77965.570312,77912.062500,77922.781250,77914.539062,77955.398438,77881.109375,77822.960938,77875.914062,77867.359375,77696.570312,77758.914062,77727.125000,77713.414062,77602.046875,77520.601562,77562.835938,77510.500000,77399.109375,77377.179688,77427.796875</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2051,6 +2051,44 @@
       </c>
       <c r="F43" t="n">
         <v>78234.015625</v>
+      </c>
+      <c r="G43" t="n">
+        <v>77719.9921875</v>
+      </c>
+      <c r="H43" t="n">
+        <v>514.0234375</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.6613786530754082</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.5613249294717828</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-31 05:13:09</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>24</v>
+      </c>
+      <c r="F44" t="n">
+        <v>77726.4140625</v>
       </c>
     </row>
   </sheetData>
@@ -2064,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4662,6 +4700,24 @@
           <t>78245.554688,78188.515625,78233.726562,78298.851562,78278.960938,78274.859375,78299.375000,78293.296875,78298.960938,78301.242188,78267.867188,78311.781250,78293.109375,78237.000000,78296.265625,78287.726562,78322.765625,78225.117188,78220.906250,78254.710938,78282.109375,78205.148438,78192.156250,78234.015625</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>78275.093750,78103.023438,78065.203125,77992.140625,78144.937500,78163.406250,78746.820312,78849.773438,78778.398438,78821.687500,79331.679688,79011.742188,79028.046875,78856.109375,78582.296875,78646.773438,78425.960938,77683.500000,77921.523438,77632.203125,77453.578125,77744.828125,77603.898438,77719.992188</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>29.539062,85.492188,168.523437,306.710937,134.023438,111.453125,447.445312,556.476562,479.437499,520.445312,1063.812499,699.960938,734.937500,619.109375,286.031250,359.046876,103.195312,541.617188,299.382812,622.507813,828.531250,460.320313,588.257812,514.023438</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0.037737,0.109461,0.215875,0.393259,0.171506,0.142590,0.568207,0.705743,0.608590,0.660282,1.340968,0.885895,0.929970,0.785113,0.363989,0.456531,0.131583,0.697210,0.384211,0.801868,1.069713,0.592091,0.758026,0.661379</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0.5613249294717828</v>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>78232.882812,78191.726562,78139.375000,78244.414062,78340.453125,78227.585938,78295.296875,78314.367188,78289.703125,78277.695312,78311.976562,78206.187500,78196.179688,78301.695312,78267.992188,78112.335938,78199.609375,78095.703125,78211.296875,78100.968750,78171.359375,77963.109375,78188.984375,78093.703125</t>
@@ -4675,6 +4731,49 @@
       <c r="M43" t="inlineStr">
         <is>
           <t>78076.671875,77980.656250,78004.492188,78050.046875,77965.570312,77912.062500,77922.781250,77914.539062,77955.398438,77881.109375,77822.960938,77875.914062,77867.359375,77696.570312,77758.914062,77727.125000,77713.414062,77602.046875,77520.601562,77562.835938,77510.500000,77399.109375,77377.179688,77427.796875</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-31 05:13:09</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>24</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>77780.851562,77751.546875,77732.992188,77778.875000,77731.515625,77761.914062,77776.484375,77759.296875,77764.906250,77776.539062,77747.445312,77791.156250,77779.398438,77716.062500,77748.515625,77718.859375,77780.046875,77715.437500,77711.875000,77717.968750,77713.046875,77712.039062,77691.750000,77726.414062</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>77760.039062,77711.148438,77633.375000,77749.367188,77797.187500,77710.296875,77725.109375,77685.710938,77670.179688,77710.085938,77742.960938,77705.515625,77635.570312,77725.265625,77642.523438,77484.414062,77641.234375,77550.687500,77670.507812,77504.765625,77563.148438,77409.125000,77639.406250,77591.312500</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>77383.546875,77323.929688,77224.765625,77295.890625,77126.460938,77079.273438,77051.226562,76965.031250,76886.914062,76877.554688,76815.781250,76800.812500,76756.359375,76631.851562,76595.398438,76518.625000,76549.953125,76452.546875,76297.914062,76196.554688,76191.687500,76160.265625,76119.718750,76125.117188</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>77600.171875,77498.679688,77431.468750,77490.703125,77367.960938,77316.289062,77309.929688,77254.593750,77275.875000,77253.375000,77177.945312,77226.453125,77205.375000,77022.390625,77053.562500,77007.914062,77041.390625,76944.312500,76856.773438,76864.664062,76805.210938,76774.226562,76754.078125,76794.609375</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2089,6 +2089,44 @@
       </c>
       <c r="F44" t="n">
         <v>77726.4140625</v>
+      </c>
+      <c r="G44" t="n">
+        <v>78741.1484375</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1014.734375</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1.288696437803972</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.007685948787414</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-01 04:48:56</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>24</v>
+      </c>
+      <c r="F45" t="n">
+        <v>78631.984375</v>
       </c>
     </row>
   </sheetData>
@@ -2102,7 +2140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4761,6 +4799,24 @@
           <t>77780.851562,77751.546875,77732.992188,77778.875000,77731.515625,77761.914062,77776.484375,77759.296875,77764.906250,77776.539062,77747.445312,77791.156250,77779.398438,77716.062500,77748.515625,77718.859375,77780.046875,77715.437500,77711.875000,77717.968750,77713.046875,77712.039062,77691.750000,77726.414062</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>78083.523438,78178.976562,78459.796875,78493.312500,78675.617188,78286.968750,77913.421875,77837.398438,78548.523438,78559.078125,78616.601562,78888.593750,79003.953125,78878.859375,78842.687500,78944.773438,78568.328125,78562.726562,78628.031250,78377.171875,78422.460938,78653.929688,78741.148438,78741.148438</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>302.671876,427.429688,726.804687,714.437500,944.101562,525.054688,136.937500,78.101562,783.617188,782.539063,869.156251,1097.437500,1224.554687,1162.796875,1094.171875,1225.914062,788.281250,847.289062,916.156250,659.203125,709.414062,941.890626,1049.398438,1014.734376</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>0.387626,0.546732,0.926340,0.910189,1.199993,0.670680,0.175756,0.100339,0.997622,0.996115,1.105563,1.391123,1.549992,1.474155,1.387791,1.552876,1.003307,1.078487,1.165178,0.841065,0.904606,1.197512,1.332719,1.288696</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>1.007685948787414</v>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>77760.039062,77711.148438,77633.375000,77749.367188,77797.187500,77710.296875,77725.109375,77685.710938,77670.179688,77710.085938,77742.960938,77705.515625,77635.570312,77725.265625,77642.523438,77484.414062,77641.234375,77550.687500,77670.507812,77504.765625,77563.148438,77409.125000,77639.406250,77591.312500</t>
@@ -4774,6 +4830,49 @@
       <c r="M44" t="inlineStr">
         <is>
           <t>77600.171875,77498.679688,77431.468750,77490.703125,77367.960938,77316.289062,77309.929688,77254.593750,77275.875000,77253.375000,77177.945312,77226.453125,77205.375000,77022.390625,77053.562500,77007.914062,77041.390625,76944.312500,76856.773438,76864.664062,76805.210938,76774.226562,76754.078125,76794.609375</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-01 04:48:56</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>24</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>78789.484375,78772.117188,78753.195312,78807.976562,78782.984375,78795.039062,78778.968750,78757.203125,78759.726562,78754.859375,78713.656250,78739.703125,78732.382812,78674.796875,78728.039062,78689.210938,78726.328125,78675.921875,78655.804688,78667.609375,78632.429688,78618.843750,78605.367188,78631.984375</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>78745.664062,78742.484375,78699.992188,78762.437500,78841.484375,78706.765625,78725.015625,78725.468750,78633.062500,78652.703125,78634.164062,78564.289062,78559.453125,78670.632812,78579.609375,78441.703125,78541.593750,78485.187500,78530.671875,78437.070312,78463.781250,78337.523438,78418.687500,78417.710938</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>78363.781250,78311.640625,78243.367188,78357.023438,78209.351562,78184.625000,78136.085938,78063.578125,77976.531250,77934.937500,77838.851562,77850.320312,77809.898438,77662.695312,77633.757812,77540.828125,77515.156250,77448.625000,77308.390625,77261.359375,77208.375000,77154.359375,77131.578125,77122.531250</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>78592.929688,78504.359375,78465.171875,78519.101562,78438.703125,78381.718750,78362.554688,78297.820312,78345.726562,78293.281250,78194.484375,78227.796875,78225.843750,78057.789062,78103.453125,78038.632812,78075.304688,77977.117188,77914.226562,77914.656250,77861.648438,77768.507812,77770.914062,77797.703125</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2127,6 +2127,44 @@
       </c>
       <c r="F45" t="n">
         <v>78631.984375</v>
+      </c>
+      <c r="G45" t="n">
+        <v>77327.390625</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1304.59375</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1.687104322873949</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.352281042412974</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-02 04:10:06</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>24</v>
+      </c>
+      <c r="F46" t="n">
+        <v>77322.9921875</v>
       </c>
     </row>
   </sheetData>
@@ -2140,7 +2178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4860,6 +4898,24 @@
           <t>78789.484375,78772.117188,78753.195312,78807.976562,78782.984375,78795.039062,78778.968750,78757.203125,78759.726562,78754.859375,78713.656250,78739.703125,78732.382812,78674.796875,78728.039062,78689.210938,78726.328125,78675.921875,78655.804688,78667.609375,78632.429688,78618.843750,78605.367188,78631.984375</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>79136.062500,78708.718750,78609.921875,77858.359375,77893.242188,77989.078125,78061.710938,77968.976562,78041.093750,78139.750000,77881.429688,77565.437500,77238.203125,77126.929688,77267.890625,77403.812500,77165.929688,77224.976562,77258.843750,77171.562500,76965.726562,77277.156250,77512.453125,77327.390625</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>346.578125,63.398438,143.273437,949.617187,889.742188,805.960937,717.257812,788.226562,718.632812,615.109375,832.226562,1174.265625,1494.179687,1547.867188,1460.148437,1285.398438,1560.398438,1450.945312,1396.960938,1496.046875,1666.703126,1341.687500,1092.914063,1304.593750</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0.437952,0.080548,0.182259,1.219673,1.142259,1.033428,0.918834,1.010949,0.920839,0.787191,1.068582,1.513903,1.934509,2.006909,1.889722,1.660640,2.022134,1.878855,1.808157,1.938599,2.165513,1.736202,1.409985,1.687104</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>1.352281042412974</v>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>78745.664062,78742.484375,78699.992188,78762.437500,78841.484375,78706.765625,78725.015625,78725.468750,78633.062500,78652.703125,78634.164062,78564.289062,78559.453125,78670.632812,78579.609375,78441.703125,78541.593750,78485.187500,78530.671875,78437.070312,78463.781250,78337.523438,78418.687500,78417.710938</t>
@@ -4873,6 +4929,49 @@
       <c r="M45" t="inlineStr">
         <is>
           <t>78592.929688,78504.359375,78465.171875,78519.101562,78438.703125,78381.718750,78362.554688,78297.820312,78345.726562,78293.281250,78194.484375,78227.796875,78225.843750,78057.789062,78103.453125,78038.632812,78075.304688,77977.117188,77914.226562,77914.656250,77861.648438,77768.507812,77770.914062,77797.703125</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-02 04:10:06</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>24</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>77289.835938,77263.398438,77253.562500,77312.218750,77269.812500,77292.617188,77298.359375,77270.421875,77283.039062,77297.937500,77287.140625,77330.484375,77307.734375,77266.171875,77310.000000,77278.601562,77283.820312,77245.093750,77258.273438,77273.523438,77308.242188,77301.921875,77277.750000,77322.992188</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>77230.429688,77283.375000,77160.570312,77286.781250,77308.984375,77248.445312,77252.218750,77188.023438,77263.023438,77243.742188,77201.671875,77278.140625,77221.218750,77302.882812,77217.093750,76988.539062,77138.632812,77137.312500,77217.328125,77085.015625,77186.203125,77015.554688,77143.460938,77206.757812</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>76918.000000,76840.093750,76749.007812,76853.117188,76654.648438,76605.609375,76635.328125,76552.828125,76396.710938,76357.093750,76283.000000,76353.992188,76278.023438,76114.617188,76119.273438,76006.421875,75988.648438,75880.671875,75808.335938,75796.882812,75795.125000,75751.234375,75711.023438,75693.203125</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>77110.015625,76981.281250,76975.218750,76967.984375,76878.390625,76843.734375,76829.671875,76752.210938,76810.921875,76750.617188,76688.375000,76722.187500,76713.125000,76572.335938,76658.195312,76546.757812,76561.867188,76417.382812,76430.320312,76452.679688,76467.328125,76381.507812,76369.664062,76413.421875</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2165,6 +2165,44 @@
       </c>
       <c r="F46" t="n">
         <v>77322.9921875</v>
+      </c>
+      <c r="G46" t="n">
+        <v>77724.03125</v>
+      </c>
+      <c r="H46" t="n">
+        <v>401.0390625</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.5159782065472833</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.3525163567214936</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-03 04:07:04</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>24</v>
+      </c>
+      <c r="F47" t="n">
+        <v>77603.6875</v>
       </c>
     </row>
   </sheetData>
@@ -2178,7 +2216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4959,6 +4997,24 @@
           <t>77289.835938,77263.398438,77253.562500,77312.218750,77269.812500,77292.617188,77298.359375,77270.421875,77283.039062,77297.937500,77287.140625,77330.484375,77307.734375,77266.171875,77310.000000,77278.601562,77283.820312,77245.093750,77258.273438,77273.523438,77308.242188,77301.921875,77277.750000,77322.992188</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>77605.398438,77573.687500,77436.242188,76802.007812,76711.070312,76638.812500,76778.492188,76567.937500,77112.640625,77025.328125,77253.039062,77139.937500,77351.460938,77348.281250,77324.640625,77378.109375,77264.906250,77003.601562,77316.101562,77027.843750,77323.523438,77786.976562,77673.960938,77724.031250</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>315.562499,310.289062,182.679688,510.210938,558.742188,653.804688,519.867188,702.484375,170.398437,272.609375,34.101562,190.546875,43.726562,82.109375,14.640625,99.507813,18.914062,241.492188,57.828124,245.679688,15.281249,485.054688,396.210938,401.039062</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0.406624,0.399993,0.235910,0.664320,0.728372,0.853099,0.677100,0.917465,0.220973,0.353922,0.044143,0.247015,0.056530,0.106155,0.018934,0.128599,0.024479,0.313612,0.074794,0.318949,0.019763,0.623568,0.510095,0.515978</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0.3525163567214936</v>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>77230.429688,77283.375000,77160.570312,77286.781250,77308.984375,77248.445312,77252.218750,77188.023438,77263.023438,77243.742188,77201.671875,77278.140625,77221.218750,77302.882812,77217.093750,76988.539062,77138.632812,77137.312500,77217.328125,77085.015625,77186.203125,77015.554688,77143.460938,77206.757812</t>
@@ -4972,6 +5028,49 @@
       <c r="M46" t="inlineStr">
         <is>
           <t>77110.015625,76981.281250,76975.218750,76967.984375,76878.390625,76843.734375,76829.671875,76752.210938,76810.921875,76750.617188,76688.375000,76722.187500,76713.125000,76572.335938,76658.195312,76546.757812,76561.867188,76417.382812,76430.320312,76452.679688,76467.328125,76381.507812,76369.664062,76413.421875</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-03 04:07:04</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>24</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>77807.226562,77800.703125,77780.093750,77824.445312,77761.039062,77762.421875,77755.242188,77746.437500,77738.351562,77722.921875,77675.046875,77720.601562,77695.000000,77682.609375,77693.648438,77667.281250,77670.773438,77589.257812,77610.375000,77560.492188,77569.796875,77567.335938,77528.210938,77603.687500</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>77677.164062,77722.132812,77701.078125,77696.007812,77711.875000,77687.156250,77625.125000,77653.289062,77625.851562,77676.562500,77565.140625,77600.070312,77567.578125,77611.750000,77545.218750,77454.281250,77439.070312,77471.015625,77463.875000,77355.960938,77437.289062,77309.523438,77358.046875,77465.648438</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>77328.218750,77262.335938,77134.015625,77205.164062,77013.234375,76911.734375,76920.804688,76886.437500,76735.242188,76647.375000,76548.992188,76626.226562,76552.765625,76456.578125,76437.234375,76363.195312,76387.109375,76253.835938,76160.648438,76065.375000,76067.914062,76021.109375,75979.695312,76014.468750</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>77577.390625,77448.250000,77444.023438,77393.695312,77298.195312,77203.218750,77187.296875,77146.687500,77197.609375,77094.375000,77006.570312,77027.976562,77026.625000,76932.281250,76972.375000,76912.843750,76938.789062,76758.023438,76774.812500,76737.531250,76739.531250,76620.906250,76613.828125,76702.398438</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2203,6 +2203,44 @@
       </c>
       <c r="F47" t="n">
         <v>77603.6875</v>
+      </c>
+      <c r="G47" t="n">
+        <v>80872.6484375</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3268.9609375</v>
+      </c>
+      <c r="I47" t="n">
+        <v>4.042109416048515</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.828447045103614</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-04 04:12:44</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>24</v>
+      </c>
+      <c r="F48" t="n">
+        <v>80215.765625</v>
       </c>
     </row>
   </sheetData>
@@ -2216,7 +2254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5058,6 +5096,24 @@
           <t>77807.226562,77800.703125,77780.093750,77824.445312,77761.039062,77762.421875,77755.242188,77746.437500,77738.351562,77722.921875,77675.046875,77720.601562,77695.000000,77682.609375,77693.648438,77667.281250,77670.773438,77589.257812,77610.375000,77560.492188,77569.796875,77567.335938,77528.210938,77603.687500</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>77781.093750,77797.992188,77621.710938,77803.132812,77572.937500,77708.609375,77910.273438,78621.289062,78815.742188,80550.007812,81358.210938,80973.953125,81052.492188,81268.421875,81760.179688,81482.851562,81626.632812,81155.570312,81270.828125,80977.312500,80975.296875,80830.476562,80850.500000,80872.648438</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>26.132812,2.710938,158.382812,21.312499,188.101562,53.812500,155.031249,874.851562,1077.390626,2827.085938,3683.164062,3253.351563,3357.492188,3585.812500,4066.531249,3815.570312,3955.859374,3566.312501,3660.453125,3416.820312,3405.500000,3263.140624,3322.289062,3268.960938</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.033598,0.003485,0.204044,0.027393,0.242483,0.069249,0.198987,1.112741,1.366974,3.509728,4.527096,4.017775,4.142368,4.412307,4.973731,4.682667,4.846285,4.394415,4.504018,4.219479,4.205604,4.037018,4.109176,4.042109</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>2.828447045103614</v>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>77677.164062,77722.132812,77701.078125,77696.007812,77711.875000,77687.156250,77625.125000,77653.289062,77625.851562,77676.562500,77565.140625,77600.070312,77567.578125,77611.750000,77545.218750,77454.281250,77439.070312,77471.015625,77463.875000,77355.960938,77437.289062,77309.523438,77358.046875,77465.648438</t>
@@ -5071,6 +5127,49 @@
       <c r="M47" t="inlineStr">
         <is>
           <t>77577.390625,77448.250000,77444.023438,77393.695312,77298.195312,77203.218750,77187.296875,77146.687500,77197.609375,77094.375000,77006.570312,77027.976562,77026.625000,76932.281250,76972.375000,76912.843750,76938.789062,76758.023438,76774.812500,76737.531250,76739.531250,76620.906250,76613.828125,76702.398438</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-04 04:12:44</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>24</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>80958.320312,80927.390625,80931.445312,80961.250000,80850.695312,80812.921875,80790.242188,80780.585938,80742.671875,80714.789062,80699.054688,80678.343750,80590.789062,80516.343750,80564.132812,80513.375000,80499.382812,80387.132812,80348.421875,80287.484375,80204.859375,80218.453125,80203.851562,80215.765625</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>80811.757812,80833.156250,80835.000000,80750.242188,80735.757812,80656.015625,80597.148438,80625.890625,80509.742188,80563.351562,80519.742188,80484.664062,80330.250000,80393.500000,80330.382812,80210.070312,80259.593750,80048.062500,80023.046875,79975.226562,80011.187500,80016.328125,79841.656250,79898.218750</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>80525.328125,80454.882812,80244.406250,80228.523438,80010.671875,79791.593750,79663.445312,79634.023438,79435.921875,79308.632812,79146.789062,79100.187500,78985.820312,78852.328125,78799.656250,78702.109375,78649.023438,78475.531250,78313.101562,78164.437500,78024.156250,78079.734375,78035.851562,78006.734375</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>80792.554688,80660.664062,80611.046875,80567.710938,80356.140625,80179.765625,80112.976562,80041.429688,80036.023438,79938.109375,79826.093750,79729.570312,79658.109375,79496.835938,79521.289062,79486.453125,79429.203125,79241.375000,79172.070312,79100.179688,79000.796875,78885.414062,78917.828125,78973.531250</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2241,6 +2241,44 @@
       </c>
       <c r="F48" t="n">
         <v>80215.765625</v>
+      </c>
+      <c r="G48" t="n">
+        <v>79585.78125</v>
+      </c>
+      <c r="H48" t="n">
+        <v>629.984375</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.7915790548327375</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.9106181733249039</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-05 04:08:41</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>24</v>
+      </c>
+      <c r="F49" t="n">
+        <v>79367.2578125</v>
       </c>
     </row>
   </sheetData>
@@ -2254,7 +2292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5157,6 +5195,24 @@
           <t>80958.320312,80927.390625,80931.445312,80961.250000,80850.695312,80812.921875,80790.242188,80780.585938,80742.671875,80714.789062,80699.054688,80678.343750,80590.789062,80516.343750,80564.132812,80513.375000,80499.382812,80387.132812,80348.421875,80287.484375,80204.859375,80218.453125,80203.851562,80215.765625</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>80983.203125,80792.000000,80650.843750,81140.007812,81045.210938,81179.093750,81219.593750,79434.609375,79363.000000,78894.648438,79422.953125,79747.968750,79469.851562,79617.921875,79812.523438,79723.476562,79654.117188,79654.101562,79675.117188,79584.007812,79551.007812,79584.500000,79596.273438,79585.781250</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>24.882813,135.390625,280.601562,178.757812,194.515626,366.171875,429.351562,1345.976563,1379.671875,1820.140624,1276.101563,930.375000,1120.937499,898.421875,751.609374,789.898438,845.265624,733.031249,673.304688,703.476562,653.851562,633.953125,607.578124,629.984375</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.030726,0.167579,0.347921,0.220308,0.240009,0.451067,0.528631,1.694446,1.738432,2.307052,1.606716,1.166644,1.410519,1.128417,0.941719,0.990798,1.061170,0.920268,0.845063,0.883942,0.821927,0.796579,0.763325,0.791579</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>0.9106181733249039</v>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>80811.757812,80833.156250,80835.000000,80750.242188,80735.757812,80656.015625,80597.148438,80625.890625,80509.742188,80563.351562,80519.742188,80484.664062,80330.250000,80393.500000,80330.382812,80210.070312,80259.593750,80048.062500,80023.046875,79975.226562,80011.187500,80016.328125,79841.656250,79898.218750</t>
@@ -5170,6 +5226,49 @@
       <c r="M48" t="inlineStr">
         <is>
           <t>80792.554688,80660.664062,80611.046875,80567.710938,80356.140625,80179.765625,80112.976562,80041.429688,80036.023438,79938.109375,79826.093750,79729.570312,79658.109375,79496.835938,79521.289062,79486.453125,79429.203125,79241.375000,79172.070312,79100.179688,79000.796875,78885.414062,78917.828125,78973.531250</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-05 04:08:41</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>24</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>79626.468750,79619.507812,79629.156250,79695.234375,79599.609375,79589.125000,79573.898438,79567.046875,79561.140625,79511.250000,79494.554688,79513.648438,79445.156250,79398.406250,79476.265625,79469.257812,79496.039062,79418.929688,79422.437500,79390.468750,79356.367188,79381.460938,79342.023438,79367.257812</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>79530.843750,79590.671875,79476.750000,79588.039062,79571.062500,79458.101562,79428.703125,79386.359375,79375.734375,79460.031250,79280.000000,79313.000000,79223.273438,79306.289062,79177.054688,79230.468750,79220.281250,79138.328125,79182.281250,79135.953125,79113.804688,79109.859375,79003.695312,79037.179688</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>79191.828125,79132.617188,79022.867188,79119.484375,78843.507812,78757.562500,78637.093750,78566.718750,78410.109375,78258.531250,78105.875000,78166.257812,77972.703125,77843.687500,77850.382812,77773.859375,77722.945312,77624.429688,77455.265625,77347.671875,77237.375000,77280.625000,77199.734375,77158.250000</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>79425.515625,79291.359375,79327.210938,79313.796875,79140.882812,79054.171875,78932.484375,78870.906250,78911.906250,78800.218750,78699.250000,78624.078125,78567.593750,78423.140625,78492.687500,78464.460938,78448.109375,78312.046875,78266.640625,78251.257812,78182.125000,78080.906250,78078.796875,78119.007812</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2279,6 +2279,44 @@
       </c>
       <c r="F49" t="n">
         <v>79367.2578125</v>
+      </c>
+      <c r="G49" t="n">
+        <v>79975.1484375</v>
+      </c>
+      <c r="H49" t="n">
+        <v>607.890625</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.7600994019724292</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.3902423254404612</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-06 04:16:31</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>24</v>
+      </c>
+      <c r="F50" t="n">
+        <v>79770.4921875</v>
       </c>
     </row>
   </sheetData>
@@ -2292,7 +2330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5256,6 +5294,24 @@
           <t>79626.468750,79619.507812,79629.156250,79695.234375,79599.609375,79589.125000,79573.898438,79567.046875,79561.140625,79511.250000,79494.554688,79513.648438,79445.156250,79398.406250,79476.265625,79469.257812,79496.039062,79418.929688,79422.437500,79390.468750,79356.367188,79381.460938,79342.023438,79367.257812</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>79590.320312,79660.000000,79726.796875,79653.296875,79634.992188,79621.140625,79621.921875,79710.726562,79624.507812,79723.187500,79802.007812,80040.531250,80072.187500,80000.031250,79753.210938,79740.078125,79910.343750,79790.367188,79856.648438,79872.242188,79954.320312,79906.812500,80031.867188,79975.148438</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>36.148438,40.492188,97.640625,41.937500,35.382812,32.015625,48.023437,143.679688,63.367188,211.937500,307.453124,526.882812,627.031250,601.625000,276.945312,270.820313,414.304688,371.437499,434.210938,481.773438,597.953124,525.351562,689.843749,607.890626</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.045418,0.050831,0.122469,0.052650,0.044431,0.040210,0.060314,0.180251,0.079583,0.265842,0.385270,0.658270,0.783082,0.752031,0.347253,0.339629,0.518462,0.465517,0.543738,0.603180,0.747868,0.657455,0.861961,0.760099</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0.3902423254404612</v>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>79530.843750,79590.671875,79476.750000,79588.039062,79571.062500,79458.101562,79428.703125,79386.359375,79375.734375,79460.031250,79280.000000,79313.000000,79223.273438,79306.289062,79177.054688,79230.468750,79220.281250,79138.328125,79182.281250,79135.953125,79113.804688,79109.859375,79003.695312,79037.179688</t>
@@ -5269,6 +5325,49 @@
       <c r="M49" t="inlineStr">
         <is>
           <t>79425.515625,79291.359375,79327.210938,79313.796875,79140.882812,79054.171875,78932.484375,78870.906250,78911.906250,78800.218750,78699.250000,78624.078125,78567.593750,78423.140625,78492.687500,78464.460938,78448.109375,78312.046875,78266.640625,78251.257812,78182.125000,78080.906250,78078.796875,78119.007812</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-06 04:16:31</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>24</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>79940.125000,79933.359375,79926.054688,79966.742188,79905.164062,79908.398438,79915.117188,79855.906250,79888.570312,79889.804688,79847.390625,79903.015625,79848.578125,79824.554688,79860.656250,79871.976562,79871.453125,79793.359375,79801.632812,79789.476562,79764.898438,79778.031250,79744.953125,79770.492188</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>79821.429688,79925.585938,79830.718750,79828.382812,79955.867188,79817.976562,79814.523438,79770.179688,79745.757812,79834.851562,79745.679688,79778.500000,79699.687500,79742.687500,79674.117188,79682.468750,79659.976562,79578.101562,79636.851562,79531.609375,79558.976562,79537.343750,79500.250000,79510.992188</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>79593.187500,79582.906250,79516.195312,79603.000000,79465.750000,79427.250000,79354.820312,79228.718750,79124.953125,79084.414062,78935.671875,78994.156250,78803.781250,78869.929688,78825.382812,78808.265625,78757.101562,78665.835938,78510.820312,78442.789062,78431.164062,78461.515625,78387.335938,78354.203125</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>79787.851562,79716.382812,79726.226562,79755.640625,79643.554688,79589.492188,79541.523438,79497.757812,79501.609375,79471.921875,79342.601562,79397.164062,79348.562500,79271.625000,79316.789062,79309.070312,79302.218750,79156.718750,79143.843750,79128.843750,79088.484375,79057.164062,79017.164062,79066.296875</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2317,6 +2317,44 @@
       </c>
       <c r="F50" t="n">
         <v>79770.4921875</v>
+      </c>
+      <c r="G50" t="n">
+        <v>79675.96875</v>
+      </c>
+      <c r="H50" t="n">
+        <v>94.5234375</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.1186348142142922</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.1770269804491108</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-07 04:15:51</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>24</v>
+      </c>
+      <c r="F51" t="n">
+        <v>79513.2265625</v>
       </c>
     </row>
   </sheetData>
@@ -2330,7 +2368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5355,6 +5393,24 @@
           <t>79940.125000,79933.359375,79926.054688,79966.742188,79905.164062,79908.398438,79915.117188,79855.906250,79888.570312,79889.804688,79847.390625,79903.015625,79848.578125,79824.554688,79860.656250,79871.976562,79871.453125,79793.359375,79801.632812,79789.476562,79764.898438,79778.031250,79744.953125,79770.492188</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>79989.687500,79771.828125,79810.062500,79845.000000,79890.476562,80000.617188,79922.992188,79920.460938,79832.992188,79538.492188,79707.648438,79679.218750,79741.187500,79941.882812,79829.976562,79892.257812,79945.156250,80048.742188,80339.320312,80148.007812,79923.046875,79863.429688,79587.312500,79675.968750</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>49.562500,161.531250,115.992188,121.742188,14.687499,92.218749,7.874999,64.554688,55.578124,351.312501,139.742188,223.796875,107.390625,117.328124,30.679688,20.281251,73.703125,255.382812,537.687501,358.531251,158.148437,85.398438,157.640625,94.523438</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.061961,0.202492,0.145335,0.152473,0.018385,0.115273,0.009853,0.080774,0.069618,0.441689,0.175318,0.280872,0.134674,0.146767,0.038431,0.025386,0.092192,0.319034,0.669271,0.447336,0.197876,0.106931,0.198073,0.118635</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0.1770269804491108</v>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>79821.429688,79925.585938,79830.718750,79828.382812,79955.867188,79817.976562,79814.523438,79770.179688,79745.757812,79834.851562,79745.679688,79778.500000,79699.687500,79742.687500,79674.117188,79682.468750,79659.976562,79578.101562,79636.851562,79531.609375,79558.976562,79537.343750,79500.250000,79510.992188</t>
@@ -5368,6 +5424,49 @@
       <c r="M50" t="inlineStr">
         <is>
           <t>79787.851562,79716.382812,79726.226562,79755.640625,79643.554688,79589.492188,79541.523438,79497.757812,79501.609375,79471.921875,79342.601562,79397.164062,79348.562500,79271.625000,79316.789062,79309.070312,79302.218750,79156.718750,79143.843750,79128.843750,79088.484375,79057.164062,79017.164062,79066.296875</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-07 04:15:51</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>24</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>79737.992188,79725.953125,79706.015625,79766.843750,79680.117188,79707.656250,79692.250000,79659.445312,79684.992188,79657.734375,79603.375000,79638.203125,79587.914062,79575.476562,79604.054688,79595.601562,79637.703125,79557.085938,79594.757812,79551.359375,79559.757812,79545.906250,79498.921875,79513.226562</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>79620.765625,79629.867188,79611.109375,79669.007812,79688.953125,79631.515625,79567.437500,79560.671875,79529.601562,79540.625000,79530.054688,79505.109375,79424.851562,79431.640625,79397.945312,79361.226562,79314.000000,79367.859375,79406.203125,79221.234375,79313.437500,79237.460938,79220.140625,79239.460938</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>79388.539062,79392.750000,79268.523438,79365.570312,79205.218750,79153.523438,79089.093750,78987.179688,78887.210938,78807.757812,78610.789062,78645.578125,78540.750000,78597.437500,78490.437500,78465.492188,78440.859375,78333.710938,78216.296875,78156.531250,78168.585938,78195.656250,78089.617188,78069.421875</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>79603.125000,79515.656250,79487.640625,79528.023438,79381.265625,79350.937500,79298.492188,79276.671875,79306.359375,79231.867188,79031.093750,79082.984375,79067.867188,79009.093750,79001.164062,78999.695312,79010.507812,78843.242188,78878.078125,78849.390625,78857.773438,78770.765625,78729.492188,78777.046875</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2355,6 +2355,44 @@
       </c>
       <c r="F51" t="n">
         <v>79513.2265625</v>
+      </c>
+      <c r="G51" t="n">
+        <v>78765.96875</v>
+      </c>
+      <c r="H51" t="n">
+        <v>747.2578125</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.9487064329415741</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.5026311980478135</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-08 04:16:35</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>24</v>
+      </c>
+      <c r="F52" t="n">
+        <v>78688.03125</v>
       </c>
     </row>
   </sheetData>
@@ -2368,7 +2406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5454,6 +5492,24 @@
           <t>79737.992188,79725.953125,79706.015625,79766.843750,79680.117188,79707.656250,79692.250000,79659.445312,79684.992188,79657.734375,79603.375000,79638.203125,79587.914062,79575.476562,79604.054688,79595.601562,79637.703125,79557.085938,79594.757812,79551.359375,79559.757812,79545.906250,79498.921875,79513.226562</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>79740.210938,79645.507812,79379.937500,79417.851562,79301.312500,79350.648438,79409.132812,79597.757812,79344.843750,79184.132812,78800.000000,79010.976562,79170.000000,79195.023438,79352.210938,79220.539062,79139.492188,78929.929688,79091.968750,79293.382812,79413.921875,78914.562500,78875.218750,78765.968750</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2.218749,80.445312,326.078125,348.992188,378.804688,357.007812,283.117188,61.687499,340.148438,473.601562,803.375000,627.226562,417.914062,380.453124,251.843751,375.062499,498.210938,627.156251,502.789062,257.976562,145.835937,631.343750,623.703125,747.257812</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.002782,0.101004,0.410782,0.439438,0.477678,0.449912,0.356530,0.077499,0.428696,0.598102,1.019511,0.793847,0.527869,0.480400,0.317375,0.473441,0.629535,0.794573,0.635702,0.325344,0.183640,0.800035,0.790747,0.948706</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0.5026311980478135</v>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>79620.765625,79629.867188,79611.109375,79669.007812,79688.953125,79631.515625,79567.437500,79560.671875,79529.601562,79540.625000,79530.054688,79505.109375,79424.851562,79431.640625,79397.945312,79361.226562,79314.000000,79367.859375,79406.203125,79221.234375,79313.437500,79237.460938,79220.140625,79239.460938</t>
@@ -5467,6 +5523,49 @@
       <c r="M51" t="inlineStr">
         <is>
           <t>79603.125000,79515.656250,79487.640625,79528.023438,79381.265625,79350.937500,79298.492188,79276.671875,79306.359375,79231.867188,79031.093750,79082.984375,79067.867188,79009.093750,79001.164062,78999.695312,79010.507812,78843.242188,78878.078125,78849.390625,78857.773438,78770.765625,78729.492188,78777.046875</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-08 04:16:35</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>24</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>78786.390625,78752.203125,78723.546875,78784.507812,78707.953125,78737.070312,78738.960938,78724.031250,78745.000000,78748.078125,78705.484375,78702.242188,78671.429688,78679.914062,78720.750000,78696.023438,78734.500000,78669.718750,78741.734375,78674.601562,78710.859375,78722.773438,78671.273438,78688.031250</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>78633.750000,78671.054688,78661.210938,78715.937500,78795.695312,78688.656250,78690.429688,78621.101562,78598.218750,78673.921875,78597.406250,78555.898438,78549.601562,78598.640625,78561.500000,78494.726562,78523.101562,78535.421875,78588.359375,78466.828125,78548.304688,78466.421875,78350.242188,78489.648438</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>78478.304688,78415.890625,78287.164062,78362.632812,78176.937500,78130.109375,78075.828125,78019.632812,77920.328125,77883.265625,77705.914062,77690.812500,77589.859375,77655.921875,77586.671875,77553.781250,77506.226562,77417.945312,77304.093750,77269.703125,77317.109375,77344.500000,77243.250000,77234.226562</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>78646.148438,78523.382812,78479.273438,78493.875000,78341.171875,78310.406250,78258.273438,78267.617188,78332.968750,78265.304688,78100.734375,78066.695312,78052.500000,78026.953125,78036.601562,78023.164062,78053.890625,77866.421875,77934.390625,77909.070312,77947.132812,77872.781250,77827.578125,77848.156250</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2393,6 +2393,44 @@
       </c>
       <c r="F52" t="n">
         <v>78688.03125</v>
+      </c>
+      <c r="G52" t="n">
+        <v>78859.1015625</v>
+      </c>
+      <c r="H52" t="n">
+        <v>171.0703125</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.2169316021999284</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.2954457499524332</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-09 04:23:13</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>24</v>
+      </c>
+      <c r="F53" t="n">
+        <v>78710.2578125</v>
       </c>
     </row>
   </sheetData>
@@ -2406,7 +2444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5553,6 +5591,24 @@
           <t>78786.390625,78752.203125,78723.546875,78784.507812,78707.953125,78737.070312,78738.960938,78724.031250,78745.000000,78748.078125,78705.484375,78702.242188,78671.429688,78679.914062,78720.750000,78696.023438,78734.500000,78669.718750,78741.734375,78674.601562,78710.859375,78722.773438,78671.273438,78688.031250</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>78556.789062,78299.281250,78451.078125,78380.617188,78732.882812,78540.367188,78401.882812,78414.218750,77933.046875,78537.726562,78899.992188,78730.820312,78493.179688,78423.593750,78437.101562,78482.453125,78485.851562,78545.406250,78446.882812,78765.500000,78879.703125,78717.171875,78619.710938,78859.101562</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>229.601562,452.921875,272.468750,403.890624,24.929688,196.703124,337.078126,309.812500,811.953125,210.351562,194.507812,28.578124,178.250001,256.320312,283.648438,213.570313,248.648438,124.312500,294.851562,90.898438,168.843750,5.601563,51.562501,171.070312</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.292275,0.578450,0.347310,0.515294,0.031664,0.250448,0.429936,0.395097,1.041860,0.267835,0.246525,0.036299,0.227090,0.326841,0.361625,0.272125,0.316807,0.158268,0.375861,0.115404,0.214052,0.007116,0.065585,0.216932</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0.2954457499524332</v>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>78633.750000,78671.054688,78661.210938,78715.937500,78795.695312,78688.656250,78690.429688,78621.101562,78598.218750,78673.921875,78597.406250,78555.898438,78549.601562,78598.640625,78561.500000,78494.726562,78523.101562,78535.421875,78588.359375,78466.828125,78548.304688,78466.421875,78350.242188,78489.648438</t>
@@ -5566,6 +5622,49 @@
       <c r="M52" t="inlineStr">
         <is>
           <t>78646.148438,78523.382812,78479.273438,78493.875000,78341.171875,78310.406250,78258.273438,78267.617188,78332.968750,78265.304688,78100.734375,78066.695312,78052.500000,78026.953125,78036.601562,78023.164062,78053.890625,77866.421875,77934.390625,77909.070312,77947.132812,77872.781250,77827.578125,77848.156250</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-09 04:23:13</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>24</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>78894.390625,78878.476562,78833.585938,78882.828125,78784.554688,78823.023438,78814.796875,78786.796875,78805.367188,78805.851562,78758.421875,78782.992188,78743.625000,78749.570312,78760.578125,78739.687500,78747.367188,78685.429688,78748.984375,78689.648438,78692.875000,78709.015625,78679.500000,78710.257812</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>78742.656250,78760.921875,78830.265625,78767.898438,78890.593750,78728.164062,78695.882812,78751.343750,78613.554688,78753.765625,78670.617188,78635.343750,78695.101562,78688.625000,78608.250000,78542.703125,78512.210938,78545.304688,78540.570312,78526.710938,78575.593750,78528.695312,78429.218750,78551.914062</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>78509.265625,78475.289062,78294.343750,78351.109375,78172.500000,78159.187500,78114.679688,78056.875000,77967.539062,77925.898438,77747.867188,77794.929688,77720.468750,77809.640625,77751.718750,77697.757812,77631.023438,77556.843750,77430.585938,77429.320312,77460.921875,77509.148438,77457.164062,77459.804688</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>78729.398438,78648.226562,78556.710938,78557.312500,78364.367188,78362.101562,78330.656250,78333.929688,78383.109375,78301.695312,78149.750000,78149.859375,78168.398438,78148.140625,78143.906250,78103.859375,78113.539062,77957.468750,78018.257812,77992.875000,78000.906250,77977.921875,77936.164062,78024.953125</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2431,6 +2431,44 @@
       </c>
       <c r="F53" t="n">
         <v>78710.2578125</v>
+      </c>
+      <c r="G53" t="n">
+        <v>78383.828125</v>
+      </c>
+      <c r="H53" t="n">
+        <v>326.4296875</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.4164503001555846</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.4866749531128341</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-10 04:20:02</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>24</v>
+      </c>
+      <c r="F54" t="n">
+        <v>78409.578125</v>
       </c>
     </row>
   </sheetData>
@@ -2444,7 +2482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5652,6 +5690,24 @@
           <t>78894.390625,78878.476562,78833.585938,78882.828125,78784.554688,78823.023438,78814.796875,78786.796875,78805.367188,78805.851562,78758.421875,78782.992188,78743.625000,78749.570312,78760.578125,78739.687500,78747.367188,78685.429688,78748.984375,78689.648438,78692.875000,78709.015625,78679.500000,78710.257812</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>78921.789062,79150.250000,79258.796875,79695.390625,78940.000000,78901.757812,79294.257812,79580.000000,79119.226562,78941.828125,78576.406250,78783.179688,78754.882812,78399.343750,78211.257812,78303.570312,78124.757812,77897.601562,78248.812500,78151.718750,78070.406250,78326.101562,78297.148438,78383.828125</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>27.398438,271.773438,425.210937,812.562500,155.445312,78.734374,479.460938,793.203125,313.859374,135.976563,182.015625,0.187499,11.257812,350.226562,549.320312,436.117188,622.609376,787.828126,500.171875,537.929688,622.468750,382.914062,382.351562,326.429687</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>0.034716,0.343364,0.536484,1.019585,0.196916,0.099788,0.604660,0.996737,0.396692,0.172249,0.231642,0.000238,0.014295,0.446721,0.702355,0.556957,0.796942,1.011364,0.639207,0.688315,0.797317,0.488872,0.488334,0.416450</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>0.4866749531128341</v>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>78742.656250,78760.921875,78830.265625,78767.898438,78890.593750,78728.164062,78695.882812,78751.343750,78613.554688,78753.765625,78670.617188,78635.343750,78695.101562,78688.625000,78608.250000,78542.703125,78512.210938,78545.304688,78540.570312,78526.710938,78575.593750,78528.695312,78429.218750,78551.914062</t>
@@ -5665,6 +5721,49 @@
       <c r="M53" t="inlineStr">
         <is>
           <t>78729.398438,78648.226562,78556.710938,78557.312500,78364.367188,78362.101562,78330.656250,78333.929688,78383.109375,78301.695312,78149.750000,78149.859375,78168.398438,78148.140625,78143.906250,78103.859375,78113.539062,77957.468750,78018.257812,77992.875000,78000.906250,77977.921875,77936.164062,78024.953125</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-10 04:20:02</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>24</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>78352.812500,78331.406250,78332.953125,78377.242188,78315.671875,78313.437500,78324.382812,78305.648438,78312.382812,78293.429688,78292.828125,78341.937500,78327.937500,78323.101562,78366.343750,78338.156250,78410.789062,78330.773438,78398.187500,78353.953125,78330.671875,78396.671875,78387.265625,78409.578125</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>78232.085938,78272.765625,78291.125000,78296.976562,78361.664062,78312.664062,78269.781250,78276.117188,78167.921875,78372.062500,78296.867188,78261.359375,78327.093750,78340.078125,78351.414062,78215.609375,78289.632812,78224.960938,78326.453125,78254.640625,78343.679688,78254.250000,78273.218750,78297.289062</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>78031.593750,77988.757812,77882.875000,77921.710938,77753.679688,77724.765625,77710.312500,77652.046875,77563.312500,77513.140625,77397.804688,77445.046875,77387.492188,77444.132812,77407.414062,77333.421875,77413.968750,77298.250000,77235.039062,77171.664062,77196.257812,77298.640625,77232.781250,77235.015625</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>78216.054688,78111.781250,78078.031250,78076.859375,77934.750000,77875.468750,77863.125000,77863.375000,77912.625000,77782.148438,77690.195312,77733.773438,77751.531250,77727.773438,77789.203125,77714.375000,77810.289062,77654.265625,77713.640625,77667.265625,77683.710938,77670.445312,77652.445312,77671.242188</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2469,6 +2469,44 @@
       </c>
       <c r="F54" t="n">
         <v>78409.578125</v>
+      </c>
+      <c r="G54" t="n">
+        <v>76939.90625</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1469.671875</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1.910155531285171</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1.323566148624642</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:19:48</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>24</v>
+      </c>
+      <c r="F55" t="n">
+        <v>76902.75</v>
       </c>
     </row>
   </sheetData>
@@ -2482,7 +2520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5751,6 +5789,24 @@
           <t>78352.812500,78331.406250,78332.953125,78377.242188,78315.671875,78313.437500,78324.382812,78305.648438,78312.382812,78293.429688,78292.828125,78341.937500,78327.937500,78323.101562,78366.343750,78338.156250,78410.789062,78330.773438,78398.187500,78353.953125,78330.671875,78396.671875,78387.265625,78409.578125</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>78499.039062,78389.703125,78079.507812,78085.460938,77941.968750,77825.726562,77820.750000,76867.242188,77145.023438,77390.796875,77218.742188,77160.218750,77294.257812,77222.531250,77119.531250,77239.007812,77110.039062,76807.109375,76531.953125,76878.718750,76948.273438,76813.679688,76863.656250,76939.906250</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>146.226562,58.296875,253.445312,291.781251,373.703125,487.710938,503.632812,1438.406251,1167.359374,902.632813,1074.085938,1181.718750,1033.679688,1100.570312,1246.812500,1099.148438,1300.749999,1523.664063,1866.234375,1475.234375,1382.398438,1582.992188,1523.609375,1469.671875</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>0.186278,0.074368,0.324599,0.373669,0.479463,0.626671,0.647170,1.871286,1.513201,1.166331,1.390965,1.531513,1.337331,1.425193,1.616727,1.423048,1.686875,1.983754,2.438504,1.918911,1.796530,2.060821,1.982223,1.910156</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>1.323566148624642</v>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>78232.085938,78272.765625,78291.125000,78296.976562,78361.664062,78312.664062,78269.781250,78276.117188,78167.921875,78372.062500,78296.867188,78261.359375,78327.093750,78340.078125,78351.414062,78215.609375,78289.632812,78224.960938,78326.453125,78254.640625,78343.679688,78254.250000,78273.218750,78297.289062</t>
@@ -5764,6 +5820,49 @@
       <c r="M54" t="inlineStr">
         <is>
           <t>78216.054688,78111.781250,78078.031250,78076.859375,77934.750000,77875.468750,77863.125000,77863.375000,77912.625000,77782.148438,77690.195312,77733.773438,77751.531250,77727.773438,77789.203125,77714.375000,77810.289062,77654.265625,77713.640625,77667.265625,77683.710938,77670.445312,77652.445312,77671.242188</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:19:48</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>24</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>76974.164062,76961.031250,76970.554688,76978.296875,76962.328125,76937.484375,76928.843750,76912.562500,76926.687500,76879.218750,76852.882812,76890.914062,76904.148438,76860.218750,76922.468750,76939.875000,76965.632812,76911.812500,76935.968750,76891.375000,76912.367188,76922.695312,76882.570312,76902.750000</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>76861.304688,76914.859375,76874.273438,76927.046875,76992.593750,76954.140625,76926.453125,76929.593750,76813.492188,76992.109375,76859.125000,76848.226562,76855.265625,76904.773438,76955.070312,76829.765625,76948.093750,76962.140625,77004.656250,76833.875000,76958.156250,76838.234375,76856.859375,76850.890625</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>76599.968750,76555.945312,76410.195312,76440.828125,76311.828125,76269.156250,76252.234375,76173.843750,76067.265625,75970.562500,75849.468750,75910.835938,75824.789062,75838.976562,75900.210938,75838.851562,75864.531250,75781.601562,75669.242188,75608.515625,75611.171875,75639.671875,75568.617188,75582.015625</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>76789.515625,76678.687500,76652.851562,76586.179688,76529.820312,76424.851562,76419.335938,76392.000000,76470.843750,76304.734375,76190.539062,76231.296875,76239.789062,76182.914062,76302.171875,76266.890625,76246.757812,76125.601562,76153.023438,76103.742188,76157.890625,76061.593750,76066.656250,76077.453125</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2507,6 +2507,44 @@
       </c>
       <c r="F55" t="n">
         <v>76902.75</v>
+      </c>
+      <c r="G55" t="n">
+        <v>77238.1171875</v>
+      </c>
+      <c r="H55" t="n">
+        <v>335.3671875</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.4341990712770441</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.6596822336159527</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-12 04:17:59</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>24</v>
+      </c>
+      <c r="F56" t="n">
+        <v>77049.0546875</v>
       </c>
     </row>
   </sheetData>
@@ -2520,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5850,6 +5888,24 @@
           <t>76974.164062,76961.031250,76970.554688,76978.296875,76962.328125,76937.484375,76928.843750,76912.562500,76926.687500,76879.218750,76852.882812,76890.914062,76904.148438,76860.218750,76922.468750,76939.875000,76965.632812,76911.812500,76935.968750,76891.375000,76912.367188,76922.695312,76882.570312,76902.750000</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>77225.281250,77265.117188,77199.531250,77337.070312,77021.976562,76966.640625,77014.882812,77990.859375,79206.562500,78789.507812,77703.351562,77904.117188,77505.179688,77017.671875,77282.859375,77305.953125,77104.179688,77121.609375,77208.656250,77271.109375,77250.023438,77286.351562,77259.226562,77238.117188</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>251.117188,304.085938,228.976562,358.773438,59.648438,29.156250,86.039062,1078.296875,2279.875000,1910.289062,850.468751,1013.203126,601.031249,157.453125,360.390625,366.078125,138.546876,209.796875,272.687500,379.734375,337.656249,363.656251,376.656251,335.367188</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0.325175,0.393562,0.296604,0.463909,0.077443,0.037882,0.111717,1.382594,2.878392,2.424548,1.094507,1.300577,0.775472,0.204438,0.466327,0.473545,0.179688,0.272034,0.353183,0.491431,0.437095,0.470531,0.487523,0.434199</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>0.6596822336159527</v>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>76861.304688,76914.859375,76874.273438,76927.046875,76992.593750,76954.140625,76926.453125,76929.593750,76813.492188,76992.109375,76859.125000,76848.226562,76855.265625,76904.773438,76955.070312,76829.765625,76948.093750,76962.140625,77004.656250,76833.875000,76958.156250,76838.234375,76856.859375,76850.890625</t>
@@ -5863,6 +5919,49 @@
       <c r="M55" t="inlineStr">
         <is>
           <t>76789.515625,76678.687500,76652.851562,76586.179688,76529.820312,76424.851562,76419.335938,76392.000000,76470.843750,76304.734375,76190.539062,76231.296875,76239.789062,76182.914062,76302.171875,76266.890625,76246.757812,76125.601562,76153.023438,76103.742188,76157.890625,76061.593750,76066.656250,76077.453125</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-12 04:17:59</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>24</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>77226.367188,77207.531250,77218.179688,77252.718750,77218.570312,77180.078125,77184.734375,77174.148438,77187.703125,77135.015625,77111.421875,77129.546875,77103.000000,77053.328125,77108.859375,77067.312500,77076.695312,77067.125000,77079.312500,77015.312500,77074.789062,77090.390625,77046.171875,77049.054688</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>77113.804688,77204.875000,77164.843750,77229.085938,77276.789062,77164.835938,77177.437500,77180.757812,77056.851562,77190.398438,77088.640625,77059.632812,77016.765625,77086.640625,77101.992188,76994.421875,77010.984375,77029.140625,77062.312500,76957.429688,77096.328125,76944.570312,76988.125000,76946.921875</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>76910.531250,76853.593750,76727.421875,76800.453125,76654.554688,76584.804688,76542.101562,76485.445312,76356.609375,76243.906250,76112.093750,76138.226562,75996.109375,76060.664062,76075.312500,75968.523438,75913.031250,75850.843750,75698.234375,75602.562500,75665.890625,75723.835938,75650.953125,75589.742188</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>77100.742188,76994.250000,76954.531250,76947.609375,76845.726562,76736.750000,76703.390625,76708.250000,76765.085938,76619.335938,76483.117188,76479.804688,76500.515625,76431.257812,76502.570312,76444.109375,76381.250000,76272.546875,76283.007812,76203.546875,76276.890625,76207.750000,76213.093750,76227.328125</t>
         </is>
       </c>
     </row>
